--- a/المنتجات/batch1-merchant-seo.xlsx
+++ b/المنتجات/batch1-merchant-seo.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>بالمرز مرطب ستيك للشفاه بزبدة الكاكاو - 14جرا من Palmer's، منتج يصنَّف ضمن فئة مرطب شفاه. يُمرَّر المرطب مباشرة على الشفاه لتوزيعه، ويمكن إعادة التطبيق عند الحاجة خلال اليوم. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم.</t>
+          <t>مرطب ستيك للشفاه بزبدة الكاكاو من بالمرز، 14 جم، Palmer's Cocoa Butter Lip Balm Stick من Palmer's؛ مرطب شفاه بصيغة ستيك، بحجم 14 جم. يأتي مرطب الشفاه من بالمرز بصيغة ستيك عملية، مع ذكر زبدة الكاكاو ضمن اسم المنتج. يمنحك هذا الشكل طريقة مباشرة لوضع المرطب على الشفاه، ويسهل حمله واستخدامه عند الحاجة ضمن روتين العناية اليومي.يعرض المنتج بحجم 14 جم، وتناسب صيغته الاستخدام على الشفاه من دون الحاجة إلى أداة منفصلة للتطبيق. ويمكن إدراجه في حقيبة العناية الشخصية أو وضعه في مكان يسهل الوصول إليه، مع الالتزام بطريقة الاستخدام الموضحة على العبوة. يتميز المنتج بأن مرطب مخصص للشفاه، ويأتي بصيغة ستيك سهلة التطبيق، وتُذكر زبدة الكاكاو في اسم المنتج. مرري الستيك برفق على الشفاه لتوزيع المنتج عليها. أعيدي التطبيق عند الرغبة وفق الحاجة، وأغلقي العبوة بعد الاستخدام. اتبعي أي إرشادات إضافية واردة على ملصق المنتج.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>يقدَّم شامبو بريورين للشعر الضعيف والمتساقط 200 مل كأحد منتجات Priorin في فئة شامبو. الحجم المدوَّن على العبوة هو 200 مل. يُطبَّق على الشعر الرطب مع التدليك برفق، ثم يُشطف بالماء قبل استخدام البلسم إن وُجد. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم.</t>
+          <t>شامبو بريورين للشعر الضعيف والمتساقط 200 مل، Priorin Shampoo for Weak and Falling Hair من Priorin؛ شامبو للشعر بحجم 200 مل. شامبو بريورين منتج مخصص لتنظيف الشعر، ويشير اسمه إلى الشعر الضعيف والمتساقط. يأتي في عبوة بحجم 200 مل، ويمكن إدراجه ضمن خطوات غسل الشعر المعتادة وفق احتياجك وطريقة العناية التي تتبعينها.يُستخدم الشامبو على الشعر أثناء الاستحمام، ثم يُشطف بالماء بحسب إرشادات العبوة. ويُعرّف المنتج من خلال نوعه وحجمه والفئة المذكورة في اسمه، من دون أن يعني ذلك وعداً بنتيجة محددة؛ لذلك يُستحسن الالتزام بتعليمات الاستخدام المطبوعة على العبوة. من أبرز خصائصه أن شامبو مخصص لتنظيف الشعر، ويشير الاسم إلى الشعر الضعيف والمتساقط، وحجم العبوة المذكور 200 مل. بللي الشعر، ثم ضعي كمية مناسبة من الشامبو ودلكي الشعر وفروة الرأس برفق، وبعدها اشطفيه جيداً بالماء. يُراعى الرجوع إلى الإرشادات الموجودة على العبوة، وتجنب ملامسة العينين أثناء الاستخدام.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ماسكارا Maybelline New York المعروف باسم ماسكارا مايلبين جلام بلاك، وهو منتج موجه لهذه الفئة من العناية. تُستخدم الماسكارا بتمرير الفرشاة على الرموش مع الحرص على عدم ملامسة العينين، ويمكن إدراجها ضمن خطوات مكياج العيون اليومي. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه.</t>
+          <t>ماسكارا مايلبين جلام بلاك، Maybelline Glam Black Mascara من Maybelline؛ ماسكارا للرموش بدرجة جلام بلاك. ماسكارا مايلبين جلام بلاك منتج تجميلي مخصص للرموش، ويظهر اسم جلام بلاك ضمن تسمية المنتج. تساعد الماسكارا على إضافة لمسة لونية للرموش ضمن إطلالة مكياج العيون، ويمكن استخدامها بمفردها أو بعد إكمال بقية خطوات المكياج.لم يرد حجم للعبوة في اسم المنتج، لذلك لا يُفترض حجم محدد هنا. اختاري طريقة التطبيق التي تفضلينها، ومرري الفرشاة على الرموش بحركة هادئة مع الحرص على عدم ملامسة العينين. وللتفاصيل الخاصة بالعبوة أو طريقة إزالة الماسكارا، اتبعي الإرشادات المرفقة مع المنتج. يذكر عن هذا المنتج أنه ماسكارا مخصصة للرموش، وتحمل اسم جلام بلاك، وتندرج ضمن مستحضرات مكياج العيون. مرري فرشاة الماسكارا على الرموش برفق من الجذور باتجاه الأطراف، مع تجنب إدخال المنتج إلى العين أو ملامستها. أغلقي العبوة بعد الاستخدام، وراجعي تعليمات الشركة على العبوة بشأن التطبيق والإزالة.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>من تشكيلة Maybelline New York، يأتي ماسكارا مايبيلين دبليو بي ضمن تصنيف ماسكارا. يُطبَّق المنتج على الرموش بحركات خفيفة من الجذور إلى الأطراف، ويُنظَّف بالمزيل المخصص بعد الاستخدام. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف.</t>
+          <t>ماسكارا مايبيلين دبليو بي، Maybelline WP Mascara من Maybelline؛ ماسكارا للرموش تحمل تسمية دبليو بي. تأتي ماسكارا مايبيلين دبليو بي ضمن مستحضرات العيون المخصصة للرموش. وتُذكر تسمية دبليو بي في اسمها كما وردت، من دون إضافة وصف آخر غير وارد في بيانات المنتج. يمكن استخدام الماسكارا لإكمال إطلالة مكياج العيون بالطريقة المعتادة، مع تطبيقها على الرموش بحذر.لا يذكر الاسم المتاح درجة لونية أو حجماً للعبوة، لذلك يقتصر الوصف على المعلومات الواضحة في تسمية المنتج ونوعه. للمزيد عن خصائص العبوة أو تعليمات الاستخدام والإزالة، يُرجى مراجعة البيانات المطبوعة عليها. احرصي على إغلاق المنتج بعد الاستعمال وعدم مشاركة أدوات مكياج العيون. تشمل خصائصه أن ماسكارا مخصصة للرموش، ومن علامة مايبيلين، وتحمل اسم دبليو بي كما ورد في تسمية المنتج. استخدمي فرشاة الماسكارا لتمرير المنتج على الرموش بلطف، مع تجنب ملامسة العينين. أغلقي العبوة بعد الانتهاء، واتبعي الإرشادات المرفقة لمعرفة تفاصيل التطبيق والإزالة الخاصة بهذا المنتج.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>يندرج ماسكارا مايبيلين السوداء الصادر عن Maybelline New York ضمن منتجات ماسكارا. تُستخدم الماسكارا بتمرير الفرشاة على الرموش مع الحرص على عدم ملامسة العينين، ويمكن إدراجها ضمن خطوات مكياج العيون اليومي. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف.</t>
+          <t>ماسكارا مايبيلين السوداء، Maybelline Black Mascara من Maybelline؛ ماسكارا للرموش بدرجة سوداء. ماسكارا مايبيلين السوداء مستحضر من مستحضرات مكياج العيون مخصص للرموش، وتوضح تسمية المنتج درجته السوداء. تمنحك أداة الماسكارا وسيلة لوضع اللون على الرموش ضمن خطوات المكياج، سواء كانت هذه الخطوة منفردة أو جزءاً من إطلالة متكاملة.لا يرد في الاسم حجم العبوة أو وصف إضافي للنتيجة، لذا يقتصر التعريف هنا على نوع المنتج والدرجة المذكورة. ضعيها على الرموش بحركة لطيفة، واحرصي على إغلاق العبوة بعد الاستخدام. ويمكن الرجوع إلى العبوة لمعرفة الإرشادات الخاصة بالتطبيق والإزالة والتخزين. يتميز المنتج بأن ماسكارا مخصصة للرموش، وتأتي بدرجة سوداء بحسب الاسم، ومن منتجات مكياج العيون. مرري الفرشاة على الرموش لتوزيع المنتج، مع استخدام حركة متأنية والابتعاد عن داخل العين. أغلقي العبوة بإحكام بعد الاستخدام، واتبعي الإرشادات المدونة عليها عند إزالة الماسكارا أو حفظها.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Maybelline New York تقدم من خلال كونسيلر مايبيلين فيت مي رقم 10 منتجاً في فئة كونسيلر. يُطبَّق المنتج بلطف على البشرة بعد كريم الأساس أو قبله حسب الروتين المفضل للمستخدمة. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص.</t>
+          <t>كونسيلر مايبيلين فيت مي رقم 10، Maybelline Fit Me Concealer Shade 10 من Maybelline؛ كونسيلر للوجه بدرجة 10. كونسيلر فيت مي من مايبيلين مستحضر للوجه يُستخدم ضمن خطوات المكياج لإخفاء مظهر بعض المناطق أو تصحيح مظهرها. يحدد اسم المنتج الدرجة برقم 10، ما يتيح تمييزها عن الدرجات الأخرى ضمن التسمية، من دون أن يورد الاسم وصفاً لونياً إضافياً أو حجماً للعبوة.يمكن وضع الكونسيلر على المواضع التي ترغبين في معالجتها تجميلياً، ثم دمجه بلطف مع البشرة أو مع بقية المكياج. تتفاوت ملاءمة الدرجة بحسب تفضيلات كل شخص وبقية منتجات المكياج المستخدمة؛ لذا يُستحسن مراجعة الدرجة على العبوة واختيارها بما يتناسب مع استخدامك. من أبرز خصائصه أن كونسيلر مخصص للاستخدام على الوجه، ومن مجموعة فيت مي من مايبيلين، ويحمل رقم الدرجة 10. ضعي كمية مناسبة على الموضع المراد تغطيته، ثم ادمجيها بلطف بأطراف الأصابع أو بأداة المكياج المناسبة. ابدئي بكمية قليلة وأضيفي المزيد عند الحاجة، مع اتباع تعليمات العبوة وتجنب ملامسة العينين.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>كونسيلر مايبيلين فيت مي رقم 15 من Maybelline New York، منتج يصنَّف ضمن فئة كونسيلر. يُستخدم الكونسيلر بنقاط صغيرة على مناطق التفاوت في لون البشرة ثم يُدمج بإسفنجة أو فرشاة مخصصة. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم.</t>
+          <t>كونسيلر مايبيلين فيت مي رقم 15، Maybelline Fit Me Concealer Shade 15 من Maybelline؛ كونسيلر للوجه بدرجة 15. يُصنف كونسيلر مايبيلين فيت مي ضمن مستحضرات المكياج المخصصة للوجه، ويُستخدم لإخفاء مظهر مناطق معينة أو تصحيح مظهرها ضمن الإطلالة. يحمل المنتج رقم الدرجة 15 في اسمه، وهو البيان المحدد للدرجة المتاح هنا، من دون ذكر حجم العبوة.تُوضع كمية مناسبة على الموضع المرغوب وتُدمج مع البشرة لتنسجم مع بقية خطوات المكياج. اختاري الدرجة وفق تفضيلك وطريقة تنسيقها مع مستحضرات الوجه الأخرى، مع الاستناد إلى الرقم المكتوب على العبوة. لا يحدد الاسم خصائص أخرى مثل التغطية أو الثبات، لذا يُرجى مراجعة معلومات المنتج المطبوعة عند الحاجة. يذكر عن هذا المنتج أنه مستحضر كونسيلر للوجه، ومن خط فيت مي من مايبيلين، ورقم الدرجة المذكور هو 15. ضعي المنتج على المنطقة التي ترغبين في إخفاء مظهرها، ثم ادمجيه بلطف باستخدام أداة مناسبة أو أطراف الأصابع. يمكن إضافة كمية أخرى عند الحاجة، مع الحرص على استخدامه خارجياً واتباع التعليمات الواردة على العبوة.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>يقدَّم كونسيلر مايبيلين فيت مي رقم 20 كأحد منتجات Maybelline New York في فئة كونسيلر. يُطبَّق المنتج بلطف على البشرة بعد كريم الأساس أو قبله حسب الروتين المفضل للمستخدمة. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه.</t>
+          <t>كونسيلر مايبيلين فيت مي رقم 20، Maybelline Fit Me Concealer Shade 20 من Maybelline؛ كونسيلر للوجه بدرجة 20. كونسيلر فيت مي بدرجة 20 هو مستحضر مكياج للوجه من مايبيلين، مخصص للاستخدام في خطوات الإخفاء والتصحيح التجميلي. يساعد وجود رقم الدرجة ضمن الاسم على تحديد النسخة المطلوبة عند الاختيار، ولا يرد في البيانات المتاحة وصف لوني إضافي أو حجم للعبوة.يمكن تطبيقه على مواضع محددة من الوجه ثم دمجه مع البشرة للحصول على مظهر متناسق مع بقية المكياج. تختلف الدرجة المناسبة باختلاف تفضيلات الاستخدام وطريقة تنسيقها، لذلك يُنصح بالتحقق من رقم 20 على المنتج نفسه. وللتفاصيل غير الواردة في الاسم، اعتمدي على المعلومات المطبوعة على العبوة. تشمل خصائصه أن كونسيلر مخصص للوجه، ويحمل تسمية فيت مي من مايبيلين، ورقم الدرجة الوارد هو 20. ضعي مقداراً مناسباً على المنطقة التي ترغبين في تصحيح مظهرها، وادمجيه بخفة باستخدام أداة مكياج أو أطراف الأصابع. ابدئي بكمية صغيرة، واتبعي إرشادات الاستخدام المطبوعة على العبوة.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>كونسيلر Maybelline New York المعروف باسم كونسيلر خافي عيوب فيت مي من ميبلين 30، وهو منتج موجه لهذه الفئة من العناية. يُستخدم الكونسيلر بنقاط صغيرة على مناطق التفاوت في لون البشرة ثم يُدمج بإسفنجة أو فرشاة مخصصة. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه.</t>
+          <t>كونسيلر خافي عيوب فيت مي من ميبلين 30، Maybelline Fit Me Concealer Shade 30 من Maybelline؛ كونسيلر للوجه بدرجة 30. كونسيلر خافي العيوب من فيت مي مستحضر تجميلي للوجه، ويظهر رقم 30 ضمن اسم المنتج بوصفه رقم الدرجة. يُستخدم في المكياج لإخفاء مظهر مناطق محددة أو للمساعدة على تصحيح مظهرها، ثم يمكن دمجه مع بقية مستحضرات البشرة للحصول على إطلالة متناسقة.لا يحدد الاسم المتاح حجم العبوة، ولا يضيف وصفاً آخر لدرجة اللون؛ لذا يُعتمد على الرقم 30 الظاهر في التسمية عند التمييز بين النسخ. اختاري الدرجة بما يناسب تفضيلك وطريقة استخدامك، وراجعي المعلومات المطبوعة على العبوة لمعرفة تعليمات المنتج المحددة. يتميز المنتج بأن كونسيلر خافي عيوب للوجه، ويحمل اسم فيت مي من ميبلين، ورقم الدرجة المذكور هو 30. ضعي كمية مناسبة على الموضع المراد إخفاء مظهره، ثم وزعيها وادمجيها بلطف مع البشرة باستخدام أداة مناسبة أو أطراف الأصابع. أضيفي كمية أخرى عند الحاجة، مع اتباع الإرشادات المطبوعة على العبوة.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>من تشكيلة Maybelline New York، يأتي ماسكارا مايبيلين سموكي ضمن تصنيف ماسكارا. يُطبَّق المنتج على الرموش بحركات خفيفة من الجذور إلى الأطراف، ويُنظَّف بالمزيل المخصص بعد الاستخدام. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف.</t>
+          <t>ماسكارا مايبيلين سموكي، Maybelline Smoky Mascara من Maybelline؛ ماسكارا للرموش تحمل تسمية سموكي. ماسكارا مايبيلين سموكي مستحضر تجميلي للعيون مخصص للرموش. وتظهر كلمة سموكي ضمن اسم المنتج، من دون أن يذكر الاسم المتاح درجة لونية أو حجماً محدداً للعبوة. يمكن إدخالها ضمن خطوات مكياج العيون وتطبيقها على الرموش باستخدام فرشاة الماسكارا.يتيح شكل الماسكارا وضع المنتج مباشرة على الرموش، مع الحرص على التحرك بهدوء وتجنب ملامسة العينين. لم تُذكر تفاصيل إضافية عن خصائص الماسكارا أو نتائجها، لذلك يُنصح بالاعتماد على معلومات العبوة لمعرفة تعليمات الاستخدام والإزالة الخاصة بها وإغلاقها جيداً بعد الاستعمال. من أبرز خصائصه أن ماسكارا مخصصة للرموش، ومن علامة مايبيلين، وتحمل تسمية سموكي في اسمها. مرري فرشاة الماسكارا على الرموش بلطف لتوزيع المنتج، مع تجنب ملامسة العين أو إدخال المستحضر إليها. بعد الانتهاء، أغلقي العبوة بإحكام. راجعي التعليمات المرفقة لمعرفة طريقة الإزالة وأي إرشادات إضافية.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>يندرج Maybelline مايبيلين ماسكارا لاش سينسيشينال فايرورك 10 مل الصادر عن Maybelline New York ضمن منتجات ماسكارا. تبلغ سعة العبوة 10 مل كما هو موضح على المنتج. تُستخدم الماسكارا بتمرير الفرشاة على الرموش مع الحرص على عدم ملامسة العينين، ويمكن إدراجها ضمن خطوات مكياج العيون اليومي. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف.</t>
+          <t>ماسكارا لاش سينسيشينال فايرورك Lash Sensational Firework Mascara من Maybelline New York، ماسكارا للرموش بحجم 10 مل. تأتي ماسكارا لاش سينسيشينال فايرورك من Maybelline New York لتكون خطوة مخصصة لمكياج الرموش. يحدد الاسم نوع المستحضر بوضوح، ويمنحك خياراً لإضافة الماسكارا إلى إطلالتك اليومية أو إلى تنسيق مكياج العيون لمناسبة خاصة، من دون الحاجة إلى تغيير بقية اختياراتك.يمكن تنسيقها مع مكياج بسيط يترك التركيز على العينين، أو استعمالها ضمن إطلالة متكاملة بحسب أسلوبك. ويُذكر حجم 10 مل في اسم المنتج، لتكون تفاصيل العبوة واضحة عند الاختيار. يذكر عن هذا المنتج أنه مستحضر مخصص لمكياج الرموش، واسم المنتج يوضح مجموعة Lash Sensational Firework، وحجم العبوة المذكور هو 10 مل. تُستخدم على الرموش ضمن روتين المكياج. مرري أداة التطبيق على الرموش بحركة هادئة من الجذور باتجاه الأطراف، ثم أضيفي تمريرة أخرى عند الحاجة إلى مزيد من التغطية. اتركي المستحضر يجف قبل استكمال بقية خطوات مكياج العين.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Maybelline New York تقدم من خلال مسكرة رموش ميبلين سكاي هاي برغندي منتجاً في فئة ماسكارا. يُطبَّق المنتج على الرموش بحركات خفيفة من الجذور إلى الأطراف، ويُنظَّف بالمزيل المخصص بعد الاستخدام. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص.</t>
+          <t>ماسكارا سكاي هاي برغندي Sky High Mascara Burgundy من Maybelline New York، ماسكارا للرموش بدرجة Burgundy. تجمع هذه الماسكارا بين اسم مجموعة Sky High ودرجة Burgundy كما وردتا في اسم المنتج. وهي خيار لمكياج الرموش لمن ترغب في إدخال درجة لونية محددة إلى تنسيق العين، مع إمكانية تنسيقها مع ظلال هادئة أو اعتمادها مع بقية الألوان التي تختارينها.يساعد تحديد الدرجة في الاسم على التعرف إلى اللون المقصود عند الاختيار، فيما يوضح اسم Sky High مجموعة المنتج. لا يرد حجم العبوة في الاسم المتاح، لذلك تبقى الدرجة والعلامة ونوع المستحضر هي التفاصيل المعروفة هنا. تشمل خصائصه أن ماسكارا مخصصة لمكياج الرموش، وتحمل اسم مجموعة Sky High، وترد درجة Burgundy في اسم المنتج. مرري أداة التطبيق على الرموش بهدوء من الجذور إلى الأطراف، مع توزيع المستحضر على الرموش التي ترغبين في إبرازها. يمكن إضافة تمريرة أخرى بحسب النتيجة التي تفضلينها، ثم اتركيه يجف قبل وضع مستحضرات أخرى حول العين.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ميبيلين احمر شفاه سوبر ستاي - 105 جولدن 4.2مل من Maybelline New York، منتج يصنَّف ضمن فئة أحمر شفاه. يأتي بحجم 4.2 مل، وهو الحجم المذكور على العبوة دون غيره. يُطبَّق أحمر الشفاه مباشرة على الشفاه، ويمكن تحديد الشفاه بقلم محدد قبل التطبيق للحصول على مظهر أوضح. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص.</t>
+          <t>أحمر شفاه سوبر ستاي 105 جولدن Super Stay Lipstick 105 Golden من Maybelline New York، أحمر شفاه بدرجة 105 Golden وبحجم 4.2 مل. أحمر شفاه سوبر ستاي من Maybelline New York مستحضر مخصص لمكياج الشفاه، وتظهر درجته في الاسم بصيغة 105 Golden. يتيح ذكر الرقم والاسم اللوني التعرف إلى الدرجة المطلوبة عند تنسيق المكياج، سواء اختيرت الشفاه لتكون نقطة التركيز أو جرى تنسيقها مع بقية الألوان.يبلغ الحجم المذكور 4.2 مل، وهو تفصيل عملي عند مقارنة المنتجات المعروضة. يظل اسم Super Stay جزءاً من تسمية المنتج، أما طريقة تنسيق اللون فترجع إلى أسلوبك واختياراتك في المكياج. يتميز المنتج بأن أحمر شفاه مخصص لتلوين الشفاه، ويحمل اسم مجموعة Super Stay، وتظهر الدرجة باسم 105 Golden. يوضع أحمر الشفاه على شفاه نظيفة، مع تمريره على الشفتين وتوزيعه حتى الوصول إلى المظهر الذي تفضلينه. يمكن تحديد حدود الشفاه أولاً إذا كان ذلك ضمن أسلوبك، ثم تنسيق بقية المكياج بما ينسجم مع الدرجة المختارة.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>يقدَّم روج سائل سوبر ستاي إكسترا من ميبيلين - 130 كأحد منتجات Maybelline New York في فئة أحمر شفاه. يُستخدم المنتج بتمريره على الشفاه مع إمكانية إعادة التطبيق خلال اليوم حسب الحاجة. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه.</t>
+          <t>روج سائل سوبر ستاي إكسترا 130 Super Stay Extra Liquid Lipstick 130 من Maybelline New York، أحمر شفاه سائل بالدرجة 130. هذا الروج السائل من مجموعة سوبر ستاي إكسترا لدى Maybelline New York، وقد ورد رقم 130 بوصفه الدرجة في اسم المنتج. يندرج ضمن مستحضرات الشفاه التي تطبق بصيغة سائلة، لتختاريه عند إعداد مكياج تبرز فيه الشفاه أو عند تنسيق لونه مع بقية المستحضرات.يساعد رقم الدرجة على تمييز هذا الاختيار عن الدرجات الأخرى، بينما لا يذكر الاسم حجماً للعبوة أو تسمية لونية إضافية. لذلك تقتصر التفاصيل المتاحة على اسم المنتج ونوعه ورقم درجته والعلامة التجارية. من أبرز خصائصه أن أحمر شفاه سائل لمكياج الشفاه، ويحمل اسم Super Stay Extra، ورقم الدرجة المذكور هو 130. مرري أداة التطبيق على الشفتين، وابدئي بكمية مناسبة ثم وزعي اللون بهدوء حتى تغطية المساحة المرغوبة. اتركيه يستقر قبل ملامسة الشفاه أو استكمال المكياج، واتبعي الطريقة التي تناسبك في تحديد حدود الشفتين وتنسيق اللون.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>أحمر شفاه Maybelline New York المعروف باسم ميبيلين احمر شفاه سائل فينيل انك 20، وهو منتج موجه لهذه الفئة من العناية. يُطبَّق أحمر الشفاه مباشرة على الشفاه، ويمكن تحديد الشفاه بقلم محدد قبل التطبيق للحصول على مظهر أوضح. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه.</t>
+          <t>أحمر شفاه سائل فينيل إنك Vinyl Ink Liquid Lipstick 20 من Maybelline New York، أحمر شفاه سائل بالدرجة 20. يأتي أحمر الشفاه السائل Vinyl Ink من Maybelline New York ضمن مستحضرات مكياج الشفاه، ويحمل رقم 20 في اسم المنتج. صيغة المستحضر السائلة تجعله خياراً لتطبيق اللون على الشفتين بأداة الاستخدام، مع إمكان تنسيقه مع أساليب مكياج مختلفة وفق ذوقك.يساعد ذكر الرقم في الاسم على تحديد الدرجة المقصودة عند الاختيار، بينما لا تظهر تسمية لونية أخرى أو حجم للعبوة في البيانات المتاحة. ويمكن أن يكون أحمر الشفاه جزءاً من إطلالة بسيطة أو من تنسيق متكامل تختارين ألوانه بعناية. يذكر عن هذا المنتج أنه مستحضر شفاه بصيغة سائلة، ويحمل اسم Vinyl Ink، ورقم الدرجة المسجل في الاسم هو 20. استخدمي أداة التطبيق لتوزيع اللون على الشفتين، وابدئي من منتصفهما باتجاه الأطراف مع مراعاة حدود الشفاه. اتركي المستحضر يستقر قبل متابعة بقية المكياج. ولإزالة أي زيادة، يمكن تعديل حدود اللون بلطف بالطريقة المعتادة لديك.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>من تشكيلة Maybelline New York، يأتي Maybelline أحمر شفاه سوبر ستاي فينيل إنك 40 ويتي ضمن تصنيف أحمر شفاه. يُستخدم المنتج بتمريره على الشفاه مع إمكانية إعادة التطبيق خلال اليوم حسب الحاجة. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف.</t>
+          <t>أحمر شفاه سوبر ستاي فينيل إنك 40 ويتي Super Stay Vinyl Ink Lipstick 40 Witty، أحمر شفاه سائل بدرجة 40 Witty من Maybelline New York. يضم اسم المنتج مجموعة Super Stay Vinyl Ink، مع رقم 40 والاسم Witty لتحديد الدرجة. وهو أحمر شفاه سائل لمكياج الشفاه، يتيح لك إضافة لون محدد إلى مظهرك وتنسيقه بحسب ألوان الملابس أو بقية مستحضرات المكياج التي تختارينها.يمكن اعتماد اللون وحده ضمن مكياج هادئ أو إدخاله في تنسيق أكثر تفصيلاً، فالاختيار يعود إلى أسلوبك. لا يتضمن الاسم حجماً للعبوة، لذلك تقتصر البيانات المعروضة على اسم المنتج ونوعه ودرجته والعلامة التجارية. تشمل خصائصه أن أحمر شفاه سائل مخصص للشفاه، ويحمل اسم Super Stay Vinyl Ink، والدرجة محددة بالرقم 40 والاسم Witty. ضعي اللون على الشفتين بأداة التطبيق، مع اتباع حدودهما وتوزيع المستحضر على المساحة المطلوبة. ابدئي بطبقة متوازنة، ثم اتركيها تستقر قبل استكمال مكياجك. يمكن تعديل رسم الشفاه بالطريقة التي تعتمدينها عادة.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>يندرج ماسكارا مايبلين نيويورك سينسيشينال سكاي هاي الصادر عن Maybelline New York ضمن منتجات ماسكارا. تُستخدم الماسكارا بتمرير الفرشاة على الرموش مع الحرص على عدم ملامسة العينين، ويمكن إدراجها ضمن خطوات مكياج العيون اليومي. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف.</t>
+          <t>ماسكارا سينسيشينال سكاي هاي Sensational Sky High Mascara من Maybelline New York، ماسكارا مخصصة لمكياج الرموش. تقدم Maybelline New York ماسكارا سينسيشينال سكاي هاي ضمن مستحضرات مكياج العين. يذكر الاسم نوع المنتج ومجموعته، فتكون مناسبة لمن تبحث عن ماسكارا للرموش وتفضل اختيار منتجاتها بالاسم المعروف للمجموعة. لا تظهر درجة لونية أو سعة للعبوة ضمن الاسم المقدم.يمكن إدخالها في روتين المكياج اليومي أو استخدامها عند إعداد إطلالة أكثر اكتمالاً. وتبقى طريقة تنسيق الرموش مع الظلال أو محدد العين مرتبطة بالنتيجة التي ترغبين بها، بينما تتمثل تفاصيل المنتج المعروفة في نوعه واسمه وعلامته التجارية. يتميز المنتج بأن مستحضر مكياج مخصص للرموش، ويحمل اسم Sensational Sky High، ومن علامة Maybelline New York. استخدمي أداة التطبيق لتمرير المستحضر على الرموش من الجذور نحو الأطراف، مع إبقاء الحركة هادئة ومتوازنة. أعيدي التمرير عند الحاجة وفق المظهر الذي تفضلينه، ثم انتظري حتى يجف قبل متابعة تطبيق مستحضرات مكياج العين.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Maybelline New York تقدم من خلال ماسكارا مايبيلين لاش سكاي هاي ترو منتجاً في فئة ماسكارا. يُطبَّق المنتج على الرموش بحركات خفيفة من الجذور إلى الأطراف، ويُنظَّف بالمزيل المخصص بعد الاستخدام. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص.</t>
+          <t>ماسكارا لاش سكاي هاي ترو Lash Sky High True Mascara من Maybelline New York، ماسكارا للرموش باسم Sky High True. تندرج ماسكارا لاش سكاي هاي ترو ضمن مستحضرات مكياج الرموش من Maybelline New York. ويظهر اسم Sky High True في التسمية كما ورد، من دون بيان درجة لونية أو حجم للعبوة. يمكن اختيارها كخطوة مستقلة لمكياج العين أو تنسيقها مع الظلال ومحدد العين وفق أسلوبك.تركز هذه الفئة على استخدام المستحضر على الرموش، وتمنحك مساحة لترتيب بقية تفاصيل المكياج حول العين. ولأن الاسم لا يورد معلومات إضافية عن الدرجة أو الحجم، فالبيانات المحددة هنا هي اسم المنتج ونوعه والعلامة التجارية. من أبرز خصائصه أن ماسكارا مخصصة للرموش، ويحمل الاسم عبارة Sky High True، ومن Maybelline New York. مرري أداة التطبيق على الرموش بلطف، مع البدء بالقرب من الجذور والتحرك إلى الأطراف. وزعي المستحضر على الرموش التي ترغبين في وضع المكياج عليها، ثم اتركيه حتى يجف. اكملي مكياج العين بعد ذلك بالطريقة المعتادة لديك.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ميبيلين احمر شفاه سائل سوبر ستاي 25 ريد هوت من Maybelline New York، منتج يصنَّف ضمن فئة أحمر شفاه. يُطبَّق أحمر الشفاه مباشرة على الشفاه، ويمكن تحديد الشفاه بقلم محدد قبل التطبيق للحصول على مظهر أوضح. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم.</t>
+          <t>أحمر شفاه سائل سوبر ستاي 25 ريد هوت Super Stay Liquid Lipstick 25 Red Hot من Maybelline New York، أحمر شفاه سائل بدرجة 25 Red Hot. أحمر الشفاه السائل سوبر ستاي من Maybelline New York يحمل الدرجة 25 Red Hot كما وردت في اسم المنتج. تمنحك هذه التسمية رقماً واسم درجة محددين للتعرف إلى المنتج عند الاختيار، وتجعله خياراً لمكياج الشفاه سواء أدرجته ضمن إطلالة يومية أم نسقته مع مكياج أكثر اكتمالاً.توضح تسمية Super Stay اسم المجموعة، فيما يحدد وصف أحمر الشفاه السائل نوع المستحضر. لا يتضمن الاسم حجماً للعبوة، لذا تظل المعلومات المتاحة هي العلامة التجارية والنوع ورقم الدرجة واسمها. يذكر عن هذا المنتج أنه أحمر شفاه سائل لمكياج الشفاه، ويحمل اسم Super Stay، والدرجة محددة باسم 25 Red Hot. ضعي المستحضر على الشفتين باستخدام أداة التطبيق، ووزعيه بعناية على المساحة المرغوبة. يمكن رسم حدود الشفاه أولاً إذا كان ذلك جزءاً من روتينك، ثم الانتظار حتى يستقر اللون قبل استكمال خطوات المكياج الأخرى.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>يقدَّم روج ميبلين سوبر ستاي 45 Capricious كأحد منتجات Maybelline New York في فئة أحمر شفاه. يُستخدم المنتج بتمريره على الشفاه مع إمكانية إعادة التطبيق خلال اليوم حسب الحاجة. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه.</t>
+          <t>أحمر شفاه سوبر ستاي 45 كابريشس Super Stay Lipstick 45 Capricious من Maybelline New York، أحمر شفاه بدرجة 45 Capricious. يأتي أحمر شفاه سوبر ستاي من Maybelline New York بدرجة تحمل الرقم 45 والاسم Capricious. يندرج ضمن مستحضرات تلوين الشفاه، ويساعدك تحديد الرقم والاسم على اختيار الدرجة التي ترغبين في تنسيقها مع مكياجك، سواء جعلت الشفاه محط الاهتمام أو وازنتها مع بقية ألوان الوجه.لا يذكر الاسم حجماً للعبوة، لكنه يوضح نوع المنتج واسم Super Stay ورقم الدرجة واسمها. ويمكن وضع أحمر الشفاه ضمن إطلالة بسيطة أو أكثر تنسيقاً بحسب مناسبتك وتفضيلاتك الشخصية. تشمل خصائصه أن أحمر شفاه مخصص لمكياج الشفاه، ويحمل اسم Super Stay، والدرجة المسماة هي 45 Capricious. مرري أحمر الشفاه على الشفتين بالتساوي، وابدئي من منتصف الشفاه باتجاه الأطراف. يمكنك تحديد الحدود أولاً أو تطبيق اللون مباشرة وفق طريقتك المعتادة، ثم تنسيق بقية مستحضرات المكياج بما يتلاءم مع اختيارك.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ماسكارا L'Oréal Paris المعروف باسم مسكرة رموش لوريال بانورامار الذهبية، وهو منتج موجه لهذه الفئة من العناية. تُستخدم الماسكارا بتمرير الفرشاة على الرموش مع الحرص على عدم ملامسة العينين، ويمكن إدراجها ضمن خطوات مكياج العيون اليومي. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه.</t>
+          <t>ماسكارا لوريال بانوراما الذهبية — L'Oréal Panorama Golden Mascara، من لوريال، ماسكارا للرموش. ماسكارا بانوراما من لوريال مستحضر مكياج مخصص للرموش، يتيح إضافة لمسة واضحة إلى إطلالة العين ضمن خطوات المكياج اليومية أو المناسبة. يحمل الاسم وصف الذهبية كما ورد في اسم المنتج، من دون تحديد درجة لونية مستقلة أو حجم في البيانات المتاحة.يمكن إدراجها في روتين تجهيز العينين لإبراز الرموش وإكمال مظهر المكياج، مع اختيار مقدار التطبيق بما يلائم الإطلالة المرغوبة. ويظل شكل النتيجة مرتبطاً بطريقة وضع الماسكارا وكمية المنتج المستخدمة. يتميز المنتج بأن مستحضر مخصص لتطبيقه على الرموش، وتنتمي إلى مجموعة بانوراما من علامة لوريال، وتساعد على إبراز الرموش ضمن إطلالة العين. تُستخدم على الرموش بعناية، مع تمرير أداة التطبيق من قاعدة الرموش باتجاه أطرافها وبحركات لطيفة. يمكن الاكتفاء بطبقة خفيفة أو إضافة طبقة أخرى بحسب المظهر المطلوب، مع ترك كل طبقة تستقر قبل متابعة التطبيق. يُراعى عدم إدخال المنتج إلى العين أو استخدامه على غير موضعه المخصص.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>من تشكيلة Maybelline New York، يأتي Maybelline روج سائل سوبر ستاي انرايفلد من ميبيلين - 30 ضمن تصنيف أحمر شفاه. يُستخدم المنتج بتمريره على الشفاه مع إمكانية إعادة التطبيق خلال اليوم حسب الحاجة. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف.</t>
+          <t>أحمر شفاه سائل سوبر ستاي إنرايفلد 30 — Maybelline Super Stay Unrivaled Liquid Lipstick 30، من ميبلين، أحمر شفاه سائل، الدرجة 30 إنرايفلد. أحمر شفاه سائل من مجموعة سوبر ستاي لدى ميبلين، معرّف بالدرجة 30 إنرايفلد كما وردت في الاسم. صُمم ليكون جزءاً من مكياج الشفاه، ويمكن تنسيقه مع إطلالات مختلفة بحسب بقية الألوان المستخدمة وطريقة وضعه.تساعد صيغة أحمر الشفاه السائل على تطبيق اللون مباشرة على الشفاه، فيما تتيح الدرجة المحددة اختيارها ضمن مجموعة المكياج. لا تذكر البيانات المقدمة حجماً أو مواصفات إضافية، لذا يقتصر الوصف على الاسم والفئة والدرجة الواردة. من أبرز خصائصه أن أحمر شفاه سائل مخصص لمكياج الشفاه، ويحمل اسم سوبر ستاي من ميبلين، والدرجة المسجلة في الاسم هي 30 إنرايفلد. يوضع على شفاه نظيفة وجافة، مع تمرير أداة التطبيق برفق لتوزيع اللون على الشفتين. ابدئي بكمية مناسبة ثم أضيفي المزيد عند الحاجة إلى تغطية أوسع، مع مراعاة رسم حدود الشفاه بالطريقة التي تفضلينها. اتركيه ليستقر قبل ملامسة الشفاه أو إضافة مستحضر آخر.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>يندرج أحمر شفاه سائل سوبر ستاي من ميبلين -ويكد 50 - الصادر عن Maybelline New York ضمن منتجات أحمر شفاه. يُطبَّق أحمر الشفاه مباشرة على الشفاه، ويمكن تحديد الشفاه بقلم محدد قبل التطبيق للحصول على مظهر أوضح. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف.</t>
+          <t>أحمر شفاه سائل سوبر ستاي ويكد 50 — Maybelline Super Stay Liquid Lipstick Wicked 50، من ميبلين، أحمر شفاه سائل، الدرجة 50 ويكد. يأتي أحمر الشفاه السائل سوبر ستاي من ميبلين بالدرجة المسماة ويكد 50، ليكون خياراً ضمن مستحضرات تلوين الشفاه. يجمع الاسم بين مجموعة المنتج ورقم الدرجة واسمها، مما يساعد على التعرف إلى اللون المقصود عند اختيار المكياج أو تنسيق مجموعة منتجات الشفاه.تُستخدم الصيغة السائلة مباشرة على الشفتين، ويمكن توزيعها بعناية للحصول على المظهر الذي تفضلينه. لم يرد في البيانات حجم العبوة أو وصف تفصيلي لخصائص اللون، لذا لا يضيف هذا التعريف مواصفات غير مذكورة في الاسم. يذكر عن هذا المنتج أنه مخصص لتلوين الشفاه ضمن روتين المكياج، وصيغة المنتج سائلة وفقاً لاسمه، وينتمي إلى مجموعة سوبر ستاي من ميبلين. مرري أداة التطبيق على الشفاه النظيفة والجافة، ووزعي المنتج بهدوء من منتصف الشفة إلى أطرافها. يمكن وضع طبقة واحدة أو بناء اللون بكمية إضافية بحسب النتيجة المرغوبة، مع العناية بتوزيع اللون عند حدود الشفاه. أغلقي العبوة بعد الانتهاء واحرصي على عدم ملامسة الأداة لأسطح غير نظيفة.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Maybelline New York تقدم من خلال Maybelline ماسكارا مايبيلين لاش سينسيشنال سكاي هاي، منتجاً في فئة ماسكارا. يُطبَّق المنتج على الرموش بحركات خفيفة من الجذور إلى الأطراف، ويُنظَّف بالمزيل المخصص بعد الاستخدام. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص.</t>
+          <t>ماسكارا لاش سينسيشنال سكاي هاي — Maybelline Lash Sensational Sky High Mascara، من ميبلين، ماسكارا للرموش. ماسكارا لاش سينسيشنال سكاي هاي من ميبلين مستحضر مخصص لمكياج الرموش. يحمل اسم المجموعة سكاي هاي، ويُدرج ضمن خطوات تجهيز العين لإضافة الماسكارا إلى الإطلالة. لا تذكر البيانات المقدمة درجة لونية أو حجماً للعبوة، لذلك يظل التعريف محصوراً بالاسم والعلامة والفئة.يُستخدم هذا النوع من المستحضرات على الرموش، ويمكن التحكم في مظهرها عبر طريقة تمرير أداة التطبيق ومقدار المنتج الموضوع. يتيح ذلك إدخال خطوة الرموش إلى مكياج بسيط أو تنسيقها مع بقية مستحضرات العين، مع مراعاة التطبيق الهادئ والدقيق. تشمل خصائصه أن ماسكارا مخصصة لتطبيقها على الرموش، وتحمل اسم لاش سينسيشنال سكاي هاي، ومن مستحضرات ميبلين لمكياج العين. ابدئي برموش نظيفة، ثم مرري أداة الماسكارا بلطف من قرب قاعدة الرموش إلى أطرافها. تجنبي إدخال الأداة إلى العين، واستخدمي كمية مناسبة مع توزيعها بالتساوي. إذا رغبتِ في مظهر أوضح، كرري التمرير بحذر بعد استقرار الطبقة الأولى، ثم أغلقي العبوة بإحكام.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Maybelline برايمر رموش لاش سينسيشنال سكاي هاي من مايبيلي من Maybelline New York، منتج يصنَّف ضمن فئة ماسكارا. تُستخدم الماسكارا بتمرير الفرشاة على الرموش مع الحرص على عدم ملامسة العينين، ويمكن إدراجها ضمن خطوات مكياج العيون اليومي. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص.</t>
+          <t>برايمر رموش لاش سينسيشنال سكاي هاي — Maybelline Lash Sensational Sky High Lash Primer، من ميبلين، برايمر للرموش. برايمر رموش من ميبلين يحمل اسم لاش سينسيشنال سكاي هاي، وهو مستحضر يسبق الماسكارا في ترتيب مكياج الرموش. يندرج ضمن منتجات العين المخصصة للرموش، ويمكن إدراجه كخطوة مستقلة قبل وضع الماسكارا بحسب روتين المكياج الذي تفضلينه.يشير اسم المنتج إلى فئته بوصفه قاعدة للرموش، ولا تتضمن البيانات المتاحة تفاصيل عن الحجم أو درجة لونية. لذلك يركز الوصف على موضعه في خطوات المكياج وطريقة استخدامه العامة، دون إضافة نتائج أو خصائص غير مذكورة في اسم المنتج. يتميز المنتج بأن برايمر مخصص للرموش وفقاً لاسم المنتج، ويحمل اسم لاش سينسيشنال سكاي هاي، ومن منتجات ميبلين المخصصة لمكياج العين. يوضع على الرموش النظيفة قبل الماسكارا، مع تمرير أداة التطبيق برفق على الرموش وتوزيع المنتج بعناية. احرصي على عدم إدخال الأداة أو المستحضر إلى العين، واتركي الخطوة تستقر قبل الانتقال إلى الماسكارا. اتبعي ترتيب الاستخدام الذي تفضلينه، وأغلقي العبوة بعد الانتهاء.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>يقدَّم Maybelline روج سائل سوبر ستاي من ميبيلين - 110 كأحد منتجات Maybelline New York في فئة أحمر شفاه. يُستخدم المنتج بتمريره على الشفاه مع إمكانية إعادة التطبيق خلال اليوم حسب الحاجة. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه.</t>
+          <t>أحمر شفاه سائل سوبر ستاي 110 — Maybelline Super Stay Liquid Lipstick 110، من ميبلين، أحمر شفاه سائل، الدرجة 110. أحمر شفاه سائل من ميبلين يحمل اسم سوبر ستاي والرقم 110 بوصفه الدرجة الواردة في اسم المنتج. صُمم للاستخدام على الشفاه ضمن المكياج، وتتيح الصيغة السائلة وضع اللون بأداة التطبيق المرفقة بالعبوة، بحسب الطريقة المعتادة التي تفضلينها.يمكن تنسيق الدرجة مع بقية ألوان الإطلالة، أو اعتمادها كلون الشفاه الأساسي في المكياج. لا تتضمن البيانات المتاحة اسماً إضافياً للدرجة أو حجماً للعبوة، لذلك لا يضاف وصف لوني أو مواصفات غير مذكورة. من أبرز خصائصه أن مستحضر مكياج مخصص للشفاه، ويأتي بصيغة أحمر شفاه سائل، ويحمل اسم سوبر ستاي من ميبلين. ابدئي بتجهيز الشفاه لتكون نظيفة وجافة، ثم استخدمي أداة التطبيق لتوزيع اللون على الشفة العليا والسفلى. مرريها بهدوء مع ضبط حدود الشفاه، وأضيفي كمية أخرى إذا رغبتِ في تغطية أوسع. أزيلي أي فائض حول الشفاه قبل إغلاق العبوة، واحرصي على تنظيف الأداة وعدم مشاركتها.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ماسكارا Maybelline New York المعروف باسم ميبلين لاش سينسيشنال سكاي هاي ماسكرا مقاومة م، وهو منتج موجه لهذه الفئة من العناية. تُستخدم الماسكارا بتمرير الفرشاة على الرموش مع الحرص على عدم ملامسة العينين، ويمكن إدراجها ضمن خطوات مكياج العيون اليومي. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه.</t>
+          <t>ماسكارا لاش سينسيشنال سكاي هاي — Maybelline Lash Sensational Sky High Mascara، من ميبلين، ماسكارا للرموش. ماسكارا ميبلين لاش سينسيشنال سكاي هاي مستحضر مخصص للرموش، ويرد في بيانات الاسم وصف إضافي غير مكتمل بعد عبارة «مقاومة م». لعدم اكتمال هذه العبارة، لا يمكن تحديد الخاصية المقصودة؛ لذلك يقتصر التعريف هنا على اسم الماسكارا وفئتها من دون افتراض أنها مقاومة للماء أو نسب أي ميزة غير مؤكدة إليها.يمكن استخدام الماسكارا ضمن خطوات مكياج العين بوضعها على الرموش، مع اختيار كمية المستحضر وطريقة التمرير وفق المظهر الذي تفضلينه. لا تذكر البيانات المتاحة درجة لونية أو حجماً للعبوة، كما لا توضح الصفة التي انقطعت في اسم المنتج. يذكر عن هذا المنتج أنه ماسكارا مخصصة للرموش بحسب الاسم الوارد، وتحمل اسم لاش سينسيشنال سكاي هاي من ميبلين، وتندرج ضمن مستحضرات مكياج العين. مرري أداة الماسكارا على الرموش النظيفة من قرب القاعدة باتجاه الأطراف بحركة لطيفة، ووزعي المنتج باعتدال مع الحرص على عدم إدخاله إلى العين. يمكن تكرار التطبيق حسب النتيجة التي ترغبين بها، مع ترك الطبقة تستقر قبل إضافة المزيد.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>من تشكيلة Maybelline New York، يأتي ميبلين نيويورك كونسيلر فيت مي 40 كراميل ضمن تصنيف كونسيلر. يُطبَّق المنتج بلطف على البشرة بعد كريم الأساس أو قبله حسب الروتين المفضل للمستخدمة. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف.</t>
+          <t>كونسيلر فيت مي 40 كراميل — Maybelline Fit Me Concealer 40 Caramel، من ميبلين، خافي عيوب للوجه، الدرجة 40 كراميل. كونسيلر فيت مي من ميبلين مستحضر للوجه يحمل الدرجة 40 كراميل، كما وردت في الاسم. يُستخدم خافي العيوب ضمن خطوات المكياج لتطبيق اللون على المواضع التي ترغبين في تغطيتها أو موازنتها بصرياً، مع دمجه مع بقية مستحضرات الوجه بحسب طريقة المكياج المتبعة.تساعد معرفة رقم الدرجة واسمها على تحديد اللون المقصود عند اختيار المنتج، بينما لا تذكر المعلومات المقدمة حجم العبوة أو تفاصيل إضافية عن قوامه. يمكن وضعه بكمية مدروسة وتوزيعه بالطريقة المناسبة لك، مع مراعاة توافق اللون مع بقية مستحضرات المكياج. تشمل خصائصه أن خافي عيوب للوجه من ميبلين، وينتمي إلى مجموعة فيت مي، والدرجة المذكورة هي 40 كراميل. ضعي كمية مناسبة على المواضع المراد تغطيتها، ثم ادمجيها بلطف بأطراف الأصابع أو بأداة المكياج التي تفضلينها، مع تجنب الشد القوي على البشرة. ابدئي بكمية قليلة وأضيفي المزيد عند الحاجة، ثم نسقيه مع بقية مستحضرات الوجه. يفضل التأكد من ملاءمة الدرجة للون البشرة قبل اعتمادها في الإطلالة.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>يندرج Maybelline خافي عيوب مايبيلين فيت مي رقم 5 الصادر عن Maybelline New York ضمن منتجات كونسيلر. يُستخدم الكونسيلر بنقاط صغيرة على مناطق التفاوت في لون البشرة ثم يُدمج بإسفنجة أو فرشاة مخصصة. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال.</t>
+          <t>كونسيلر فيت مي رقم 5 — Maybelline Fit Me Concealer 5، من ميبلين، خافي عيوب للوجه، الدرجة 5. خافي عيوب فيت مي من ميبلين يحمل رقم الدرجة 5، وهو مستحضر مكياج للوجه يمكن إدخاله ضمن خطوات تجهيز البشرة. يتيح نوع المنتج وضعه على مواضع محددة ثم دمجه مع مستحضرات الوجه الأخرى، وفق التغطية والمظهر اللذين تفضلينهما.يرد الرقم 5 في اسم المنتج من دون اسم لوني وصفي أو حجم للعبوة. لذلك يقتصر التعريف على نوعه ومجموعته ودرجته المسجلة، وينبغي اختيار اللون بالاستناد إلى الرقم والملاءمة الشخصية، دون افتراض وصف لوني غير مدون. يتميز المنتج بأن خافي عيوب مخصص لمكياج الوجه، ومن مجموعة فيت مي التابعة لميبلين، ويحمل رقم الدرجة 5. ضعي نقاطاً صغيرة على المواضع التي ترغبين في تغطيتها، ثم ادمجيها بخفة باستخدام أداة مناسبة أو أطراف الأصابع. ابدئي بكمية قليلة، وزيديها تدريجياً إن رغبتِ في ذلك، مع توزيع المستحضر حتى ينسجم مع المكياج المحيط. تحققي من ملاءمة الدرجة لبشرتك قبل الاستخدام على كامل المواضع المقصودة.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Maybelline New York تقدم من خلال ميبلين سوبر ستاي فينيلينك - 150 STRIKING منتجاً في فئة أحمر شفاه. يُستخدم المنتج بتمريره على الشفاه مع إمكانية إعادة التطبيق خلال اليوم حسب الحاجة. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص.</t>
+          <t>أحمر شفاه سوبر ستاي فينيل إنك 150 سترايكينغ — Maybelline Super Stay Vinyl Ink 150 Striking، من ميبلين، أحمر شفاه سائل، الدرجة 150 سترايكينغ. أحمر شفاه فينيل إنك من مجموعة سوبر ستاي لدى ميبلين، ويحمل الدرجة 150 سترايكينغ كما وردت في الاسم. يندرج ضمن مستحضرات تلوين الشفاه بصيغة سائلة، ويمكن وضعه ضمن خطوات المكياج لإضافة لون إلى الشفتين وتنسيقه مع بقية الإطلالة.تساعد تسمية المجموعة ورقم الدرجة واسمها على تحديد المنتج عند اختيار مستحضر الشفاه. لا تتضمن المعلومات المتاحة حجماً للعبوة أو تفاصيل إضافية عن اللون أو خصائصه؛ لذلك يقتصر الوصف على البيانات المذكورة وطريقة الاستخدام العامة لأحمر الشفاه السائل. من أبرز خصائصه أن أحمر شفاه سائل من مجموعة سوبر ستاي، ويحمل اسم فينيل إنك كما ورد في المنتج، ومن علامة ميبلين لمكياج الشفاه. استخدمي أداة التطبيق لتوزيع أحمر الشفاه على شفاه نظيفة وجافة، بدءاً من منتصف الشفتين ثم التحرك برفق نحو الأطراف. مرري الأداة بكمية معتدلة، واضبطي حدود الشفاه قبل إضافة أي كمية أخرى. اتركي اللون يستقر قبل متابعة المكياج، ثم أغلقي العبوة بإحكام واحفظي أداة التطبيق نظيفة.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ميبلين سوبر ستاي فينيلينك - 165 EDGY من Maybelline New York، منتج يصنَّف ضمن فئة أحمر شفاه. يُطبَّق أحمر الشفاه مباشرة على الشفاه، ويمكن تحديد الشفاه بقلم محدد قبل التطبيق للحصول على مظهر أوضح. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم.</t>
+          <t>أحمر شفاه سوبر ستاي فينيل إنك 165 إيدجي Super Stay Vinyl Ink 165 Edgy من Maybelline، أحمر شفاه بالدرجة 165 Edgy. يجمع هذا اللون من Super Stay Vinyl Ink بين لون الشفاه الواضح واللمسة الفينيلية اللامعة التي تعكسها تسمية المجموعة. وتمنح الدرجة 165 Edgy خياراً محدداً لمن ترغب في اختيار لونها وفق رقم الدرجة واسمها المدوّن على المنتج.يمكن تنسيق أحمر الشفاه مع إطلالات المكياج المختلفة، سواء كان التركيز على لون الشفاه وحده أو على مظهر متكامل. وتساعد تسمية الدرجة الواضحة على تمييز اللون عند الاختيار أو عند مقارنته بدرجات أخرى من المجموعة. يذكر عن هذا المنتج أنه من مجموعة Super Stay Vinyl Ink من Maybelline، ودرجة محددة برقم 165 واسم Edgy، ولمسة فينيلية ذات مظهر لامع. يوضع اللون على شفاه نظيفة وجافة، مع تمرير أداة التطبيق على الشفتين وتوزيع اللون بالطريقة المرغوبة. يمكن البدء بكمية قليلة ثم إضافة المزيد للوصول إلى المظهر الذي تفضلينه. اتركيه يستقر قبل ملامسة الشفاه أو وضع طبقة أخرى، واتّبعي إرشادات العبوة.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>يقدَّم أحمر شفاه مايبيلين سوبر ستاي فينيل إنك 170 كأحد منتجات Maybelline New York في فئة أحمر شفاه. يُستخدم المنتج بتمريره على الشفاه مع إمكانية إعادة التطبيق خلال اليوم حسب الحاجة. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه.</t>
+          <t>أحمر شفاه سوبر ستاي فينيل إنك 170 Super Stay Vinyl Ink 170 من Maybelline، أحمر شفاه يحمل الدرجة 170. يأتي أحمر الشفاه ضمن مجموعة Super Stay Vinyl Ink، ويجمع اسمه بين وصف المجموعة ورقم الدرجة 170. وتساعد اللمسة الفينيلية المرتبطة باسم Vinyl Ink على إضفاء مظهر لامع على الشفاه، فيما يتيح رقم الدرجة تحديد اللون المطلوب بوضوح.يمكن اعتماد اللون جزءاً من روتين المكياج اليومي أو إضافته إلى إطلالة أكثر تنسيقاً، مع اختيار بقية المستحضرات بما يلائم ذوقك. صُممت هذه الصفحة للتعريف بالمنتج وفق المعلومات الواردة في اسمه، من دون افتراض حجم أو تفاصيل إضافية غير مذكورة. تشمل خصائصه أن أحمر شفاه من مجموعة Super Stay Vinyl Ink، ويحمل رقم الدرجة 170، وتصف تسمية Vinyl Ink مظهر المجموعة الفينِيلي. مرري أحمر الشفاه على الشفتين بعد التأكد من نظافتهما وجفافهما. وزعي اللون بالتساوي، وابدئي بطبقة خفيفة ثم أضيفي طبقة أخرى عند الرغبة في مظهر أوضح. اتركيه يستقر، وراجعي تعليمات الاستخدام على العبوة قبل الاستعمال.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ماسكارا Maybelline New York المعروف باسم Maybelline ميبيلين لاش سينسيشنال سكاي هاي ماسكرا اسود، وهو منتج موجه لهذه الفئة من العناية. تُستخدم الماسكارا بتمرير الفرشاة على الرموش مع الحرص على عدم ملامسة العينين، ويمكن إدراجها ضمن خطوات مكياج العيون اليومي. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه.</t>
+          <t>ماسكارا لاش سينسيشنال سكاي هاي السوداء Lash Sensational Sky High Black Mascara من Maybelline، ماسكارا للرموش بدرجة الأسود. تجمع هذه الماسكارا بين اسمي Lash Sensational وSky High ضمن منتج مخصص للرموش، وتأتي باللون الأسود كما يوضح الاسم. تضيف الماسكارا لوناً للرموش وتساعد على إبرازها ضمن مكياج العين، مع إمكانية استخدامها وحدها أو إلى جانب ظلال العيون وآيلاينر.تمنح تسمية Sky High هوية المجموعة، بينما يحدد وصف Black لون المنتج بوضوح. اختاري طريقة وضع تناسب شكل الإطلالة التي ترغبين بها، مع الحرص على تطبيق المستحضر بعناية على الرموش واتباع المعلومات المدونة على العبوة. يتميز المنتج بأن ماسكارا للعين من مجموعة Lash Sensational Sky High، وتأتي باللون الأسود وفق الاسم، ومخصصة لتلوين الرموش وإبرازها. استخدمي الفرشاة لتمرير الماسكارا على الرموش من القاعدة باتجاه الأطراف بحركة متأنية، مع الحرص على عدم إدخال المنتج إلى العين. يمكن إضافة طبقة أخرى بعد استقرار الأولى بحسب المظهر المرغوب. أغلقي العبوة بعد الاستخدام، واتبعي تعليمات المنتج المدونة عليها.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>من تشكيلة L'Oréal Paris، يأتي كونسيلر لوريال انفيلابل 322 ضمن تصنيف كونسيلر. يُطبَّق المنتج بلطف على البشرة بعد كريم الأساس أو قبله حسب الروتين المفضل للمستخدمة. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف.</t>
+          <t>كونسيلر إنفاليبل 322 Infallible Concealer 322 من L'Oréal Paris، كونسيلر للوجه يحمل الدرجة 322. ينتمي هذا الكونسيلر إلى مجموعة Infallible من L'Oréal Paris، وقد حُددت درجته بالرقم 322 في اسم المنتج. يستخدم الكونسيلر ضمن مكياج الوجه لتغطية مظهر مواضع محددة أو لإضافة لمسة تصحيحية إلى المظهر، مع اختيار الدرجة بما يتناسب مع لون البشرة والنتيجة التي تفضلينها.يساعد رقم الدرجة على تمييز هذا المنتج عن بقية الخيارات التي تحمل الاسم نفسه. وللحصول على تنسيق متجانس، يمكن وضع كمية مناسبة على المنطقة المطلوبة ودمجها مع مستحضرات الوجه الأخرى وفق روتين المكياج المعتاد. من أبرز خصائصه أن كونسيلر للوجه من مجموعة Infallible، ويحمل رقم الدرجة 322، ومخصص للاستخدام ضمن مكياج الوجه. ضعي كمية صغيرة على المواضع التي ترغبين في تغطيتها، ثم ادمجيها بلطف باستخدام الإصبع أو أداة المكياج المناسبة. يمكن وضعه قبل مستحضر الأساس أو بعده بحسب طريقتك المعتادة. ابدئي بكمية قليلة، وراجعي تعليمات الاستخدام الموجودة على العبوة.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>يندرج كونسلر لوريال انفيلابل 324 الصادر عن L'Oréal Paris ضمن منتجات كونسيلر. يُستخدم الكونسيلر بنقاط صغيرة على مناطق التفاوت في لون البشرة ثم يُدمج بإسفنجة أو فرشاة مخصصة. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال.</t>
+          <t>كونسيلر إنفاليبل 324 Infallible Concealer 324 من L'Oréal Paris، كونسيلر للوجه بدرجة 324. يأتي كونسيلر Infallible من L'Oréal Paris بالدرجة التي يحمل رقمها 324. وهو مستحضر للوجه يمكن إدخاله في روتين المكياج عند الرغبة في تغطية مظهر مناطق بعينها أو توحيد مظهر المكياج في تلك المواضع. يتيح الرقم التمييز بين درجات المجموعة عند الاختيار.يمكن توزيع المنتج بقدر يناسب المنطقة المستهدفة، ثم دمجه برفق حتى ينسجم مع بقية مستحضرات الوجه. يختلف اختيار موضع التطبيق وطريقته حسب تفضيلك، لذلك ابدئي بتطبيق محدود ثم زيدي الكمية عند الحاجة، مع الالتزام بإرشادات العبوة. يذكر عن هذا المنتج أنه مستحضر كونسيلر مخصص للوجه، ومن مجموعة Infallible التابعة لـ L'Oréal Paris، ورقم الدرجة الموضح هو 324. وزعي كمية صغيرة على المنطقة المراد تغطيتها، ثم ربتي عليها بأداة مناسبة حتى يندمج المستحضر. يمكن استخدامه منفرداً على مواضع مختارة أو ضمن خطوات مكياج الوجه المعتادة. تحققي من تعليمات العبوة قبل الاستخدام، ولا تضعيه على بشرة متهيجة.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>L'Oréal Paris تقدم من خلال كونسلر لوريال انفيلابل 330 منتجاً في فئة كونسيلر. يُطبَّق المنتج بلطف على البشرة بعد كريم الأساس أو قبله حسب الروتين المفضل للمستخدمة. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص.</t>
+          <t>كونسيلر إنفاليبل 330 Infallible Concealer 330 من L'Oréal Paris، مستحضر للوجه بدرجة 330. يقدم كونسيلر Infallible خياراً من مستحضرات مكياج الوجه، وتحدد الدرجة 330 هويته اللونية ضمن الاسم. يمكن استخدامه في المناطق التي ترغبين في تغطيتها أو إبراز تناسق المكياج فيها، مع دمجه بعناية حتى يتلاءم مع المستحضرات المحيطة به.يفيد رقم الدرجة في التعرف على المنتج عند إعادة اختياره أو مقارنته بخيارات أخرى من المجموعة. ولأن الاسم لا يحدد حجماً أو وصفاً تفصيلياً للتركيبة، فتعتمد معلومات العبوة في معرفة أي تفاصيل إضافية قبل الاستعمال. تشمل خصائصه أن كونسيلر للوجه من مجموعة Infallible، ورقم الدرجة المحدد في الاسم هو 330، ويستخدم ضمن مكياج الوجه للتغطية والتصحيح. ضعي مقداراً مناسباً على المنطقة المراد تغطيتها، وادمجيه بالتربيت الخفيف باستخدام أداة نظيفة. يمكن إضافته إلى روتين المكياج قبل أو بعد مستحضر الأساس وفق تفضيلك. لا تكثري من الكمية في البداية، واتبعي تعليمات الاستعمال المطبوعة على العبوة.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Maybelline ماسكارا سكاي هاي سبيس دايموند، 7.2 مل من Maybelline New York، منتج يصنَّف ضمن فئة ماسكارا. يأتي بحجم 7.2 مل، وهو الحجم المذكور على العبوة دون غيره. تُستخدم الماسكارا بتمرير الفرشاة على الرموش مع الحرص على عدم ملامسة العينين، ويمكن إدراجها ضمن خطوات مكياج العيون اليومي. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص.</t>
+          <t>ماسكارا سكاي هاي سبيس دايموند Sky High Space Diamond Mascara من Maybelline، ماسكارا للرموش بحجم 7.2 مل. ماسكارا للرموش تحمل اسم Sky High Space Diamond من Maybelline، ويبلغ حجمها 7.2 مل وفق البيانات الواردة في الاسم. تضيف الماسكارا لوناً للرموش وتدخل ضمن مستحضرات مكياج العين، ويمكن اعتمادها منفردة أو تنسيقها مع ظلال العيون ومنتجات تحديد العين.يمنح اسم Space Diamond المنتج تعريفاً مميزاً داخل مجموعة Sky High، من دون أن يحدد لوناً أو درجة بعينها في الاسم المقدم. لذلك يمكن الرجوع إلى العبوة لمراجعة لون المستحضر وتفاصيله قبل الاستخدام، مع تطبيقه بعناية على الرموش. يتميز المنتج بأن ماسكارا مخصصة للرموش، وتحمل اسم Sky High Space Diamond، ومن علامة Maybelline. مرري الفرشاة على الرموش من الجذور إلى الأطراف بحركة هادئة، مع توزيع المستحضر دون إدخاله إلى العين. إذا رغبتِ في طبقة إضافية، انتظري قليلاً قبل تكرار التطبيق. أغلقي العبوة بإحكام بعد الاستخدام، واتّبعي التعليمات المدونة على المنتج.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>يقدَّم مايبيلين نيويورك ماسكارا سكاي هاي ارتفاع أخضر كأحد منتجات Maybelline New York في فئة ماسكارا. يُطبَّق المنتج على الرموش بحركات خفيفة من الجذور إلى الأطراف، ويُنظَّف بالمزيل المخصص بعد الاستخدام. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم.</t>
+          <t>ماسكارا سكاي هاي الخضراء Sky High Green Mascara من Maybelline New York، ماسكارا للرموش باللون الأخضر. تأتي ماسكارا Sky High Green من Maybelline New York بلون أخضر موضح في اسمها، لتكون خياراً لونيّاً ضمن مكياج الرموش. يمكن استخدام اللون لإضافة لمسة مختلفة إلى مكياج العين، أو تنسيقه مع بقية الألوان وفق الأسلوب الذي تفضلينه.تحدد التسمية نوع المستحضر ومجموعته ولونه، ولا تذكر حجماً للعبوة. عند وضع الماسكارا، مرريها على الرموش بعناية، واختاري عدد الطبقات بما يتناسب مع النتيجة المرغوبة. يمكن مراجعة العبوة لمعرفة التفاصيل الإضافية وإرشادات الاستعمال الخاصة بهذا المنتج. من أبرز خصائصه أن ماسكارا للرموش من مجموعة Sky High، وتأتي باللون الأخضر بحسب الاسم، ومن Maybelline New York. استخدمي الفرشاة لتمرير اللون على الرموش من الجذور إلى الأطراف مع الانتباه إلى عدم ملامسة العين. ابدئي بطبقة خفيفة، ويمكن إضافة طبقة أخرى بعد جفاف الأولى إذا رغبتِ في مظهر أوضح. أغلقي العبوة بعد الاستخدام، والتزمي بإرشادات المنتج الموجودة على العبوة.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>كريم للشعر Wella المعروف باسم ويلا ويلكسون اوكسجين6% -60مل، وهو منتج موجه لهذه الفئة من العناية. تبلغ سعة العبوة 60 مل كما هو موضح على المنتج. يُستخدم بتوزيع كمية مناسبة منه على الشعر من الجذور إلى الأطراف حسب الحاجة. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه.</t>
+          <t>أكسجين صبغة الشعر ويلكسون 6% Welloxon 6% من Wella، مستحضر أكسجين للصبغة بتركيز 6% وحجم 60 مل. مستحضر Welloxon من Wella مخصص للاستخدام مع صبغات الشعر وفق التعليمات المحددة للمنتج، ويأتي بتركيز 6% وحجم 60 مل كما ورد في الاسم. يندرج ضمن مستحضرات تجهيز لون الشعر، ويجب استخدامه بما يتوافق مع تعليمات العبوة والمنتج الملون الذي سيُستعمل معه.تساعد بيانات التركيز والحجم على تمييز هذا الخيار عند تجهيز مستلزمات صبغ الشعر. تختلف طريقة الاستخدام ونسب المزج باختلاف المنتج المصاحب وتعليمات الشركة، لذلك لا يُعتمد على تقديرات عامة؛ راجعي إرشادات العبوتين أو استعيني بمختص قبل الاستخدام. يذكر عن هذا المنتج أنه أكسجين صبغة شعر من Wella Welloxon، وتركيز 6% كما هو مذكور في الاسم، وحجم العبوة 60 مل. يستخدم مع صبغة الشعر المتوافقة وفق النسب وطريقة التحضير المحددتين في تعليمات العبوة. لا تخلطيه أو تضعيه منفرداً على الشعر من دون الرجوع إلى إرشادات الشركة المصنّعة. ارتدي وسائل الوقاية المناسبة أثناء التحضير، ونفذي اختبار الحساسية إذا أوصت به تعليمات الصبغة.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>من تشكيلة Vaseline، يأتي مرطب ومورد للشفاه من فازلين - 20جم ضمن تصنيف مرطب شفاه. يُطرح المنتج بحجم 20 جم فقط. يُستخدم بوضعه على الشفاه الجافة لترطيبها، مع إغلاق العبوة جيداً بعد كل استخدام. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف.</t>
+          <t>مرطب ومورد للشفاه من فازلين Vaseline Lip Moisturizer، بحجم 20 جم، للعناية بمظهر الشفاه وترطيبها. مرطب شفاه من Vaseline بحجم 20 جم، يحمل وصف مورد للشفاه كما ورد في الاسم. يجمع المنتج بين ترطيب الشفاه وإضافة مظهر مورّد لها، ليكون جزءاً من روتين العناية اليومية أو لمسة بسيطة تسبق المكياج. ويتيح حجمه المحدد التعرف على سعة العبوة عند الاختيار.يمكن وضعه على الشفاه بمفرده أو استخدامه ضمن خطوات تجهيز الشفاه للمكياج. لا يحدد الاسم درجة لون أو لوناً بعينه، لذلك يرجى مراجعة العبوة لمعرفة تفاصيل المنتج الدقيقة وطريقة استعماله. استخدميه بالقدر الذي يناسبك، وأغلقي العبوة بعد كل استخدام. تشمل خصائصه أن مرطب مخصص للشفاه من Vaseline، ويحمل وصف مورد للشفاه في الاسم، وحجم العبوة 20 جم. ضعي كمية مناسبة على الشفاه النظيفة، ووزعيها بلطف على كامل سطحها. يمكن تجديد الاستخدام عند الحاجة أو وضعه قبل المكياج بحسب روتينك. راجعي ملصق العبوة لمعرفة طريقة الاستخدام التفصيلية، وتجنبي استعمال المنتج إذا تغيرت رائحته أو قوامه.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>يندرج مطهر ومعقم للجراثيم ديتول 250مل الصادر عن Dettol ضمن منتجات مطهر ومعقم. يأتي بحجم 250 مل، وهو الحجم المذكور على العبوة دون غيره. يُستخدم المطهر بتخفيفه بالماء حسب الحاجة أو يُطبَّق مباشرة على السطح أو المنطقة المطلوبة وفق التعليمات المدوَّنة على العبوة. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف.</t>
+          <t>مطهر ومعقم للجراثيم ديتول 250مل (Dettol Germ Disinfectant 250 ml)، من ديتول، نوعه مطهر ومعقم وحجمه 250 مل. مطهر ومعقم للجراثيم من ديتول، ويأتي الاسم التجاري محدداً لطبيعة المنتج كما وردت في بياناته. يتيح حجم 250 مل التعرف على سعة العبوة، بينما تظل طريقة الاستخدام والغرض المحدد مرتبطين بالتعليمات المدونة عليها.صيغ هذا الوصف للتعريف بالمنتج من دون افتراض موضع استعماله أو إضافة معلومات عن تركيبته أو خصائص لم ترد في اسمه. يُرجى مراجعة العبوة قبل الاستخدام لمعرفة الإرشادات الملائمة للمنتج. يتميز المنتج بأن منتج موصوف بأنه مطهر ومعقم للجراثيم، ويحمل علامة ديتول التجارية، وحجم العبوة المذكور هو 250 مل. تُقرأ تعليمات العبوة كاملة قبل الاستعمال، ويُستخدم المنتج وفق الغرض والطريقة والكمية المحددة من الشركة على العبوة. لا تفترض ملاءمته لموضع معين، ولا تخلطه بمنتجات أخرى.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Max Factor تقدم من خلال كريم أساس بيرفورمنس 102 باستيل من ماكس فاكتور منتجاً في فئة كريم أساس. يُستخدم بتوزيعه على البشرة النظيفة والمرطبة قبل استكمال باقي خطوات المكياج. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص.</t>
+          <t>كريم أساس بيرفورمنس 102 باستيل من ماكس فاكتور (Max Factor Performance Foundation 102 Pastel)، نوعه كريم أساس ودرجته 102 باستيل. كريم أساس من ماكس فاكتور يحمل اسم بيرفورمنس ودرجة 102 باستيل. يجمع الاسم بين نوع المنتج ورقم الدرجة وتسميتها، لتسهيل التعرف على هذا الخيار ضمن مستحضرات أساس الوجه. لا يذكر الاسم حجماً للعبوة أو وصفاً لنتيجة نهائية، لذا يقتصر التعريف هنا على التفاصيل المعلنة.يُدرج كريم الأساس ضمن خطوات مكياج الوجه، وتُختار الدرجة وفق التفضيل الشخصي ومقارنتها ببيانات العبوة. لا تُضاف إلى المنتج وعود بشأن التغطية أو الثبات أو طبيعة البشرة، إذ لم ترد هذه المعلومات في الاسم. من أبرز خصائصه أن كريم أساس من علامة ماكس فاكتور، ويحمل اسم بيرفورمنس كما ورد في المنتج، ودرجة المنتج محددة بالرقم 102. يوزع كريم الأساس على بشرة نظيفة بالطريقة المعتادة، مع البدء بكمية مناسبة ثم دمجها بلطف حتى يتوزع المستحضر. يُستحسن التحقق من اسم الدرجة على العبوة قبل الاستخدام، واتباع أي إرشادات موضحة عليها.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>كريم اساس سائل من ماكس فاكتر- 101 من Max Factor، منتج يصنَّف ضمن فئة كريم أساس. يُطبَّق كريم الأساس على الوجه بإسفنجة أو فرشاة مخصصة، ويمكن دمجه بحركات دائرية خفيفة. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم.</t>
+          <t>كريم أساس سائل من ماكس فاكتر بدرجة 101 (Max Factor Liquid Foundation 101)، نوعه كريم أساس سائل والدرجة المذكورة 101. كريم أساس سائل من ماكس فاكتر، يرد في اسمه رقم الدرجة 101 من دون تسمية إضافية للدرجة أو ذكر حجم العبوة. ويحدد وصفه نوع المستحضر وشكله السائل، ما يجعله واضح التصنيف ضمن مستحضرات مكياج الوجه.يمكن إدراجه ضمن روتين وضع كريم الأساس، مع اختيار الدرجة بالرجوع إلى الرقم المدون ومراجعة العبوة. لا تتضمن البيانات المتاحة تفاصيل عن التغطية أو اللمسة النهائية أو خصائص أخرى، لذلك يقتصر الوصف على الاسم والمعلومات المذكورة. يذكر عن هذا المنتج أنه كريم أساس بصيغة سائلة حسب اسمه، ويحمل علامة ماكس فاكتور التجارية، ورقم الدرجة المحدد هو 101. يوضع المستحضر على بشرة نظيفة، ثم يوزع بالتساوي بالطريقة المعتادة لدمج كريم الأساس. ابدئي بكمية مناسبة، وتحققي من رقم الدرجة على العبوة قبل التطبيق، مع الالتزام بالإرشادات الخاصة بالمنتج إن وجدت.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>يقدَّم ماكس فاكتور كريم أساس 100 فير كأحد منتجات Max Factor في فئة كريم أساس. يُستخدم بتوزيعه على البشرة النظيفة والمرطبة قبل استكمال باقي خطوات المكياج. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه.</t>
+          <t>كريم أساس ماكس فاكتور 100 فير (Max Factor Foundation 100 Fair)، نوعه كريم أساس ودرجته 100 فير. كريم أساس من ماكس فاكتور، يحمل رقم 100 وتسمية فير كما وردا في اسم المنتج. تمنح هذه البيانات تعريفاً محدداً بنوع المستحضر ودرجته، من دون أن يرد معها حجم للعبوة أو وصف تفصيلي للنتيجة التي يمنحها.يُستخدم كريم الأساس ضمن مكياج الوجه، ويمكن الاسترشاد باسم الدرجة ورقمها عند المقارنة بين المنتجات. تختلف التفضيلات في اختيار الدرجات، لذا يُرجى مراجعة العبوة والتأكد من تسمية 100 فير قبل التطبيق. لا يتضمن الاسم معلومات عن نوع البشرة أو مستوى التغطية. تشمل خصائصه أن كريم أساس يحمل علامة ماكس فاكتور، ورقم الدرجة المذكور هو 100، وتسمية الدرجة الواردة هي فير. يوضع كريم الأساس على بشرة نظيفة ويوزع بلطف باستخدام الأصابع أو أداة المكياج المناسبة. تحققي من رقم الدرجة واسمها على العبوة قبل الاستخدام، واتّبعي أي تعليمات خاصة مدونة عليها.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>مزيل عرق Rexona المعروف باسم ريكسونا-مزيل عرق رول أون-50 مل--يعمل للملابس، وهو منتج موجه لهذه الفئة من العناية. يأتي بحجم 50 مل، وهو الحجم المذكور على العبوة دون غيره. يُستخدم بتمريره على منطقة الإبط النظيفة والجافة، ويمكن إدراجه ضمن روتين العناية الشخصية اليومي. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه.</t>
+          <t>ريكسونا مزيل عرق رول أون 50 مل يعمل للملابس (Rexona Roll-On Deodorant 50 ml, Works for Clothing)، نوعه مزيل عرق رول وحجمه 50 مل. مزيل عرق رول أون من ريكسونا بحجم 50 مل. تتضمن تسمية المنتج عبارة «يعمل للملابس»، وهي جزء من الاسم المقدم، لذلك يُرجى الرجوع إلى بيانات العبوة للتحقق من الاستخدام المقصود وطريقة التطبيق قبل استعماله على الملابس أو غيرها.يحدد الاسم العلامة التجارية وشكل المنتج وحجمه، ولا يذكر تفاصيل عن الرائحة أو مدة الاستخدام أو خصائص أخرى. يتيح شكل الرول أون التعرف على هيئة المستحضر، فيما تبقى الإرشادات المدونة على العبوة المرجع عند الاستخدام. يتميز المنتج بأن مزيل عرق يحمل علامة ريكسونا، ويأتي بصيغة رول أون حسب الاسم، وحجم العبوة المذكور 50 مل. راجعي العبوة لتحديد موضع الاستخدام وطريقته، ولا تطبقي المنتج على الملابس إلا إذا أجازت التعليمات ذلك. إذا كان الاستخدام على البشرة موضحاً، يُستخدم وفق الإرشادات المدونة مع تجنب الإفراط في التطبيق.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>من تشكيلة Rexona، يأتي ريكسونا - مزيل عرق رول أون 50مل الالو فيرا ضمن تصنيف مزيل عرق. الحجم المدوَّن على العبوة هو 50 مل. يُطبَّق المنتج مباشرة بعد الاستحمام على المنطقة المستهدفة مع تركه حتى يجف قبل ارتداء الملابس. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف.</t>
+          <t>ريكسونا مزيل عرق رول أون 50 مل ألو فيرا (Rexona Aloe Vera Roll-On Deodorant 50 ml)، نوعه مزيل عرق رول وحجمه 50 مل. مزيل عرق رول أون من ريكسونا، بحجم 50 مل، ويحمل اسم ألو فيرا ضمن تسمية الإصدار. يوضح الاسم شكل المنتج وحجمه والعلامة التجارية، بينما لا تتضمن المعلومات المتاحة تفاصيل أخرى عن الرائحة أو التركيبة أو مدة الاستخدام.للتعرف على المنتج، يُرجع إلى الاسم المطبوع على العبوة وإلى تعليمات الاستخدام الخاصة به. وترد عبارة ألو فيرا ضمن اسم الإصدار، من دون إضافة ادعاء عن مكونات أو خصائص غير مذكورة في بياناته. من أبرز خصائصه أن مزيل عرق من علامة ريكسونا، ويأتي بصيغة رول أون، وحجم العبوة المذكور هو 50 مل. يُستخدم على موضع الاستخدام المحدد على العبوة مع اتباع الإرشادات الواردة عليها. عند تطبيقه على البشرة، يُمرر وفق الطريقة الموضحة، ويُترك ليجف قبل ارتداء الملابس إذا أشارت تعليمات المنتج إلى ذلك.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>يندرج دوف ديو عصا أوريجينال 50 مل الصادر عن Dove ضمن منتجات مزيل عرق. تبلغ سعة العبوة 50 مل كما هو موضح على المنتج. يُستخدم بتمريره على منطقة الإبط النظيفة والجافة، ويمكن إدراجه ضمن روتين العناية الشخصية اليومي. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف.</t>
+          <t>دوف ديو عصا أصلية 50 مل (Dove Original Deodorant Stick 50 ml)، من دوف، نوعه مزيل عرق عصا وحجمه 50 مل. مزيل عرق من دوف بصيغة العصا، ويظهر في الاسم وصف «أصلية» مع حجم 50 مل. تتيح هذه البيانات التعرف على هيئة المنتج والعلامة وسعة العبوة، من دون افتراض رائحة أو خصائص لم تُذكر في التسمية المقدمة.اختير وصف العصا لبيان شكل المنتج كما ورد، ويُرجع إلى تعليمات العبوة لمعرفة الاستخدام وطريقة التطبيق. كما يرد اسم ديو ضمن التسمية، ولا يذكر الاسم المتاح درجة أو حجمًا آخر. يذكر عن هذا المنتج أنه مزيل عرق من علامة دوف، ويأتي بصيغة العصا المذكورة في الاسم، وحجم العبوة المحدد هو 50 مل. يُستخدم المنتج حسب الإرشادات المدونة على العبوة. يُمرر على موضع الاستخدام المحدد وبالطريقة الموضحة، مع التأكد من إغلاق العبوة بعد الانتهاء وحفظها كما توصي تعليماتها.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>QV تقدم من خلال رول مضاد للتعرق من كيوفي - 80ج منتجاً في فئة مزيل عرق. يُطبَّق المنتج مباشرة بعد الاستحمام على المنطقة المستهدفة مع تركه حتى يجف قبل ارتداء الملابس. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص.</t>
+          <t>رول مضاد للتعرق من كيوفي 80 جم (QV Roll-On Antiperspirant 80 g)، نوعه مضاد تعرق رول وحجمه 80 جم. مضاد تعرق من كيوفي بصيغة الرول، وتبلغ الكمية المذكورة في اسم المنتج 80 جم. ويحدد الاسم فئة المنتج وعلامته التجارية وشكله، ما يتيح التعرف عليه ضمن مستحضرات العناية الشخصية من دون الخلط بينه وبين منتجات الجسم ذات الأنواع الأخرى.لا يذكر الاسم تفاصيل عن الرائحة أو المكونات أو مدة الاستخدام، لذا يقتصر الوصف على المعلومات الواردة. تُراجع العبوة لمعرفة تعليمات الاستخدام الخاصة بالمنتج، ويُعتمد على بياناتها عند تحديد طريقة التطبيق. تشمل خصائصه أن مضاد تعرق يحمل علامة كيوفي، ويأتي بصيغة رول حسب الاسم، والكمية المذكورة هي 80 جم. تُتبع تعليمات العبوة لتحديد موضع الاستخدام وطريقته. يُطبق المنتج وفق الإرشادات المدونة عليه، مع مراعاة التحذيرات وأي توجيهات تتعلق بتكرار الاستعمال أو حفظ العبوة.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>كيوفي رول للعرق 80 جم من QV، منتج يصنَّف ضمن فئة مزيل عرق. يأتي بحجم 80 جم، وهو الحجم المذكور على العبوة دون غيره. يُستخدم بتمريره على منطقة الإبط النظيفة والجافة، ويمكن إدراجه ضمن روتين العناية الشخصية اليومي. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم.</t>
+          <t>كيوفي رول للعرق 80 جم (QV Roll-On Deodorant 80 g)، من كيوفي، نوعه مزيل عرق رول وحجمه 80 جم. منتج رول للعرق من كيوفي، وتظهر كمية 80 جم في اسمه. يوضح الاسم المختصر العلامة التجارية وشكل المنتج وفئته، ويقدمه بوصفه مستحضراً للعناية الشخصية. ولا يتضمن الاسم المتاح بيانات عن الرائحة أو خصائص إضافية أو تعليمات مفصلة.للتعرف على الاستخدام المناسب، تُراجع المعلومات المطبوعة على العبوة قبل التطبيق. وتساعد الكمية المحددة واسم العلامة على تمييز هذا المنتج ضمن المجموعة، من دون افتراض اختلافات أو مزايا لم يرد ذكرها. يتميز المنتج بأن رول للعرق من علامة كيوفي، والكمية المذكورة في الاسم 80 جم، وصيغة الرول ظاهرة في تسمية المنتج. يرجى اتباع تعليمات العبوة لمعرفة موضع الاستعمال والطريقة الموصى بها. يُطبق المنتج بالكيفية الموضحة، وتُراعى الإرشادات الخاصة بالعبوة قبل الاستخدام وبعده.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>يقدَّم كونسيلر أناستازيا 2 كأحد منتجات Anastasia Beverly Hills في فئة كونسيلر. يُطبَّق المنتج بلطف على البشرة بعد كريم الأساس أو قبله حسب الروتين المفضل للمستخدمة. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه.</t>
+          <t>كونسيلر أناستازيا 2 (Anastasia Concealer 2)، من أناستازيا، نوعه مستحضر كونسيلر والدرجة المذكورة 2. كونسيلر من أناستازيا يحمل الرقم 2 في اسم المنتج، وهو مصنف ضمن كريمات الإخفاء والتصحيح للوجه. يساعد تحديد الدرجة بالرقم على تمييز هذا الإصدار عن غيره من الخيارات التي قد تحمل أرقاماً مختلفة، مع ضرورة مطابقة الاسم على العبوة قبل الشراء أو الاستخدام.لا يذكر الاسم المتاح حجم العبوة أو الصيغة أو تفاصيل التغطية، لذا لا تُضاف معلومات عن هذه الخصائص. يمكن إدراج الكونسيلر ضمن مستحضرات مكياج الوجه، مع اختيار الدرجة وفق التفضيل الشخصي وما توضحه بيانات العبوة. من أبرز خصائصه أن كونسيلر يحمل علامة أناستازيا، ورقم الدرجة المذكور هو 2، ومصنف ضمن مستحضرات إخفاء وتصحيح الوجه. يوضع مقدار مناسب على الموضع المراد تصحيحه أو تغطيته، ثم يدمج بلطف مع مستحضرات الوجه الأخرى عند الحاجة. تُراجع تعليمات العبوة، ويُتحقق من رقم الدرجة قبل التطبيق للتأكد من مطابقة المنتج المطلوب.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>منتج عناية St. Ives المعروف باسم St. Ives مرطب الكولاجين والايلاستين المجدد من سانت اي، وهو منتج موجه لهذه الفئة من العناية. يُستخدم المنتج حسب التعليمات المطبوعة على العبوة ضمن روتين العناية المناسب له. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال.</t>
+          <t>مرطب الكولاجين والإيلاستين المجدد، Renewing Collagen Elastin Moisturizer، St. Ives، مرطب. يجمع اسم المنتج بين وصف المرطب وعبارة التجديد، ويذكر الكولاجين والإيلاستين ضمن التسمية. مرطب من St. Ives يحمل اسماً يعرّفه بالكولاجين والإيلاستين، مع وصف المجدد الوارد في التسمية. ويقدّم الاسم صورة مباشرة عن فئة المنتج، من دون تحديد حجم العبوة أو درجة لونية أو موضع استخدام بعينه في البيانات المتاحة.يمكن إدراجه ضمن روتين العناية بالبشرة بوصفه مرطباً، مع الرجوع إلى العبوة لمعرفة تفاصيل الاستعمال والملاءمة. وتبقى المعلومات المؤكدة هنا هي اسم العلامة، ونوع المنتج، والعناصر المذكورة في اسمه، لا تفاصيل إضافية عن تركيبته أو خصائصه. يذكر عن هذا المنتج أنه مرطب يحمل اسم St. Ives، ويذكر الكولاجين والإيلاستين في تسمية المنتج، وتتضمن التسمية وصف المجدد. يُستخدم وفق التعليمات الموضحة على العبوة. لا تتضمن التسمية المتاحة كمية محددة أو عدد مرات التطبيق أو موضعاً دقيقاً للاستخدام، لذا يُرجع إلى بيانات المنتج المطبوعة.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>يندرج فورميولا ليب بالم يرطب الشفاه الجافة 15 ضمن منتجات مرطب شفاه. يُستخدم بوضعه على الشفاه الجافة لترطيبها، مع إغلاق العبوة جيداً بعد كل استخدام. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف.</t>
+          <t>ليب بالم فورميولا لترطيب الشفاه الجافة، Formula Lip Balm for Dry Lips 15، Formula، مرطب شفاه. يعرّف الاسم المنتج بأنه بلسم للشفاه الجافة، ويتضمن الرقم 15 من دون وحدة قياس ظاهرة. بلسم شفاه من Formula، يوضح اسمه أنه موجه لترطيب الشفاه الجافة. وتناسب تسميته من يبحث عن منتج مخصص للعناية بالشفاه، مع الانتباه إلى أن البيانات المتاحة لا تعرض تفاصيل إضافية عن مكوناته أو قوامه.يرد الرقم 15 في الاسم، لكن من دون وحدة قياس؛ لذلك لا يمكن اعتباره حجماً محدداً. أما طريقة الاستعمال والكمية أو عدد مرات التطبيق، فتُعرف من التعليمات المطبوعة على العبوة، لا من الاسم وحده. تشمل خصائصه أن بلسم شفاه من علامة Formula، ويوضح الاسم أنه مخصص للشفاه الجافة، ويُصنف ضمن منتجات العناية الشخصية. يُطبق على الشفاه وفق الإرشادات الواردة على العبوة. لا تحدد البيانات المتاحة عدد مرات الاستخدام أو الكمية، كما لا توضح وحدة قياس الرقم 15 الوارد في الاسم.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3300,7 +3300,6 @@
           <t>17 SAR</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
       <c r="J53" t="b">
         <v>0</v>
       </c>
@@ -3328,7 +3327,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>يندرج كريم تصفيف الشعر بزيت الزيتون من بالمرز 150 ج الصادر عن Palmer's ضمن منتجات مرطب شفاه. يُمرَّر المرطب مباشرة على الشفاه لتوزيعه، ويمكن إعادة التطبيق عند الحاجة خلال اليوم. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال.</t>
+          <t>كريم تصفيف الشعر بزيت الزيتون من بالمرز، Palmer's Olive Oil Hair Styling Cream، Palmer's، كريم تصفيف الشعر، 150 جرام. يحدد اسم المنتج نوعه بوصفه كريم تصفيف، ويذكر زيت الزيتون وحجم العبوة. كريم تصفيف للشعر من Palmer's، يذكر زيت الزيتون في اسمه ويأتي بوزن 150 جراماً. يوضح الاسم وظيفة المنتج بوصفه مخصصاً للتصفيف، ما يجعله خياراً ضمن منتجات العناية بالشعر لمن يبحث عن كريم يحمل هذه التسمية.لا تتضمن البيانات المتاحة تفاصيل عن درجة التثبيت أو نوع الشعر أو ملمس المنتج، لذلك لا تُنسب إليه خصائص إضافية. وللتعرف إلى أسلوب التطبيق والكمية المناسبة، تُراجع التعليمات الموجودة على العبوة. يتميز المنتج بأن كريم مخصص لتصفيف الشعر وفق الاسم، ويحمل علامة Palmer's، ويذكر زيت الزيتون ضمن التسمية. يُستخدم لتصفيف الشعر بحسب الإرشادات المدونة على العبوة. لا تحدد البيانات المتاحة كمية المنتج أو طريقة توزيعه، لذا تُتبع التعليمات المرفقة لتفاصيل التطبيق.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3378,7 +3377,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Palmer's تقدم من خلال بالمرز مرطب الشفاه بخلاصة جوز الهند 4 جرام منتجاً في فئة مرطب شفاه. الحجم المدوَّن على العبوة هو 4 جرام. يُستخدم بوضعه على الشفاه الجافة لترطيبها، مع إغلاق العبوة جيداً بعد كل استخدام. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص.</t>
+          <t>مرطب الشفاه بالمرز بخلاصة جوز الهند، Palmer's Coconut Extract Lip Balm، Palmer's، مرطب شفاه، 4 جرام. يحدد الاسم نوع المنتج، ويذكر خلاصة جوز الهند ووزن العبوة. مرطب شفاه من Palmer's يذكر خلاصة جوز الهند في اسمه، ويأتي بوزن 4 جرام. وتوضح التسمية بجلاء أن المنتج مخصص للعناية بالشفاه، ضمن عبوة محددة الحجم يسهل التعرف إلى بياناتها الأساسية.لا تتضمن المعلومات المتاحة وصفاً إضافياً للتركيبة أو الرائحة أو القوام، كما لا تحدد عدد مرات الاستخدام. لذلك يُكتفى بالبيانات المعلنة في الاسم، وتُراجع العبوة لمعرفة تفاصيل التطبيق وأي تعليمات مصاحبة. من أبرز خصائصه أن مرطب شفاه يحمل علامة Palmer's، ويذكر خلاصة جوز الهند ضمن اسمه، ويأتي بوزن 4 جرام. يُطبق على الشفاه وفق الإرشادات الواردة على العبوة. لا تحدد بيانات الاسم عدد مرات الاستخدام أو كمية التطبيق، لذا يُرجع إلى التعليمات المرفقة بالمنتج.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3428,7 +3427,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>بالمرز كريم زبدة الكاكاو 100 جم من Palmer's، منتج يصنَّف ضمن فئة مرطب شفاه. تبلغ سعة العبوة 100 جم كما هو موضح على المنتج. يُمرَّر المرطب مباشرة على الشفاه لتوزيعه، ويمكن إعادة التطبيق عند الحاجة خلال اليوم. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم.</t>
+          <t>كريم بالمرز بزبدة الكاكاو، Palmer's Cocoa Butter Cream، Palmer's، كريم، 100 جرام. يذكر اسم المنتج زبدة الكاكاو، ويحدد نوعه وحجم العبوة. كريم من Palmer's يحمل زبدة الكاكاو في اسمه، ويأتي بوزن 100 جرام. ويتيح الاسم التعرف إلى العلامة التجارية ونوع المنتج والعنصر المذكور، كما يندرج المنتج ضمن فئة العناية بالجسم.لا تعرض البيانات المتاحة تفاصيل إضافية عن تركيبة الكريم أو قوامه أو طريقة استخدامه. لذلك يُقدَّم المنتج وفق المعلومات الواردة في اسمه، مع الرجوع إلى العبوة للتعرف إلى موضع التطبيق والتعليمات وأي تفاصيل أخرى. يذكر عن هذا المنتج أنه كريم يحمل علامة Palmer's، ويذكر زبدة الكاكاو في اسم المنتج، ويأتي بوزن 100 جرام. يُستخدم وفق التعليمات الموجودة على العبوة. لا تحدد المعلومات المتاحة موضع الاستخدام أو الكمية أو وتيرة التطبيق، لذا تُعتمد الإرشادات المطبوعة على المنتج.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3478,7 +3477,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>يقدَّم بالمرز كريم زبدة كاكاو 200 جرام كأحد منتجات Palmer's في فئة مرطب شفاه. يُطرح المنتج بحجم 200 جرام فقط. يُستخدم بوضعه على الشفاه الجافة لترطيبها، مع إغلاق العبوة جيداً بعد كل استخدام. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه.</t>
+          <t>كريم بالمرز بزبدة الكاكاو 200 جرام، Palmer's Cocoa Butter Cream، من علامة بالمرز، كريم للعناية بالجسم بحجم 200 جرام. كريم للجسم يحمل زبدة الكاكاو في اسمه، ويأتي من بالمرز في عبوة 200 جرام. صيغته الكريمية مخصصة للعناية ببشرة الجسم، ويمكن إدراجه ضمن خطوات العناية اليومية وفق الحاجة وطريقة الاستخدام الموضحة على العبوة.يمنحك حجمه مساحة مناسبة للاستخدام ضمن روتينك المعتاد، سواء خصصتِ له وقتاً بعد الاستحمام أو جعلتِه جزءاً من عنايتك بالبشرة في أي وقت آخر. يظل وصف المنتج محصوراً في اسمه ونوعه وحجمه، لذا يُرجى الرجوع إلى بيانات العبوة للتفاصيل الإضافية. تشمل خصائصه أن كريم مخصص للعناية ببشرة الجسم، ويحمل اسم زبدة الكاكاو ضمن تعريف المنتج، وعبوة بحجم 200 جرام. يُوزع مقدار مناسب على بشرة الجسم النظيفة، ثم يُدلك بلطف حتى يتوزع. يُستخدم وفق تعليمات العبوة، ويمكن تكرار الاستخدام بحسب ما توضحه الجهة المصنّعة. تجنبي وضعه على بشرة متهيجة أو غير سليمة، وتحققي من ملاءمته لبشرتك قبل إدخاله في روتينك.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3528,7 +3527,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>مرطب شفاه Palmer's المعروف باسم كريم بالمرز لعلامات تمدد الجلد 125جم، وهو منتج موجه لهذه الفئة من العناية. يأتي بحجم 125 جم، وهو الحجم المذكور على العبوة دون غيره. يُمرَّر المرطب مباشرة على الشفاه لتوزيعه، ويمكن إعادة التطبيق عند الحاجة خلال اليوم. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه.</t>
+          <t>كريم بالمرز لعلامات تمدد الجلد 125 جم، Palmer's Stretch Marks Cream، من علامة بالمرز، كريم للعناية بالجسم بحجم 125 جم. كريم للعناية بالجسم يرد في اسمه ارتباطه بعلامات تمدد الجلد، وتقدمه علامة بالمرز بعبوة وزنها 125 جم. يتيح شكل الكريم توزيعه على البشرة ضمن خطوات العناية المعتادة، مع الالتزام بما توضحه العبوة بشأن مواضع الاستخدام وطريقته.اختيرت صياغة هذا الوصف لتوضيح هوية المنتج من دون إضافة وعود أو نتائج غير مذكورة في الاسم. يمكن تخصيصه للعناية بالمناطق التي يرغب المستخدم في إدراجها ضمن روتينه، مع مراعاة اختلاف احتياجات البشرة واتباع الإرشادات المدونة على المنتج. يتميز المنتج بأن كريم للعناية ببشرة الجسم، ويرتبط اسمه بعلامات تمدد الجلد، وعبوة بوزن 125 جم. تُتبع التعليمات المثبتة على العبوة لتحديد موضع الاستخدام وتكراره. عند الاستخدام، توزع كمية مناسبة على بشرة نظيفة وتدلك برفق حتى تنتشر على المنطقة المرغوبة. يُنصح بالبدء على مساحة صغيرة إذا كانت هذه أول مرة لاستخدام المنتج، والتوقف عند ظهور انزعاج.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3578,7 +3577,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>من تشكيلة Palmer's، يأتي بالمرز كريم رضاعة مع زبدة الكاكاو 30 جرام ضمن تصنيف مرطب شفاه. الحجم المدوَّن على العبوة هو 30 جرام. يُستخدم بوضعه على الشفاه الجافة لترطيبها، مع إغلاق العبوة جيداً بعد كل استخدام. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف.</t>
+          <t>كريم بالمرز للرضاعة مع زبدة الكاكاو 30 جرام، Palmer's Nursing Cream with Cocoa Butter، من علامة بالمرز، كريم عناية بحجم 30 جرام. كريم يحمل في اسمه الإشارة إلى الرضاعة وزبدة الكاكاو، وتقدمه بالمرز بعبوة صغيرة وزنها 30 جراماً. يُصنف ضمن مستحضرات العناية الشخصية ذات الاستخدام الموضعي، وتُعتمد تعليمات العبوة لتحديد موضع الاستخدام وطريقته، ولا سيما في هذه المرحلة التي تتطلب مراعاة الإرشادات الخاصة بالمنتج.تُعرض العبوة بحجم عملي يسهل الاحتفاظ به ضمن مستلزمات العناية، مع ضرورة قراءة الملصق كاملاً قبل الاستعمال. لا يذكر الاسم تفاصيل إضافية عن الاستخدام أو أي خصائص أخرى؛ لذا يُكتفى بالمعلومات المتاحة على العبوة، ويُستحسن الاستفسار من مختص عند وجود أي تساؤل متعلق باستخدام مستحضر في فترة الرضاعة. من أبرز خصائصه أن كريم عناية مرتبط بالرضاعة بحسب الاسم، ويتضمن اسم المنتج زبدة الكاكاو، وعبوة صغيرة بوزن 30 جراماً. اقرئي التعليمات المطبوعة على العبوة بعناية قبل الاستخدام، واتبعيها كما هي من حيث الموضع والكمية والتوقيت.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3628,7 +3627,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>يندرج بالمرز كريم الصدر 125 جرام الصادر عن Palmer's ضمن منتجات مرطب شفاه. تبلغ سعة العبوة 125 جرام كما هو موضح على المنتج. يُمرَّر المرطب مباشرة على الشفاه لتوزيعه، ويمكن إعادة التطبيق عند الحاجة خلال اليوم. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف.</t>
+          <t>كريم بالمرز للصدر 125 جرام، Palmer's Bust Cream، من علامة بالمرز، كريم عناية بالجسم بحجم 125 جرام. كريم للعناية بالجسم يُعرّف باسمه على أنه مخصص لمنطقة الصدر، وتأتي العبوة من بالمرز بوزن 125 جراماً. يساعد وضوح التسمية على تمييز المنتج ضمن مستحضرات العناية الموضعية، مع ضرورة الرجوع إلى ملصق العبوة لمعرفة التفاصيل الدقيقة المتعلقة بمناطق الاستعمال وطريقته.يمكن إدراجه ضمن روتين العناية الشخصية لمن يبحث عن كريم يحمل هذا الوصف تحديداً. لا يتضمن الاسم درجة أو نتيجة معلنة، لذلك يقتصر التعريف هنا على نوع المستحضر وحجمه والمنطقة المذكورة في اسمه. يُستخدم وفق إرشادات العبوة، مع مراعاة طبيعة البشرة وتجنب وضعه على مناطق غير موصى بها. يذكر عن هذا المنتج أنه كريم عناية للجسم يحمل وصف الصدر في اسمه، وعبوة بوزن 125 جراماً، وصيغة كريم قابلة للتوزيع الموضعي. راجعي العبوة أولاً لتأكيد موضع الاستخدام وطريقة تطبيق الكريم. إذا كانت التعليمات تسمح باستخدامه على المنطقة المقصودة، توزع كمية مناسبة على بشرة نظيفة وتدلك برفق. لا يوضع على مناطق أخرى لم يشر إليها الملصق، ويُوقف الاستخدام عند حدوث انزعاج أو تهيج.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3678,7 +3677,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Palmer's تقدم من خلال بالمرز لعلامات التمدد 125 جرام منتجاً في فئة مرطب شفاه. يُطرح المنتج بحجم 125 جرام فقط. يُستخدم بوضعه على الشفاه الجافة لترطيبها، مع إغلاق العبوة جيداً بعد كل استخدام. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص.</t>
+          <t>كريم بالمرز لعلامات التمدد 125 جرام، Palmer's Stretch Marks Cream، من علامة بالمرز، كريم جسم بحجم 125 جرام. يأتي هذا المنتج من بالمرز في صورة كريم للجسم، ويشير اسمه إلى علامات التمدد بوصفها مجال العناية المرتبط به. تحتوي العبوة على 125 جراماً، ما يجعلها خياراً واضحاً لمن يبحثون عن كريم بهذا الاسم والحجم ضمن مستحضرات العناية الشخصية.يمكن تخصيصه لخطوات العناية بالبشرة وفق تعليمات العبوة، مع عدم افتراض نتائج أو خصائص غير واردة في المعلومات المتاحة. تختلف طريقة الاستخدام بحسب إرشادات المنتج، لذلك يُنصح بقراءتها قبل البدء، خصوصاً عند استخدامه للمرة الأولى أو عند إدخاله في روتين قائم. تشمل خصائصه أن كريم جسم يرتبط اسمه بعلامات التمدد، ووزن العبوة 125 جراماً، وصيغة كريمية للاستخدام الموضعي على البشرة. اتبعي إرشادات العبوة بشأن الكمية والمواضع المقترحة وتكرار الاستخدام. عند التطبيق، وزعي الكريم برفق على بشرة نظيفة في المنطقة المراد العناية بها، من دون الضغط أو الفرك القوي. تجنبي استعماله على مناطق لم ترد ضمن التعليمات، وأوقفي الاستخدام إذا ظهر تهيج.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3728,7 +3727,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>بالمرز زيت بزبدة الكاكاو 150 مل من Palmer's، منتج يصنَّف ضمن فئة مرطب شفاه. يأتي بحجم 150 مل، وهو الحجم المذكور على العبوة دون غيره. يُمرَّر المرطب مباشرة على الشفاه لتوزيعه، ويمكن إعادة التطبيق عند الحاجة خلال اليوم. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم.</t>
+          <t>زيت بالمرز بزبدة الكاكاو 150 مل، Palmer's Cocoa Butter Oil، من علامة بالمرز، زيت للعناية بالجسم بحجم 150 مل. زيت عناية للجسم يحمل زبدة الكاكاو ضمن اسمه، ويأتي من بالمرز في عبوة حجمها 150 مل. تمنح صيغة الزيت طريقة مختلفة عن الكريمات في تطبيق مستحضرات الجسم، ويمكن تخصيصه لخطوة العناية التي تناسب تفضيلاتك، مع الرجوع إلى الملصق لمعرفة التعليمات التفصيلية.العبوة ذات الحجم المحدد تتيح التعرف بسهولة على كمية المنتج قبل الاختيار. يظل وصفه هنا مرتبطاً بما يورده الاسم: زيت من بالمرز، بزبدة الكاكاو، مخصص للعناية بالجسم. لا تُفترض خصائص أو مكونات إضافية غير مذكورة، وتُراعى احتياجات البشرة عند إدخاله في الروتين. يتميز المنتج بأن زيت للعناية ببشرة الجسم، ويتضمن الاسم زبدة الكاكاو، وعبوة بحجم 150 مل. يُستخدم الزيت وفق التعليمات الواردة على العبوة. إذا سمحت الإرشادات بذلك، توضع كمية مناسبة على البشرة وتوزع برفق، مع تجنب الإفراط في الكمية لتفادي بقاء فائض على الجلد أو الأسطح. تأكدي من ملاءمته للمنطقة المراد استخدامها قبل تطبيقه على مساحة واسعة.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3778,7 +3777,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>يقدَّم بالمرز زيت العناية بالبشرة عطر ثمر الورد 60مل كأحد منتجات Palmer's في فئة مرطب شفاه. الحجم المدوَّن على العبوة هو 60 مل. يُستخدم بوضعه على الشفاه الجافة لترطيبها، مع إغلاق العبوة جيداً بعد كل استخدام. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم.</t>
+          <t>زيت بالمرز للعناية بالبشرة بعطر ثمر الورد 60 مل، Palmer's Skin Care Oil Rosehip Fragrance، من علامة بالمرز، زيت عناية بحجم 60 مل. زيت من بالمرز للعناية بالبشرة، يرد عطر ثمر الورد في اسمه، ويتوفر بعبوة 60 مل. يجمع تعريفه بين صيغة الزيت ووصف الرائحة المذكور في التسمية، من دون افتراض مكونات أو خصائص أخرى غير موضحة في الاسم. يمكن إدراجه ضمن روتين العناية بالبشرة بحسب تعليمات العبوة.يُعد الحجم الصغير تفصيلاً عملياً عند المقارنة بين مستحضرات العناية، كما تتيح صيغة الزيت اختيار أسلوب تطبيق يناسب المستخدم. قبل الاستخدام، راجعي بيانات العبوة لمعرفة المناطق المقترحة وطريقة التوزيع، وجرّبي المنتج على مساحة محدودة إذا لم يسبق لك استخدامه. من أبرز خصائصه أن زيت مخصص للعناية بالبشرة، ويذكر الاسم عطر ثمر الورد، وعبوة بحجم 60 مل. اتبعي إرشادات العبوة قبل وضع الزيت، ولا تستخدميه على الوجه أو الجسم إلا إذا كانت التعليمات تشير إلى ذلك. توزع كمية قليلة على البشرة بالطريقة الموضحة على الملصق، مع تجنب ملامسة العينين والأغشية الحساسة.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3828,7 +3827,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>مرطب شفاه Palmer's المعروف باسم زيت مرطب للجسم من بالمرز 250 مل، وهو منتج موجه لهذه الفئة من العناية. تبلغ سعة العبوة 250 مل كما هو موضح على المنتج. يُمرَّر المرطب مباشرة على الشفاه لتوزيعه، ويمكن إعادة التطبيق عند الحاجة خلال اليوم. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه.</t>
+          <t>زيت مرطب للجسم من بالمرز 250 مل، Palmer's Moisturizing Body Oil، من علامة بالمرز، زيت للجسم بحجم 250 مل. زيت للجسم يحمل وصف المرطب ضمن اسمه، وتقدمه علامة بالمرز بحجم 250 مل. تمنح تسمية المنتج دلالة واضحة على صيغته واستخدامه المعلن للعناية بالجسم، فيما توفر العبوة حجماً محدداً يسهل أخذه في الحسبان عند تنظيم مستحضرات العناية اليومية.يمكن توزيع الزيت على البشرة بالطريقة التي توضحها الشركة على العبوة، مع الانتباه إلى أن صيغة الزيت تختلف في طريقة التعامل معها عن الكريمات. لا ترد في الاسم معلومات أخرى عن الرائحة أو المكونات أو خصائص إضافية، لذا يُعتمد على الملصق لاستكمال التفاصيل قبل الاستخدام. يذكر عن هذا المنتج أنه زيت موصوف بأنه مرطب للجسم ضمن الاسم، وعبوة كبيرة نسبياً بحجم 250 مل، وصيغة زيت للعناية بالبشرة. يُستخدم بحسب الإرشادات المكتوبة على العبوة. يمكن توزيع كمية مناسبة على البشرة بالطريقة الموضحة، مع مراعاة أن الزيت قد يترك أثراً على الملابس أو الأسطح قبل جفافه، لذلك يُنتظر وفق تعليمات المنتج قبل ارتداء الملابس.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3878,7 +3877,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>من تشكيلة Palmer's، يأتي بالمرز زيت الجسم بزبدة الكاكو ثمرة الورد150مل ضمن تصنيف مرطب شفاه. يُطرح المنتج بحجم 150 مل فقط. يُستخدم بوضعه على الشفاه الجافة لترطيبها، مع إغلاق العبوة جيداً بعد كل استخدام. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف.</t>
+          <t>زيت الجسم بالمرز بزبدة الكاكاو وثمرة الورد 150 مل، Palmer's Cocoa Butter Rosehip Body Oil، من علامة بالمرز، زيت جسم بحجم 150 مل. زيت للجسم من بالمرز، يذكر في اسمه زبدة الكاكاو وثمرة الورد، ويتوفر بحجم 150 مل. يساعد هذا الوصف على تمييزه عن زيوت الجسم الأخرى في المجموعة، من دون إضافة تفاصيل عن مكونات أو خصائص لم يوردها الاسم المعروض. تُعتمد معلومات العبوة لمعرفة طريقة الاستخدام المحددة.تتيح صيغة الزيت إدراجه في روتين العناية بالجسم لمن يفضلون المستحضرات السائلة، ويُراعى عند استعماله توزيع كمية مناسبة بحسب الإرشادات. لا يذكر الاسم درجة أو لوناً، كما لا يوضح تفاصيل إضافية عن العطر؛ لذا تظل المعلومات المطبوعة على العبوة المرجع لاستكمال البيانات. تشمل خصائصه أن زيت مخصص للعناية بالجسم، ويذكر الاسم زبدة الكاكاو وثمرة الورد، وعبوة بحجم 150 مل. اتبعي التعليمات المدونة على العبوة لتحديد طريقة وضع الزيت والمواضع المناسبة. توزع كمية ملائمة على البشرة وفق الإرشادات، مع الحرص على عدم ملامسة العينين وغسل اليدين بعد التطبيق إذا اقتضت الحاجة.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3928,7 +3927,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>يندرج بالمرز كريم القدمين ماجيك 60 جرام الصادر عن Palmer's ضمن منتجات مرطب شفاه. يأتي بحجم 60 جرام، وهو الحجم المذكور على العبوة دون غيره. يُمرَّر المرطب مباشرة على الشفاه لتوزيعه، ويمكن إعادة التطبيق عند الحاجة خلال اليوم. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف.</t>
+          <t>كريم القدمين ماجيك من بالمرز Palmer's Magic Foot Cream، كريم للقدمين بحجم 60 جرام. يحمل الاسم وصف ماجيك، ويقدّم في عبوة مخصصة للعناية بالقدمين، مع تحديد العلامة التجارية والحجم في اسم المنتج. اختيار عملي ضمن مستحضرات العناية بالجسم، صُمم على هيئة كريم للقدمين ليدخل بسهولة في روتين العناية اليومي. يأتي باسم ماجيك من بالمرز، وتوضح بياناته الأساسية نوع المنتج وحجمه بوضوح، لتتمكني من التعرف إلى العبوة ومحتواها قبل الاستخدام.يمكن توزيع الكريم على بشرة القدمين النظيفة مع تدليك لطيف حتى يتوزع على المنطقة المراد العناية بها. لا يتضمن الاسم تفاصيل إضافية عن مكونات المنتج أو درجة محددة، لذلك يُرجى الرجوع إلى بيانات العبوة للاطلاع على أي إرشادات أو معلومات تفصيلية أخرى. يتميز المنتج بأن كريم مخصص للعناية بالقدمين، ويحمل اسم ماجيك كما ورد في المنتج، ويأتي من علامة بالمرز. توضع كمية مناسبة على بشرة القدمين النظيفة، ثم توزع بتدليك لطيف حتى تغطي المنطقة المطلوبة. يُستخدم وفق الإرشادات المدونة على العبوة، مع تجنب وضعه على المناطق التي لا تذكرها تعليمات المنتج.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3978,7 +3977,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Palmer's تقدم من خلال بالمرز لوشن الجسم زبدة الشيا 250 مل منتجاً في فئة مرطب شفاه. الحجم المدوَّن على العبوة هو 250 مل. يُستخدم بوضعه على الشفاه الجافة لترطيبها، مع إغلاق العبوة جيداً بعد كل استخدام. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص.</t>
+          <t>لوشن الجسم بزبدة الشيا من بالمرز Palmer's Shea Butter Body Lotion، لوشن للجسم بحجم 250 مل. يذكر اسم المنتج زبدة الشيا بوصفها جزءًا من اسمه، ويحدد شكل المستحضر وحجمه والعلامة التجارية. يأتي هذا المستحضر من بالمرز بصيغة لوشن مخصص للجسم، ويحمل اسم زبدة الشيا كما ورد في بيانات المنتج. يتيح شكل اللوشن توزيعه على البشرة ضمن روتين العناية المعتاد، فيما تساعد معلومات الحجم والعلامة التجارية على تمييز العبوة عند اختيار مستحضرات الجسم.يمكن استخدامه على بشرة الجسم بالطريقة الموضحة على العبوة، مع توزيع كمية مناسبة على المنطقة المطلوبة. لا يحدد الاسم تفاصيل عن نسبة زبدة الشيا أو مكونات أخرى، لذلك تظل بيانات العبوة المرجع لمعرفة أي معلومات إضافية تخص المنتج. من أبرز خصائصه أن لوشن مخصص للاستخدام على الجسم، ويحمل اسم زبدة الشيا ضمن وصف المنتج، ومن علامة بالمرز التجارية. يوزع مقدار مناسب على بشرة الجسم، ثم يمرر بلطف على المنطقة المراد العناية بها. يُستخدم بحسب إرشادات العبوة، ويُترك أو يُغسل وفق ما توضحه تعليمات المنتج، إذ لا يذكر الاسم طريقة تفصيلية للاستخدام.</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4028,7 +4027,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>كريم مغذي للشعر ضد القشره من بالمرز - 150 جم من Palmer's، منتج يصنَّف ضمن فئة مرطب شفاه. تبلغ سعة العبوة 150 جم كما هو موضح على المنتج. يُمرَّر المرطب مباشرة على الشفاه لتوزيعه، ويمكن إعادة التطبيق عند الحاجة خلال اليوم. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم.</t>
+          <t>كريم مغذي للشعر ضد القشرة من بالمرز Palmer's Nourishing Anti-Dandruff Hair Cream، كريم للشعر بحجم 150 جم. يجمع اسم المنتج بين وصف مغذٍ للشعر والإشارة إلى القشرة، من دون أن يحدد تفاصيل عن مكونات الكريم أو طريقة استخدامه الدقيقة. يأتي هذا الكريم من بالمرز ضمن مستحضرات العناية بالشعر، ويحمل في اسمه وصفًا مغذيًا وإشارة إلى القشرة. يوضح الاسم حجم العبوة، 150 جم، ونوع المنتج بوصفه كريمًا، بينما تبقى تفاصيل التركيبة وطريقة التطبيق الدقيقة مرتبطة بما هو مدون على العبوة.يمكن استخدامه للعناية بالشعر وفق التعليمات المرفقة بالمنتج. ولأن الاسم لا يحدد موضع وضع الكريم أو مدة بقائه أو عدد مرات الاستخدام، فمن الأفضل الرجوع إلى بيانات العبوة قبل إدخاله في الروتين. يصف الاسم المنتج بأنه ضد القشرة، من دون إضافة ادعاءات علاجية أو معلومات غير واردة فيه. يذكر عن هذا المنتج أنه كريم مخصص للعناية بالشعر، ويذكر الاسم وصفًا مغذيًا للشعر، ويتضمن الاسم إشارة إلى القشرة. يستخدم على الشعر وفق الإرشادات المدونة على العبوة، مع الالتزام بموضع التطبيق والكمية وطريقة التوزيع المحددة للمنتج.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4078,7 +4077,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>يقدَّم بالمرز صابون زبدة الكاكاو مع فيتامين 133 جم كأحد منتجات Palmer's في فئة مرطب شفاه. يُطرح المنتج بحجم 133 جم فقط. يُستخدم بوضعه على الشفاه الجافة لترطيبها، مع إغلاق العبوة جيداً بعد كل استخدام. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم.</t>
+          <t>صابون زبدة الكاكاو مع فيتامين من بالمرز Palmer's Cocoa Butter Soap with Vitamin، صابون للجسم بحجم 133 جم. يذكر الاسم زبدة الكاكاو وفيتامين من دون تحديد نوع الفيتامين، كما يوضح العلامة التجارية وحجم قطعة الصابون. قطعة صابون للعناية بالجسم من بالمرز، يحمل اسمها زبدة الكاكاو مع فيتامين. يحدد الاسم شكل المنتج وحجمه البالغ 133 جم، ويتيح تمييزه ضمن مستحضرات التنظيف والعناية الشخصية. لا يذكر اسم المنتج نوع الفيتامين أو تفاصيل تركيبته، لذا تُراجع بيانات العبوة لأي معلومات إضافية.يمكن استعمال الصابون لتنظيف الجسم بالطريقة المعتادة، مع ترطيب القطعة بالماء وتكوين رغوة ثم شطف البشرة جيدًا. تبقى تعليمات الاستخدام المطبوعة على المنتج هي المرجع، خصوصًا إذا كانت هناك توجيهات خاصة بطريقة الاستعمال أو مناطق الاستخدام. تشمل خصائصه أن صابون مخصص للاستخدام على الجسم، ويذكر زبدة الكاكاو ضمن اسم المنتج، ويتضمن الاسم إشارة إلى فيتامين من دون تحديد نوعه. تبلل البشرة وقطعة الصابون بالماء، ثم تمرر القطعة لتكوين رغوة على المنطقة المراد تنظيفها، وبعد ذلك تشطف البشرة جيدًا.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4128,7 +4127,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>مقشر Dove المعروف باسم دوف مقشر جسم بحليب الأرز 298، وهو منتج موجه لهذه الفئة من العناية. يُستخدم المقشر بتدليكه على البشرة الرطبة بحركات دائرية خفيفة ثم يُشطف بالماء. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال.</t>
+          <t>مقشر الجسم بحليب الأرز من دوف Dove Rice Milk Body Scrub، مقشر للجسم بحجم 298. يذكر اسم المنتج حليب الأرز، ويحدد نوع المستحضر بوصفه مقشرًا للجسم، بينما يرد الحجم بالرقم 298 من دون وحدة في الاسم. مقشر للجسم من دوف يحمل حليب الأرز ضمن اسمه، ويأتي ضمن مستحضرات العناية المخصصة للجسم. يوضح الاسم العلامة التجارية ونوع المنتج، كما يذكر الرقم 298 للحجم من دون إظهار وحدة قياس؛ لذلك لا تُضاف وحدة غير واردة في بياناته.يمكن استخدام المقشر على بشرة الجسم وفق التعليمات المدونة على العبوة. يوزع بلطف على المنطقة المطلوبة ثم يشطف إذا كانت تعليمات المنتج تنص على ذلك. لا يحدد الاسم طريقة التدليك أو عدد مرات الاستخدام أو مكونات أخرى، ولهذا ينبغي الرجوع إلى العبوة لمعرفة التفاصيل المرتبطة بالاستخدام. يتميز المنتج بأن مقشر مخصص للعناية بالجسم، ويذكر حليب الأرز ضمن اسم المنتج، ومن علامة دوف التجارية. يوضع المقشر على بشرة الجسم وفق إرشادات العبوة، ويدلك بلطف إذا أوصت التعليمات بذلك، ثم يشطف بالطريقة المحددة للمنتج. راجعي طريقة الاستخدام المطبوعة قبل الاستعمال، إذ لا يحدد الاسم تفاصيل التكرار أو مدة التدليك.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4178,7 +4177,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>من تشكيلة Dove، يأتي دوف مقشر الجسم بخلاصة بذور الرمان 298 جم ضمن تصنيف مقشر. الحجم المدوَّن على العبوة هو 298 جم. يُطبَّق على الجسم أثناء الاستحمام بحركات تدليك لطيفة، ثم يُغسل جيداً بالماء. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف.</t>
+          <t>مقشر الجسم بخلاصة بذور الرمان من دوف Dove Pomegranate Seed Body Scrub، مقشر للجسم بحجم 298 جم. يحدد اسم المنتج خلاصة بذور الرمان، ويبين نوع المستحضر والعلامة التجارية والوزن الوارد على العبوة. هذا مقشر للجسم من دوف، يحمل خلاصة بذور الرمان ضمن اسمه ويأتي بوزن 298 جم. يوضح وصفه أنه مخصص للعناية بالجسم، فيما توفر بيانات الاسم معلومات مباشرة عن العلامة التجارية والمادة المذكورة والحجم، من دون تحديد مكونات أخرى أو نسبها.يستخدم المقشر على الجسم وفق التعليمات الموجودة على العبوة. يمكن توزيعه بلطف على البشرة بالطريقة التي توصي بها الشركة، ثم شطفه إذا كانت تعليمات المنتج تنص على ذلك. لا يحدد الاسم عدد مرات الاستخدام أو مدة التدليك، لذا تُتبع الإرشادات المرفقة بدل افتراض روتين ثابت. من أبرز خصائصه أن مقشر مخصص للاستخدام على الجسم، ويذكر خلاصة بذور الرمان في اسمه، ومن علامة دوف التجارية. يوضع على بشرة الجسم بالطريقة المحددة على العبوة، ويوزع بتدليك لطيف إذا ورد ذلك ضمن التعليمات، ثم يشطف وفق الإرشادات. راجعي العبوة لمعرفة طريقة الاستخدام كاملة وتفاصيل التكرار المناسبة للمنتج.</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4228,7 +4227,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>يندرج مقشر الجسم دوف باللافندر وحليب جوز الهند 298 الصادر عن Dove ضمن منتجات مقشر. يُستخدم المقشر بتدليكه على البشرة الرطبة بحركات دائرية خفيفة ثم يُشطف بالماء. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال.</t>
+          <t>مقشر الجسم باللافندر وحليب جوز الهند من دوف Dove Lavender and Coconut Milk Body Scrub، مقشر للجسم بحجم 298. يذكر الاسم اللافندر وحليب جوز الهند، ويحدد نوع المنتج والعلامة التجارية، بينما لا يورد وحدة قياس للرقم 298. مقشر للجسم من دوف، يجمع اسمه بين اللافندر وحليب جوز الهند كما وردا في بيانات المنتج. يندرج ضمن مستحضرات العناية بالجسم، ويأتي الرقم 298 ضمن الاسم من دون وحدة قياس، لذلك يُنقل الحجم كما ورد من غير افتراض جرام أو مل.تُستخدم المقشرات على الجسم وفق تعليمات العبوة، مع الالتزام بطريقة التوزيع والشطف المحددة للمنتج. لا يوضح الاسم تفاصيل عن التركيبة أو نسب المكونات، كما لا يحدد مدة التدليك أو عدد مرات الاستخدام. تساعد قراءة بيانات العبوة على معرفة الإرشادات الخاصة بهذا المنتج قبل إضافته إلى روتين العناية. يذكر عن هذا المنتج أنه مقشر مخصص للجسم، ويذكر اللافندر ضمن اسم المنتج، ويتضمن الاسم حليب جوز الهند. يوزع على بشرة الجسم بالطريقة المذكورة على العبوة، مع تدليك لطيف فقط إذا كانت التعليمات توصي بذلك، ثم يشطف وفق الإرشادات.</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4278,7 +4277,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dove تقدم من خلال دوف مقشر الجسم بزبدة اللوز والمانجو298جم منتجاً في فئة مقشر. يُطرح المنتج بحجم 298 جم فقط. يُطبَّق على الجسم أثناء الاستحمام بحركات تدليك لطيفة، ثم يُغسل جيداً بالماء. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص.</t>
+          <t>مقشر الجسم بزبدة اللوز والمانجو من دوف Dove Almond Butter and Mango Body Scrub، مقشر للجسم بحجم 298 جم. يذكر الاسم زبدة اللوز والمانجو، ويحدد وزن العبوة والعلامة التجارية ونوع المستحضر. مقشر للجسم من دوف، يحمل زبدة اللوز والمانجو في اسمه، ويأتي بوزن 298 جم. يوضح الاسم طبيعة المستحضر المخصص للجسم والعلامة التجارية، كما يورد العناصر المذكورة في تعريف المنتج من دون عرض قائمة كاملة بالمكونات أو نسبها.يمكن إدخال المقشر ضمن روتين العناية بالجسم، مع استخدامه بالطريقة التي توضحها العبوة. يوزع على المنطقة المطلوبة وفق التعليمات، ويشطف إذا كانت الإرشادات تنص على ذلك. لا يحدد الاسم عدد مرات الاستخدام أو تفاصيل التدليك، لذا تُتبع المعلومات المدونة على العبوة ولا يُفترض برنامج استخدام ثابت. تشمل خصائصه أن مقشر مخصص للعناية بالجسم، ويذكر زبدة اللوز ضمن اسم المنتج، ويتضمن الاسم المانجو. يستخدم على بشرة الجسم وفق التعليمات المطبوعة على العبوة. يوزع بلطف على المنطقة المطلوبة، ثم يشطف إذا نصت الإرشادات على ذلك. راجعي تفاصيل الاستعمال قبل الاستخدام لمعرفة التكرار وطريقة التطبيق الخاصة بالمنتج.</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4328,7 +4327,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>دوف مقشر الجسم بملح الهيمالايا وزيت الورد425ج من Dove، منتج يصنَّف ضمن فئة مقشر. يُستخدم المقشر بتدليكه على البشرة الرطبة بحركات دائرية خفيفة ثم يُشطف بالماء. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم.</t>
+          <t>دوف مقشر الجسم بملح الهيمالايا وزيت الورد Dove Himalayan Salt and Rose Oil Body Scrub من دوف، نوعه مقشر جسم، بحجم 425 جم. مقشر جسم من دوف يجمع في اسمه بين ملح الهيمالايا وزيت الورد، ليكون خطوة مخصصة لتقشير بشرة الجسم ضمن روتين العناية. يأتي المنتج بعبوة وزنها 425 جم، ويمكن إدراجه في روتين الاستحمام مع مراعاة طريقة الاستخدام الموضحة على العبوة.تمنحك تسمية المنتج تصوراً واضحاً عن طابعه: مقشر للجسم بتركيبة يرد فيها ملح الهيمالايا وزيت الورد. اختاريه عندما ترغبين في تخصيص خطوة للتقشير، مع استخدام لطيف وتجنب الضغط الشديد على البشرة. يتميز المنتج بأن مخصص لتقشير بشرة الجسم، ويحتوي اسم المنتج على ملح الهيمالايا وزيت الورد، ويندرج ضمن منتجات العناية بالجسم من دوف. اتبعي الإرشادات المطبوعة على العبوة. يوزع المقشر على بشرة الجسم بالطريقة المحددة للمنتج، مع تدليك لطيف ثم الشطف إذا كانت تعليمات العبوة تنص على ذلك. تجنبي استخدامه على البشرة المتهيجة أو المجروحة، ولا تكثري من الضغط أثناء التدليك.</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4378,7 +4377,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>يقدَّم دوف, مقشر جسم بالكرز, وحليب الشيا , 425جم كأحد منتجات Dove في فئة مقشر. الحجم المدوَّن على العبوة هو 425 جم. يُطبَّق على الجسم أثناء الاستحمام بحركات تدليك لطيفة، ثم يُغسل جيداً بالماء. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه.</t>
+          <t>دوف مقشر الجسم بالكرز وحليب الشيا Dove Cherry and Shea Milk Body Scrub من دوف، نوعه مقشر جسم، بحجم 425 جم. يأتي هذا المقشر من دوف مخصصاً للعناية ببشرة الجسم، ويحمل في اسمه الكرز وحليب الشيا. ويبلغ وزن العبوة 425 جم، ما يتيح إدراجه ضمن مستلزمات العناية بالجسم والاستحمام. استخدميه وفق الطريقة المبيّنة على العبوة، مع مراعاة احتياجات بشرتك وتجنب الفرك القوي.يجمع الاسم بين طابع الفاكهة وإشارة حليب الشيا، مع تحديد واضح لوظيفة المنتج كمقشر للجسم. ويمكن تخصيصه لخطوة التقشير في روتينك، على أن تظل تفاصيل الاستخدام وعدد مرات التكرار مرتبطة بتوجيهات العبوة. من أبرز خصائصه أن مقشر مخصص لبشرة الجسم، ويذكر اسم المنتج الكرز وحليب الشيا، ومن منتجات دوف للعناية بالجسم. راجعي تعليمات الاستخدام على العبوة قبل البدء. استخدمي المقشر على الجسم بالطريقة الموضحة، ودلكي بلطف دون ضغط زائد، ثم اشطفيه إذا كانت طريقة الاستخدام تنص على ذلك. تجنبي وضعه على البشرة المتضررة أو شديدة التحسس، ولا تستخدميه أكثر مما توصي به العبوة.</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4428,7 +4427,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>معجون أسنان Sensodyne المعروف باسم سنسوداين معجون اسنان إنتعاش زائد 50 مل، وهو منتج موجه لهذه الفئة من العناية. تبلغ سعة العبوة 50 مل كما هو موضح على المنتج. يُستخدم المعجون بكمية مناسبة على فرشاة الأسنان مرتين يومياً ضمن روتين تنظيف الفم المعتاد. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه.</t>
+          <t>سنسوداين معجون أسنان انتعاش زائد Sensodyne Extra Fresh Toothpaste من سنسوداين، نوعه معجون أسنان، بحجم 50 مل. معجون أسنان من سنسوداين يحمل اسم انتعاش زائد، ويأتي بحجم 50 مل. يندرج ضمن منتجات العناية الشخصية المخصصة لتنظيف الأسنان، ويمكن استخدامه كجزء من روتين العناية بالفم وفق الإرشادات المدونة على العبوة.يوضح الاسم نوع المنتج واسمه التجاري دون الإشارة إلى درجة أو مقاس آخر. ولأن معاجين الأسنان تختلف في تعليمات الاستخدام والفئة العمرية المناسبة، ينبغي قراءة بيانات العبوة واتباعها، وعدم تجاوز الكمية أو الطريقة الموضحة من الشركة المصنّعة. يذكر عن هذا المنتج أنه معجون أسنان من علامة سنسوداين، ويحمل اسم انتعاش زائد، وحجم العبوة 50 مل. استخدمي المعجون وفق الإرشادات المطبوعة على العبوة، وبالطريقة المناسبة للعمر المحدد في بيانات المنتج. لا تبتلعي المعجون، واحرصي على إغلاق العبوة بعد الاستخدام. عند وجود استفسار حول ملاءمته أو طريقة استعماله، يمكن الرجوع إلى تعليمات الشركة أو سؤال مختص بالعناية بالأسنان.</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4478,7 +4477,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>من تشكيلة Clinique، يأتي بودرة كلينيك المضغوطة الشفافة غير اللامعة ضمن تصنيف بودرة. تُستخدم بتمرير الفرشاة بها خفيفاً على الوجه، مع إمكانية إعادة التطبيق خلال اليوم عند الحاجة. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف.</t>
+          <t>بودرة كلينيك المضغوطة الشفافة غير اللامعة Clinique Transparent Matte Pressed Powder من كلينيك، نوعها بودرة وجه مضغوطة. بودرة وجه مضغوطة من كلينيك، يحدد اسمها أنها شفافة وغير لامعة. تأتي بصيغة مضغوطة وتندرج ضمن منتجات مكياج الوجه. لا يذكر الاسم درجة لونية أو حجماً محدداً، لذلك يفضل مراجعة بيانات العبوة أو المنتج للتعرف على أي تفاصيل إضافية قبل الاختيار.تتيح طبيعتها المضغوطة حملها واستخدامها ضمن روتين المكياج، مع إمكانية توزيعها بأداة نظيفة مناسبة. وللحفاظ على مظهر متوازن، توضع بكمية قليلة وتزاد تدريجياً عند الحاجة، مع اتباع تعليمات الاستخدام التي يوردها المنتج. تشمل خصائصه أن بودرة مخصصة لمكياج الوجه، وتركيبة مضغوطة وفق اسم المنتج، وموصوفة بأنها شفافة وغير لامعة. استخدمي أداة مكياج نظيفة، وخذي كمية مناسبة ثم وزعيها برفق على الوجه وفق حاجتك. ابدئي بطبقة خفيفة، ويمكن زيادة الكمية تدريجياً. راجعي تعليمات العبوة، وأغلقيها بعد الاستخدام لحماية المنتج من التلوث أو الانسكاب.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4528,7 +4527,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>يندرج بخاخ مويستشر سيرج للوجه 125 مل - كلينيك الصادر عن Clinique ضمن منتجات بخاخ. يأتي بحجم 125 مل، وهو الحجم المذكور على العبوة دون غيره. يُستخدم البخاخ برشه على المنطقة المستهدفة من مسافة مناسبة. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال.</t>
+          <t>بخاخ مويستشر سيرج للوجه Moisture Surge Face Spray من كلينيك، نوعه رذاذ ترطيب الوجه، بحجم 125 مل. رذاذ للوجه من مجموعة مويستشر سيرج من كلينيك، ويأتي بحجم 125 مل. يندرج ضمن منتجات الترطيب والعناية بالبشرة، وتمنح صيغة البخاخ طريقة استخدام مختلفة عن الكريمات أو المستحضرات التي توزع باليد. يمكن إدخاله في روتين الوجه وفق الإرشادات المدونة على العبوة.يحمل المنتج اسماً يوضح ارتباطه بترطيب الوجه، من دون أن يذكر الاسم نوع البشرة أو مكونات محددة. لذلك احرصي على مراجعة بيانات العبوة للتعرف على تفاصيل المنتج وطريقة تطبيقه، واستخدميه بحذر مع إبعاد الرذاذ عن العينين. يتميز المنتج بأن بخاخ مخصص للوجه، وينتمي إلى مجموعة مويستشر سيرج من كلينيك، ويأتي بحجم 125 مل. راجعي الإرشادات على العبوة قبل الاستعمال. عند الاستخدام، أغمضي العينين واتبعي الطريقة المحددة للرش، مع تجنب توجيه الرذاذ مباشرة إلى العينين أو استنشاقه. لا تستبدلي تعليمات الشركة بطريقة غير موضحة، وأغلقي العبوة بعد الانتهاء.</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4578,7 +4577,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Clinique تقدم من خلال كلينيك بلسم تنظيف تيك ذا داي اوف للجنسين125مل منتجاً في فئة بلسم تنظيف. الحجم المدوَّن على العبوة هو 125 مل. يُطبَّق على البشرة الجافة بحركات دائرية ثم يُغسل بالماء الفاتر. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص.</t>
+          <t>كلينيك بلسم تنظيف تيك ذا داي أوف Clinique Take The Day Off Cleansing Balm من كلينيك، نوعه بلسم تنظيف الوجه، بحجم 125 مل، ومذكور أنه للجنسين. بلسم تنظيف للوجه من كلينيك يحمل اسم تيك ذا داي أوف، ويأتي بحجم 125 مل. ويشير الاسم الإنجليزي إلى بلسم للتنظيف، بينما يرد في بيانات المنتج أنه للجنسين. يمكن إدراجه في خطوات تنظيف الوجه، مع الرجوع إلى تعليمات العبوة لمعرفة كيفية تطبيقه وإزالته.يقدم البلسم بديلاً بصيغة مختلفة عن الغسول السائل، ويتيح اختيار طريقة التنظيف وفق ما يلائم روتينك. لا يذكر الاسم نوع البشرة أو تفاصيل التركيبة؛ لذا من الأفضل مراجعة بيانات المنتج كاملة قبل الاستخدام، واتباع الخطوات الموضحة من العلامة. من أبرز خصائصه أن بلسم مخصص لتنظيف الوجه، ويحمل اسم تيك ذا داي أوف، ومن علامة كلينيك. اتبعي التعليمات المطبوعة على العبوة لمعرفة طريقة توزيع البلسم وإزالته. استخدميه على الوجه بالطريقة المحددة، ثم أكملي روتين التنظيف وفق احتياجك. تجنبي وضعه على محيط العينين ما لم توضح العبوة خلاف ذلك، واغسلي اليدين بعد الاستخدام.</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4628,7 +4627,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>كلينيك جل مرطب درامتكلي ديفرنت - 125 مل من Clinique، منتج يصنَّف ضمن فئة جل. تبلغ سعة العبوة 125 مل كما هو موضح على المنتج. يُستخدم الجل بتوزيعه على المنطقة المطلوبة ضمن روتين العناية المعتاد. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم.</t>
+          <t>كلينيك جل مرطب درامتكلي ديفرنت Clinique Dramatically Different Moisturizing Gel من كلينيك، نوعه جل مرطب للوجه، بحجم 125 مل. جل مرطب من كلينيك يحمل اسم درامتكلي ديفرنت، ويأتي بحجم 125 مل. يندرج ضمن مستحضرات ترطيب البشرة، وتمنحه صيغة الجل قواماً مختلفاً عن الكريمات التقليدية. يمكن إدخاله في روتين العناية بالوجه وفق الطريقة الموضحة على العبوة.لا يحدد الاسم نوع البشرة أو أوقات الاستخدام، لذا اطلعي على بيانات المنتج قبل تطبيقه، خاصة إذا كنت تستخدمين منتجات أخرى ضمن الروتين نفسه. يوزع الجل على البشرة بالطريقة الملائمة حسب إرشادات العبوة، مع تجنب محيط العينين. يذكر عن هذا المنتج أنه جل مرطب للوجه من كلينيك، ويحمل اسم درامتكلي ديفرنت، ويأتي بحجم 125 مل. ضعي الجل وفق تعليمات العبوة، ووزعيه برفق على بشرة الوجه مع تجنب العينين. ابدئي بالكمية التي توصي بها الشركة، واتركي المستحضر يمتص بحسب توجيهات المنتج قبل متابعة روتينك. راجعي العبوة لمعرفة التوقيت والتكرار المناسبين.</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4678,7 +4677,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>يقدَّم كلينيك صابون سائل للوجه للبشرة الدهنية 200مل كأحد منتجات Clinique في فئة صابون. يُطرح المنتج بحجم 200 مل فقط. تُستعمل بفرك الصابونة باليدين أو بليفة حتى تتكون الرغوة، ثم تُغسل المنطقة بالماء. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم.</t>
+          <t>كلينيك صابون سائل للوجه للبشرة الدهنية Clinique Liquid Facial Soap Oily Skin من كلينيك، نوعه غسول وجه سائل، بحجم 200 مل. منظف سائل للوجه من كلينيك، يذكر اسمه أنه مخصص للبشرة الدهنية، ويأتي بحجم 200 مل. يندرج ضمن منتجات تنظيف الوجه، ويمكن إدراجه في خطوة غسل البشرة ضمن الروتين اليومي وفق تعليمات العبوة.تساعد صيغة الصابون السائل على توزيع المنتج أثناء التنظيف، مع ضرورة الالتزام بطريقة الاستخدام الموصى بها وتجنب المبالغة في الغسل. إذا كانت لديك استفسارات حول ملاءمته لبشرتك أو توافقه مع مستحضرات أخرى، راجعي بيانات المنتج أو استشيري مختصاً. تشمل خصائصه أن صابون سائل مخصص لتنظيف الوجه، ومذكور للبشرة الدهنية في الاسم، ومن علامة كلينيك. اتبعي تعليمات العبوة، وبللي الوجه إذا كانت طريقة الاستخدام تنص على ذلك، ثم وزعي كمية مناسبة من المنظف بلطف واشطفيه جيداً عند الانتهاء. تجنبي ملامسة العينين، ولا تستخدميه على بشرة متضررة. أغلقي العبوة بعد الاستعمال.</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4728,7 +4727,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>زيت De La Cruz المعروف باسم زيت فيتامين E من دي لا كروز، 65 مل، وهو منتج موجه لهذه الفئة من العناية. يأتي بحجم 65 مل، وهو الحجم المذكور على العبوة دون غيره. يُستخدم الزيت بتوزيع كمية مناسبة منه على الجسم أو المنطقة المستهدفة ودلكه برفق. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه.</t>
+          <t>زيت فيتامين هـ من دي لا كروز، 65 مل — De La Cruz Vitamin E Oil, 65 ml؛ زيت للعناية بالبشرة من علامة دي لا كروز، بالحجم المذكور في الاسم. تأتي صيغته الزيتية لتكون خياراً واضحاً لمن يفضّلون إدراج الزيوت ضمن خطوات عنايتهم اليومية، مع الحفاظ على بساطة الاختيار بحسب طبيعة الروتين الشخصي. يجمع هذا المنتج بين شكل الزيت واسم فيتامين هـ في عبوة محددة الحجم، ليمنحك خياراً عملياً عند ترتيب منتجات العناية بالبشرة. ويمكن التعامل معه كخطوة مستقلة أو إدراجه ضمن الروتين المعتاد وفق تعليمات العبوة، مع اختيار موضع الاستخدام والكمية بما يلائم تفضيلاتك.لا يذكر الاسم درجة لونية أو رائحة أو مواصفات إضافية؛ لذلك يظل التركيز هنا على هويته كزيت فيتامين هـ من دي لا كروز وحجمه البالغ 65 مل. اختاريه بناءً على رغبتك في استخدام مستحضر ذي قوام زيتي، وتحققي من إرشادات العبوة قبل إدخاله في روتينك. يتميز المنتج بأن مستحضر زيتي يحمل اسم فيتامين هـ، وحجم العبوة 65 مل كما ورد في اسم المنتج، ومن علامة دي لا كروز. راجعي تعليمات العبوة أولاً، ثم ضعي كمية مناسبة على بشرة نظيفة في الموضع المرغوب.</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4778,7 +4777,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>من تشكيلة De La Cruz، يأتي كريم فيتامين هـ من دي لا كروز - 12جم ضمن تصنيف كريم. الحجم المدوَّن على العبوة هو 12 جم. يُطبَّق على البشرة النظيفة بكمية مناسبة حسب الحاجة. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف.</t>
+          <t>كريم فيتامين هـ من دي لا كروز، 12 جم — De La Cruz Vitamin E Cream, 12 g؛ كريم للعناية بالبشرة من علامة دي لا كروز، بحجم 12 جم. يأتي في صورة كريم سهلة التمييز عن المستحضرات الزيتية، ويقدّم خياراً محدد الاسم والحجم لمن يرغب في تنظيم مستحضراته واختيارها وفق شكل المنتج الذي يفضّله. يحمل الكريم اسم فيتامين هـ، وتأتي العبوة بحجم 12 جم، ما يجعل تفاصيله الأساسية واضحة عند المقارنة أو ترتيب منتجات العناية. ينسجم شكله الكريمي مع الروتين الذي يفضّل فيه المستخدم مستحضراً بهذا القوام، ويمكن استعماله وفق الإرشادات المكتوبة على العبوة.لا يتضمن الاسم درجة أو رائحة أو معلومات أخرى عن خصائص المنتج؛ لذا يقتصر التعريف به على كونه كريم فيتامين هـ من دي لا كروز وحجمه المحدد. اختاري موضع الاستعمال وطريقته بالرجوع إلى تعليمات العبوة، وادمجيه في روتينك بما يتوافق مع تفضيلاتك. من أبرز خصائصه أن قوام كريم وفق نوع المنتج الوارد في الاسم، ويحمل اسم فيتامين هـ، وحجم العبوة 12 جم. استخدميه وفق التعليمات المدونة على العبوة.</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4828,7 +4827,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>يندرج كريم أساس 1 دبليو1 دبل وير من استي لودر الصادر عن Estée Lauder ضمن منتجات كريم أساس. يُطبَّق كريم الأساس على الوجه بإسفنجة أو فرشاة مخصصة، ويمكن دمجه بحركات دائرية خفيفة. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال.</t>
+          <t>كريم أساس دبل وير بدرجة 1W1 من استي لودر — Estée Lauder Double Wear Foundation 1W1؛ كريم أساس للوجه من العلامة التجارية استي لودر، والدرجة المذكورة في الاسم هي 1W1. يقدم تعريف المنتج اسمه ودرجته بوضوح لتسهيل تمييزه عند اختيار كريم الأساس ومقارنته بالدرجات الأخرى من المجموعة. يحمل هذا المنتج اسم دبل وير ودرجة 1W1، وهما التفصيلان الظاهران في تسمية كريم الأساس. يتيح لك تحديد الدرجة وفق ما تبحثين عنه عند تنسيق مكياج الوجه، مع الرجوع إلى ما يناسبك من خيارات الدرجات المتاحة لديك؛ فالاسم وحده لا يحدد وصفاً لونياً إضافياً للدرجة.يمكن توزيع كريم الأساس على الوجه بالطريقة التي تفضلينها ضمن خطوات المكياج، مع مراعاة تجهيز البشرة بما يلائم روتينك. لا يذكر الاسم حجماً أو تفاصيل عن مستوى التغطية أو اللمسة النهائية، لذلك يقتصر الوصف على العلامة التجارية ونوع المنتج واسمه ودرجة 1W1. يذكر عن هذا المنتج أنه كريم أساس للوجه من استي لودر، ويحمل اسم دبل وير كما ورد في تعريف المنتج، والدرجة المحددة في الاسم هي 1W1.</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4878,7 +4877,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Estée Lauder تقدم من خلال كريم أساس دبل وير 1w2 من استي لودر منتجاً في فئة كريم أساس. يُستخدم بتوزيعه على البشرة النظيفة والمرطبة قبل استكمال باقي خطوات المكياج. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص.</t>
+          <t>كريم أساس دبل وير بدرجة 1W2 من استي لودر — Estée Lauder Double Wear Foundation 1W2؛ مستحضر أساس للوجه من علامة استي لودر، بدرجة 1W2 كما وردت في الاسم. يجمع تعريفه بين اسم دبل وير ورقم الدرجة، لتتمكني من تمييز هذا الخيار عن الدرجات الأخرى عند ترتيب مستحضرات المكياج أو اختيارها. هذا كريم أساس يحمل اسم دبل وير، وتحدد التسمية درجته برقم 1W2. يساعد وضوح الاسم والدرجة على التعرف إلى النسخة المطلوبة عند المقارنة بين خيارات المكياج، مع اختيار الدرجة وفق تفضيلك الشخصي وما تعتمدينه عادةً لمظهر الوجه.يُستخدم ضمن خطوات المكياج ويمكن توزيعه على الوجه بأداة مناسبة. لا يتضمن الاسم حجم العبوة أو وصفاً إضافياً للدرجة أو للنتيجة على البشرة؛ لذا لا تُفترض خصائص أخرى غير المعلومات الواردة. راجعي بيانات العبوة عند الحاجة إلى تفاصيل إضافية عن المنتج وطريقة استخدامه. تشمل خصائصه أن كريم أساس من استي لودر، ويحمل تسمية دبل وير، والدرجة الظاهرة في الاسم هي 1W2. بعد تجهيز البشرة، وزعي كمية مناسبة من كريم الأساس على الوجه باستخدام الأصابع أو أداة المكياج المفضلة.</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4928,7 +4927,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Estée Lauder كريم أساس مزدوج الثبات من ايستية لودر 2دابليو من Estée Lauder، منتج يصنَّف ضمن فئة كريم أساس. يُطبَّق كريم الأساس على الوجه بإسفنجة أو فرشاة مخصصة، ويمكن دمجه بحركات دائرية خفيفة. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم.</t>
+          <t>كريم أساس مزدوج الثبات من استي لودر بدرجة 2W — Estée Lauder Double Wear Foundation 2W؛ مستحضر أساس للوجه من العلامة التجارية استي لودر، والدرجة المذكورة في الاسم هي 2W. يوضح اسم المنتج فئته ونسخته لتسهيل التعرف إليه عند اختيار كريم الأساس أو تنظيم مستحضرات المكياج. يأتي هذا المنتج تحت اسم كريم أساس مزدوج الثبات، مع الإشارة إلى الدرجة 2W في التسمية. يتيح ذلك تحديد الخيار المقصود بالاسم والدرجة عند المقارنة مع مستحضرات أخرى، من دون الحاجة إلى افتراض وصف لوني أو خصائص غير واردة في بيانات المنتج.يمكن إدراجه ضمن مكياج الوجه وتوزيعه بالطريقة التي تفضلينها بعد تهيئة البشرة. لا يذكر الاسم حجماً للعبوة، كما لا يورد تفاصيل عن مستوى التغطية أو اللمسة النهائية؛ لذا يظل التعريف مقتصراً على كونه كريم أساس من استي لودر بدرجة 2W. يتميز المنتج بأن مستحضر كريم أساس للوجه، ومن علامة استي لودر، ويحمل وصف مزدوج الثبات في الاسم. ضعي كمية مناسبة على الوجه بعد تجهيز البشرة، ثم وزعيها بالتساوي باستخدام أصابعك أو أداة مكياج مناسبة.</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4978,7 +4977,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>يقدَّم ارم اند هامر اسنشيالز مزيل عرق النظافه 71 جم كأحد منتجات Arm &amp; Hammer في فئة مزيل عرق. الحجم المدوَّن على العبوة هو 71 جم. يُطبَّق المنتج مباشرة بعد الاستحمام على المنطقة المستهدفة مع تركه حتى يجف قبل ارتداء الملابس. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم.</t>
+          <t>مزيل عرق إسنشيالز برائحة النظافة من ارم اند هامر، 71 جم — Arm &amp; Hammer Essentials Deodorant Clean, 71 g؛ مزيل عرق من علامة ارم اند هامر، بحجم 71 جم، ويشير الاسم إلى رائحة النظافة. يقدّم المنتج تعريفاً مباشراً بنوعه ورائحته وحجم العبوة، ليسهل تمييزه ضمن مستحضرات العناية الشخصية. ينتمي هذا المنتج إلى فئة مزيلات العرق، ويحمل اسم إسنشيالز مع وصف رائحة النظافة كما ورد في التسمية. تأتي العبوة بحجم 71 جم، وهو تفصيل عملي عند التعرف إلى المنتج أو تمييزه عن أحجام أخرى. لا يذكر الاسم نوعاً آخر من الحماية أو خصائص إضافية، لذلك يقتصر وصفه على هويته ورائحته وحجمه.يمكن إدراجه ضمن روتين العناية الشخصية اليومي وفق الطريقة الموضحة على العبوة. اختيار المنتج يعتمد على تفضيلك لرائحة النظافة وعلى شكل المستحضر المناسب لك؛ ويُرجى الرجوع إلى بيانات العبوة لمعرفة تعليمات الاستخدام الخاصة به. من أبرز خصائصه أن مزيل عرق من علامة ارم اند هامر، ويحمل اسم إسنشيالز، ويرد وصف رائحة النظافة ضمن اسم المنتج. استخدميه وفق التعليمات المكتوبة على العبوة وعلى بشرة نظيفة وجافة إذا كانت الإرشادات تسمح بذلك.</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5028,7 +5027,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>مزيل عرق Arm &amp; Hammer المعروف باسم Arm &amp; Hammer مزيل العرق برائحة الروزماري واللافندر 71 جم، وهو منتج موجه لهذه الفئة من العناية. تبلغ سعة العبوة 71 جم كما هو موضح على المنتج. يُستخدم بتمريره على منطقة الإبط النظيفة والجافة، ويمكن إدراجه ضمن روتين العناية الشخصية اليومي. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه.</t>
+          <t>مزيل العرق من ارم اند هامر برائحة الروزماري واللافندر، 71 جم — Arm &amp; Hammer Rosemary Lavender Deodorant, 71 g؛ مزيل عرق للعناية الشخصية من علامة ارم اند هامر، بحجم 71 جم، ويذكر الاسم رائحتي الروزماري واللافندر. يجمع تعريفه بين العلامة التجارية ونوع المستحضر والرائحة والحجم في صياغة واضحة. يُعرَف هذا المنتج بوصفه مزيل عرق يحمل رائحة الروزماري واللافندر، وفق ما ورد في اسمه، وتبلغ كمية العبوة 71 جم. تمنحك هذه التفاصيل طريقة مباشرة للتمييز بينه وبين المنتجات ذات الروائح أو الأحجام الأخرى، من غير إضافة وصف لمكونات أو خصائص لم ترد في التسمية.يناسب إدراجه ضمن خطوات العناية الشخصية بالطريقة الموضحة على العبوة. اختاريه إذا كان وصف الرائحة المذكور قريباً من تفضيلك، وراجعي بيانات المنتج لمعرفة إرشادات الاستخدام الدقيقة. لا يذكر الاسم أنه مانع للتعرق، لذا يُعرّف هنا بمزيل عرق فقط. يذكر عن هذا المنتج أنه مزيل عرق من ارم اند هامر، ويذكر الاسم رائحة الروزماري واللافندر، وحجم العبوة 71 جم. اتبعي طريقة الاستخدام المدونة على العبوة.</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5078,7 +5077,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>من تشكيلة Arm &amp; Hammer، يأتي Arm &amp; Hammer مزيل مانع للتعرق الترا ماكس من ارم اندهامر28غ ضمن تصنيف مزيل عرق. يُطرح المنتج بحجم 28 غ فقط. يُطبَّق المنتج مباشرة بعد الاستحمام على المنطقة المستهدفة مع تركه حتى يجف قبل ارتداء الملابس. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال.</t>
+          <t>مزيل مانع للتعرق ألترا ماكس من ارم اند هامر، 28 جم — Arm &amp; Hammer Ultra Max Antiperspirant, 28 g؛ مستحضر للعناية الشخصية من علامة ارم اند هامر، بحجم 28 جم، ويحمل اسم ألترا ماكس. يعرّف الاسم المنتج بصفته مانعاً للتعرق، ويميزه عن مزيلات العرق التي لا يرد فيها هذا الوصف. يجمع المنتج بين وصف مانع التعرق واسم ألترا ماكس، ويأتي في عبوة محددة بحجم 28 جم. تبرز هذه المعلومات الأساسية لمن يرغب في تحديد نوع المستحضر وحجمه قبل إدراجه ضمن مستلزمات العناية الشخصية. لا يورد الاسم رائحة أو صيغة تطبيق محددة، لذلك لا تُضاف تفاصيل غير واردة في التسمية.يمكن استخدامه وفق الإرشادات المدونة على العبوة، مع الانتباه إلى طريقة التطبيق المناسبة للمنتج. يظل اختيار هذا المستحضر مرتبطاً بتفضيلك لفئة موانع التعرق واسم ألترا ماكس، بينما يوضح الحجم مقدار العبوة المذكور للمنتج. تشمل خصائصه أن مانع تعرّق من علامة ارم اند هامر، ويحمل اسم ألترا ماكس، وحجم العبوة المذكور 28 جم. راجعي تعليمات العبوة قبل الاستخدام، ثم طبقي المنتج على المنطقة المحددة بالطريقة والوقت الواردين فيها.</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5128,7 +5127,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>يندرج Arm &amp; Hammer مزيل مانع للتعرق الترا ماكس للنساء 28غ الصادر عن Arm &amp; Hammer ضمن منتجات مزيل عرق. يأتي بحجم 28 غ، وهو الحجم المذكور على العبوة دون غيره. يُستخدم بتمريره على منطقة الإبط النظيفة والجافة، ويمكن إدراجه ضمن روتين العناية الشخصية اليومي. يُفضَّل تجربة المنتج على مساحة صغيرة من الجلد قبل الاستخدام الكامل لمن تحسس بشرتهم. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف.</t>
+          <t>مزيل مانع للتعرق ألترا ماكس للنساء من ارم اند هامر، 28 جم — Arm &amp; Hammer Ultra Max Antiperspirant for Women, 28 g؛ مستحضر عناية شخصية موصوف للنساء، من علامة ارم اند هامر، بحجم 28 جم. يجمع الاسم بين فئة المنتج واسم ألترا ماكس والفئة المذكورة والحجم، لتكون معلوماته الأساسية واضحة عند الاختيار. هذا المنتج من فئة موانع التعرق، ويحمل اسم ألترا ماكس ويُذكر في تسميته أنه مخصص للنساء. حجم العبوة هو 28 جم، ما يتيح تمييزه من حيث الكمية إلى جانب اسم العلامة التجارية والفئة. ولا يذكر الاسم رائحة أو تفاصيل تركيب أو صيغة استخدام بعينها.يمكن إدراجه ضمن روتين العناية الشخصية بحسب التعليمات المدونة على العبوة. عند اختيار المنتج، راجعي طريقة استعماله والبيانات المرفقة به، واستخدميه وفق ما توضحه الشركة. يقتصر هذا التعريف على تفاصيل الاسم والنوع والحجم دون إضافة ادعاءات أو مواصفات غير متاحة. يتميز المنتج بأن مانع تعرّق من ارم اند هامر، ويحمل اسم ألترا ماكس، وموصوف في الاسم بأنه للنساء. اتبعي الإرشادات الموضحة على العبوة، وطبقي المنتج بالطريقة المحددة فيها.</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5178,7 +5177,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Arm &amp; Hammer تقدم من خلال ارم اند هامر الترا ماكس مزيل عرق ستيك غير معط منتجاً في فئة مزيل عرق. يُطبَّق المنتج مباشرة بعد الاستحمام على المنطقة المستهدفة مع تركه حتى يجف قبل ارتداء الملابس. يمكن إدراج هذا المنتج ضمن روتين العناية الشخصية اليومي أو الأسبوعي حسب نوعه. يُستخدم خارجياً فقط، ويُحفظ بعيداً عن متناول الأطفال. يُفضَّل اتباع تعليمات الاستخدام المطبوعة على العبوة، ويُحفظ المنتج في مكان بارد وجاف. يُراعى إغلاق العبوة جيداً بعد كل استخدام وحفظها بعيداً عن متناول الأطفال. عند ظهور أي تحسس يُفضَّل التوقف عن الاستخدام ومراجعة مختص.</t>
+          <t>مزيل عرق ستيك ألترا ماكس غير معطر من ارم اند هامر — Arm &amp; Hammer Ultra Max Unscented Deodorant Stick؛ مستحضر للعناية الشخصية بصيغة ستيك، وتوضح التسمية أنه غير معطر. يحمل المنتج اسم ألترا ماكس من علامة ارم اند هامر، ولا يرد حجم للعبوة في الاسم المتاح. يأتي هذا الخيار بصيغة ستيك، ويُعرَف بأنه مزيل عرق غير معطر وفق الوصف الوارد في الاسم. وتظهر علامة ارم اند هامر واسم ألترا ماكس ضمن هويته، ما يساعد على تحديد المنتج عند مقارنته بمزيلات العرق الأخرى. لا يتضمن الاسم حجم العبوة، لذلك لا تُضاف كمية غير مذكورة.يمكن إدراجه ضمن روتين العناية الشخصية بالطريقة الموضحة على العبوة. ويمنح وصف غير معطر معلومة مباشرة عن الرائحة كما وردت في التسمية، من دون افتراض وجود رائحة أخرى. تحققي من الإرشادات المرفقة لتحديد كيفية التطبيق والموضع المناسب للاستخدام. من أبرز خصائصه أن مزيل عرق بصيغة ستيك، ويحمل اسم ألترا ماكس من ارم اند هامر، وموصوف بأنه غير معطر. راجعي تعليمات العبوة قبل التطبيق، ثم مرري ستيك مزيل العرق على المنطقة المحددة بالطريقة الواردة فيها. استخدميه وفق الإرشادات وأغلقي الغطاء بعد الانتهاء.</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5264,7 +5263,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>تسوق مرطب شفاه Palmer's لترطيب الشفاه الجافة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تسوق الآن من منتنيرو فعلاً بالفعل.</t>
+          <t>تسوق بالمرز مرطب ستيك للشفاه بزبدة الكاكاو - 14جرا من Palmer's، مرطب مخصص للشفاه ضمن تشكيلة مرطب الشفاه في السعودية، يأتي بصيغة ستيك سهلة التطبيق.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -5286,7 +5285,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>اكتشف شامبو Priorin 200 مل للعناية اليومية بالشعر، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اكتشف التفاصيل كاملة الآن.</t>
+          <t>اكتشف شامبو بريورين للشعر الضعيف والمتساقط 200 مل من منتنيرو، شامبو مخصص لتنظيف الشعر ضمن تشكيلة العناية بالشعر في السعودية، يشير الاسم إلى الشعر الضعيف.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -5308,7 +5307,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>تصفح ماسكارا Maybelline New York لإطلالة عيون مميزة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تصفح المزيد وتسوقي اليوم.</t>
+          <t>تصفح ماسكارا مايلبين جلام بلاك من Maybelline New York، ماسكارا مخصصة للرموش ضمن تشكيلة ماسكارا في السعودية، تحمل اسم جلام بلاك تصفحي المزيد.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -5325,12 +5324,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ماسكارا Maybelline New York 2</t>
+          <t>ماسكارا Maybelline مقاومة للماء</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>اطلب ماسكارا Maybelline New York لإطلالة عيون مميزة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اطلبه الآن بسهولة فعلاً.</t>
+          <t>اطلب الآن ماسكارا مايبيلين دبليو بي من Maybelline New York، ماسكارا مخصصة للرموش ضمن تشكيلة ماسكارا في السعودية، من علامة مايبيلين اطلبيه اليوم.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -5347,12 +5346,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ماسكارا Maybelline New York 3</t>
+          <t>ماسكارا Maybelline سوداء كلاسيكية</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>تسوق ماسكارا Maybelline New York لإطلالة عيون مميزة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تسوق الآن من منتنيرو فعلاً.</t>
+          <t>اكتشف ماسكارا مايبيلين السوداء من Maybelline New York، ماسكارا رموش بدرجة سوداء كلاسيكية ضمن تشكيلة ماسكارا في السعودية، تسوقي اليوم بسهولة.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5374,7 +5373,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>اكتشف كونسيلر Maybelline New York لتغطية خفيفة ومظهر متجانس للبشرة، متوفر أونلاين في السعودية. اكتشف التفاصيل كاملة الآن، وهو منتج من فئة كونسيلر.</t>
+          <t>جرّبي كونسيلر مايبيلين فيت مي رقم 10 من Maybelline New York، كونسيلر مخصص للاستخدام على الوجه ضمن تشكيلة كريمات الإخفاء والتصحيح في السعودية.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -5396,7 +5395,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>تصفح كونسيلر Maybelline New York لتغطية خفيفة ومظهر متجانس للبشرة، متوفر أونلاين في السعودية. تصفح المزيد وتسوقي اليوم، وهو منتج من فئة كونسيلر.</t>
+          <t>تسوق كونسيلر مايبيلين فيت مي رقم 15 من Maybelline New York، مستحضر كونسيلر للوجه ضمن تشكيلة كريمات الإخفاء والتصحيح في السعودية، من خط فيت مي من مايبيلين.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -5418,7 +5417,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>اطلب كونسيلر Maybelline New York لتغطية خفيفة ومظهر متجانس للبشرة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اطلبه الآن بسهولة.</t>
+          <t>اكتشف كونسيلر مايبيلين فيت مي رقم 20 من Maybelline New York، كونسيلر مخصص للوجه ضمن تشكيلة كريمات الإخفاء والتصحيح في السعودية، يحمل تسمية فيت مي من.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -5440,7 +5439,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>تسوق كونسيلر Maybelline New York لتغطية خفيفة ومظهر متجانس للبشرة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تسوق الآن من منتنيرو.</t>
+          <t>تصفح كونسيلر خافي عيوب فيت مي من ميبلين 30 من Maybelline New York، كونسيلر خافي عيوب للوجه ضمن تشكيلة كريمات الإخفاء والتصحيح في السعودية، يحمل اسم فيت مي.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -5457,12 +5456,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ماسكارا Maybelline New York 4</t>
+          <t>ماسكارا Maybelline سموكي آيز</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>اكتشف ماسكارا Maybelline New York لإطلالة عيون مميزة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اكتشف التفاصيل كاملة الآن.</t>
+          <t>اطلب الآن ماسكارا مايبيلين سموكي من Maybelline New York، ماسكارا مخصصة للرموش ضمن تشكيلة ماسكارا في السعودية، من علامة مايبيلين اكتشفي التفاصيل.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -5484,7 +5483,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>تصفح ماسكارا Maybelline New York 10 مل لإطلالة عيون مميزة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تصفح المزيد وتسوقي اليوم.</t>
+          <t>اطلعي على Maybelline مايبيلين ماسكارا لاش سينسيشينال فايرورك 10 مل من Maybelline New York، مستحضر مخصص لمكياج الرموش ضمن تشكيلة ماسكارا في السعودية.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -5501,12 +5500,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ماسكارا Maybelline New York 5</t>
+          <t>ماسكارا Maybelline سكاي هاي برغندي</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>اطلب ماسكارا Maybelline New York لإطلالة عيون مميزة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اطلبه الآن بسهولة فعلاً (2).</t>
+          <t>جرّبي مسكرة رموش ميبلين سكاي هاي برغندي من Maybelline New York، ماسكارا مخصصة لمكياج الرموش ضمن تشكيلة ماسكارا في السعودية، تحمل اسم مجموعة Sky High.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5528,7 +5527,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>تسوق أحمر شفاه Maybelline New York 4.2 مل للون شفاه يدوم طويلاً، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تسوق الآن من منتنيرو.</t>
+          <t>تسوق ميبيلين احمر شفاه سوبر ستاي - 105 جولدن 4.2مل من Maybelline New York، أحمر شفاه مخصص لتلوين الشفاه ضمن تشكيلة أحمر الشفاه في السعودية تسوقي الآن.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -5550,7 +5549,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>اكتشف أحمر شفاه Maybelline New York للون شفاه يدوم طويلاً، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اكتشف التفاصيل كاملة الآن.</t>
+          <t>اكتشف روج سائل سوبر ستاي إكسترا من ميبيلين - 130 من Maybelline New York، أحمر شفاه سائل لمكياج الشفاه ضمن تشكيلة أحمر الشفاه في السعودية، يحمل اسم Super.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5572,7 +5571,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>تصفح أحمر شفاه Maybelline New York للون شفاه يدوم طويلاً، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تصفح المزيد وتسوقي اليوم.</t>
+          <t>تصفح ميبيلين احمر شفاه سائل فينيل انك 20 من Maybelline New York، مستحضر شفاه بصيغة سائلة ضمن تشكيلة أحمر الشفاه في السعودية، يحمل اسم Vinyl Ink.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5594,7 +5593,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>اطلب أحمر شفاه Maybelline New York للون شفاه يدوم طويلاً، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اطلبه الآن بسهولة.</t>
+          <t>اطلب الآن Maybelline أحمر شفاه سوبر ستاي فينيل إنك 40 ويتي من Maybelline New York، أحمر شفاه سائل مخصص للشفاه ضمن تشكيلة أحمر الشفاه في السعودية.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5611,12 +5610,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ماسكارا Maybelline New York 6</t>
+          <t>ماسكارا Maybelline سكاي هاي سينسيشنال</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>تسوق ماسكارا Maybelline New York لإطلالة عيون مميزة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تسوق الآن من منتنيرو فعلاً (2).</t>
+          <t>تصفح ماسكارا مايبلين نيويورك سينسيشينال سكاي هاي من Maybelline New York ضمن تشكيلة ماسكارا في السعودية، نسخة قابلة للغسل، اكتشفي التفاصيل الآن.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5633,12 +5632,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ماسكارا Maybelline New York 7</t>
+          <t>ماسكارا Maybelline سكاي هاي ترو بلاك</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>اكتشف ماسكارا Maybelline New York لإطلالة عيون مميزة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اكتشف التفاصيل كاملة الآن (2).</t>
+          <t>جرّبي ماسكارا مايبيلين لاش سكاي هاي ترو من Maybelline New York، ماسكارا مخصصة للرموش ضمن تشكيلة ماسكارا في السعودية، يحمل الاسم عبارة Sky High True.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5660,7 +5659,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>تصفح أحمر شفاه Maybelline New York للون شفاه يدوم طويلاً، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تصفح المزيد وتسوقي اليوم (2).</t>
+          <t>تسوق ميبيلين احمر شفاه سائل سوبر ستاي 25 ريد هوت من Maybelline New York، أحمر شفاه سائل لمكياج الشفاه ضمن تشكيلة أحمر الشفاه في السعودية، يحمل اسم Super.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -5682,7 +5681,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>اطلب أحمر شفاه Maybelline New York للون شفاه يدوم طويلاً، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اطلبه الآن بسهولة (2).</t>
+          <t>اكتشف روج ميبلين سوبر ستاي 45 Capricious من Maybelline New York، أحمر شفاه مخصص لمكياج الشفاه ضمن تشكيلة أحمر الشفاه في السعودية، يحمل اسم Super Stay.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -5704,7 +5703,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>تسوق ماسكارا L'Oréal Paris لإطلالة عيون مميزة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تسوق الآن من منتنيرو فعلاً بالفعل.</t>
+          <t>تصفح مسكرة رموش لوريال بانورامار الذهبية من L'Oréal Paris، مستحضر مخصص لتطبيقه على الرموش ضمن تشكيلة ماسكارا في السعودية، تنتمي إلى مجموعة بانوراما من.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -5726,7 +5725,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>اكتشف أحمر شفاه Maybelline New York للون شفاه يدوم طويلاً، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اكتشف التفاصيل كاملة الآن (2).</t>
+          <t>اطلب الآن Maybelline روج سائل سوبر ستاي انرايفلد من ميبيلين - 30 من Maybelline New York، أحمر شفاه سائل مخصص لمكياج الشفاه ضمن تشكيلة أحمر الشفاه في.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -5748,7 +5747,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>تصفح أحمر شفاه Maybelline New York للون شفاه يدوم طويلاً، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تصفح المزيد وتسوقي اليوم (3).</t>
+          <t>اطلعي على أحمر شفاه سائل سوبر ستاي من ميبلين -ويكد 50 - من Maybelline New York، مخصص لتلوين الشفاه ضمن روتين المكياج ضمن تشكيلة أحمر الشفاه في السعودية.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5765,12 +5764,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ماسكارا Maybelline New York 8</t>
+          <t>ماسكارا Maybelline لاش سينسيشنال الأساسية</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>اطلب ماسكارا Maybelline New York لإطلالة عيون مميزة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اطلبه الآن بسهولة فعلاً (3).</t>
+          <t>جرّبي Maybelline ماسكارا مايبيلين لاش سينسيشنال سكاي هاي، من Maybelline New York، ماسكارا مخصصة لتطبيقها على الرموش ضمن تشكيلة ماسكارا في السعودية.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5787,12 +5786,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ماسكارا Maybelline New York 9</t>
+          <t>برايمر رموش Maybelline سكاي هاي</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>تسوق ماسكارا Maybelline New York لإطلالة عيون مميزة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تسوق الآن من منتنيرو فعلاً (3).</t>
+          <t>تسوق Maybelline برايمر رموش لاش سينسيشنال سكاي هاي من مايبيلي من Maybelline New York، برايمر مخصص للرموش وفقاً لاسم المنتج ضمن تشكيلة ماسكارا في السعودية.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5814,7 +5813,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>اكتشف أحمر شفاه Maybelline New York للون شفاه يدوم طويلاً، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اكتشف التفاصيل كاملة الآن (3).</t>
+          <t>اكتشف Maybelline روج سائل سوبر ستاي من ميبيلين - 110 من Maybelline New York، مستحضر مكياج مخصص للشفاه ضمن تشكيلة أحمر الشفاه في السعودية، يأتي بصيغة أحمر.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5836,7 +5835,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>تصفح ماسكارا Maybelline New York لإطلالة عيون مميزة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تصفح المزيد وتسوقي اليوم (2).</t>
+          <t>تصفح ميبلين لاش سينسيشنال سكاي هاي ماسكرا مقاومة م من Maybelline New York، ماسكارا مخصصة للرموش بحسب الاسم الوارد ضمن تشكيلة ماسكارا في السعودية.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5858,7 +5857,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>اطلب كونسيلر Maybelline New York لتغطية خفيفة ومظهر متجانس للبشرة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اطلبه الآن بسهولة (2).</t>
+          <t>اطلب الآن ميبلين نيويورك كونسيلر فيت مي 40 كراميل من Maybelline New York، خافي عيوب للوجه من ميبلين ضمن تشكيلة كريمات الإخفاء والتصحيح في السعودية.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5875,12 +5874,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>كونسيلر Maybelline New York 5</t>
+          <t>كونسيلر Maybelline فيت مي رقم 5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>تسوق كونسيلر Maybelline New York لتغطية خفيفة ومظهر متجانس للبشرة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تسوق الآن من منتنيرو (2)</t>
+          <t>اطلعي على Maybelline خافي عيوب مايبيلين فيت مي رقم 5 من Maybelline New York، خافي عيوب مخصص لمكياج الوجه ضمن تشكيلة كريمات الإخفاء والتصحيح في السعودية.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5902,7 +5901,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>اكتشف أحمر شفاه Maybelline New York للون شفاه يدوم طويلاً، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اكتشف التفاصيل كاملة الآن (4).</t>
+          <t>جرّبي ميبلين سوبر ستاي فينيلينك - 150 STRIKING من Maybelline New York، أحمر شفاه سائل من مجموعة سوبر ستاي ضمن تشكيلة أحمر الشفاه في السعودية.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5924,7 +5923,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>تصفح أحمر شفاه Maybelline New York للون شفاه يدوم طويلاً، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تصفح المزيد وتسوقي اليوم (4).</t>
+          <t>تسوق ميبلين سوبر ستاي فينيلينك - 165 EDGY من Maybelline New York، من مجموعة Super Stay Vinyl Ink من Maybelline ضمن تشكيلة أحمر الشفاه في السعودية.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5946,7 +5945,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>اطلب أحمر شفاه Maybelline New York للون شفاه يدوم طويلاً، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اطلبه الآن بسهولة (3).</t>
+          <t>اكتشف أحمر شفاه مايبيلين سوبر ستاي فينيل إنك 170 من Maybelline New York، أحمر شفاه من مجموعة Super Stay Vinyl Ink ضمن تشكيلة أحمر الشفاه في السعودية.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5968,7 +5967,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>تسوق ماسكارا Maybelline New York لإطلالة عيون مميزة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تسوق الآن من منتنيرو فعلاً (4).</t>
+          <t>تصفح Maybelline ميبيلين لاش سينسيشنال سكاي هاي ماسكرا اسود من Maybelline New York، ماسكارا للعين من مجموعة Lash Sensational Sky High ضمن تشكيلة ماسكارا في.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5990,7 +5989,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>اكتشف كونسيلر L'Oréal Paris لتغطية خفيفة ومظهر متجانس للبشرة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اكتشف التفاصيل كاملة الآن.</t>
+          <t>اطلب الآن كونسيلر لوريال انفيلابل 322 من L'Oréal Paris، كونسيلر للوجه من مجموعة Infallible ضمن تشكيلة كريمات الإخفاء والتصحيح في السعودية، يحمل رقم الدرجة.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -6012,7 +6011,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>تصفح كونسيلر L'Oréal Paris لتغطية خفيفة ومظهر متجانس للبشرة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تصفح المزيد وتسوقي اليوم.</t>
+          <t>اطلعي على كونسلر لوريال انفيلابل 324 من L'Oréal Paris، مستحضر كونسيلر مخصص للوجه ضمن تشكيلة كريمات الإخفاء والتصحيح في السعودية تصفحي المزيد.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6034,7 +6033,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>اطلب كونسيلر L'Oréal Paris لتغطية خفيفة ومظهر متجانس للبشرة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اطلبه الآن بسهولة.</t>
+          <t>جرّبي كونسلر لوريال انفيلابل 330 من L'Oréal Paris، كونسيلر للوجه من مجموعة Infallible ضمن تشكيلة كريمات الإخفاء والتصحيح في السعودية اطلبيه اليوم.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6051,12 +6050,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ماسكارا Maybelline New York 7 2</t>
+          <t>ماسكارا Maybelline سكاي هاي سبيس دايموند</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>تسوق ماسكارا Maybelline New York 7.2 مل لإطلالة عيون مميزة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تسوق الآن من منتنيرو.</t>
+          <t>تسوق Maybelline ماسكارا سكاي هاي سبيس دايموند، 7.2 مل من Maybelline New York، ماسكارا مخصصة للرموش ضمن تشكيلة ماسكارا في السعودية، تحمل اسم Sky High Space.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6078,7 +6077,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>اكتشف ماسكارا Maybelline New York لإطلالة عيون مميزة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اكتشف التفاصيل كاملة الآن (3).</t>
+          <t>اكتشف مايبيلين نيويورك ماسكارا سكاي هاي ارتفاع أخضر من Maybelline New York، ماسكارا للرموش من مجموعة Sky High ضمن تشكيلة ماسكارا في السعودية.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6100,7 +6099,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>تصفح كريم للشعر Wella 60 مل للعناية بالشعر وترطيبه، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تصفح المزيد وتسوقي اليوم.</t>
+          <t>اطلب الآن ويلا ويلكسون أوكسجين 6% بحجم 60 مل من Wella، مثبت أكسجيني للشعر بتركيز 6% ضمن تشكيلة العناية بالشعر في السعودية، اطلبيه اليوم بسهولة.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6122,7 +6121,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>اطلب مرطب شفاه Vaseline 20 جم لترطيب الشفاه الجافة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اطلبه الآن بسهولة فعلاً.</t>
+          <t>جرّبي مرطب ومورد للشفاه من فازلين 20 جم من Vaseline، مرطب شفاه بصيغة معدنية ولمسة وردية ضمن تشكيلة مرطب الشفاه في السعودية، اكتشفي أكثر الآن.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6144,7 +6143,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>تسوق مطهر ومعقم Dettol 250 مل للتعقيم وروتين النظافة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تسوق الآن من منتنيرو فعلاً.</t>
+          <t>اطلعي على مطهر ومعقم للجراثيم ديتول 250مل من منتنيرو، منتج موصوف بأنه مطهر ومعقم للجراثيم ضمن تشكيلة العناية الشخصية في السعودية، يحمل علامة ديتول.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6166,7 +6165,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>اكتشف كريم أساس Max Factor لمظهر بشرة متجانس، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اكتشف التفاصيل كاملة الآن فعلاً.</t>
+          <t>جرّبي كريم أساس بيرفورمنس 102 باستيل من ماكس فاكتور من Max Factor، كريم أساس من علامة ماكس فاكتور ضمن تشكيلة أساس وبرايمر في السعودية اكتشفي التفاصيل.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6188,7 +6187,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>تصفح كريم أساس Max Factor لمظهر بشرة متجانس، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تصفح المزيد وتسوقي اليوم فعلاً.</t>
+          <t>تسوق كريم اساس سائل من ماكس فاكتر- 101 من Max Factor، كريم أساس بصيغة سائلة حسب اسمه ضمن تشكيلة أساس وبرايمر في السعودية، يحمل علامة ماكس فاكتور التجارية.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6210,7 +6209,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>اطلب كريم أساس Max Factor لمظهر بشرة متجانس، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اطلبه الآن بسهولة، وهو منتج من فئة كريم أساس.</t>
+          <t>اكتشف ماكس فاكتور كريم أساس 100 فير من Max Factor، كريم أساس يحمل علامة ماكس فاكتور ضمن تشكيلة أساس وبرايمر في السعودية، رقم الدرجة المذكور هو 100.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6232,7 +6231,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>تسوق مزيل عرق Rexona 50 مل للعناية اليومية بمنطقة الإبط، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تسوق الآن من منتنيرو.</t>
+          <t>تصفح ريكسونا-مزيل عرق رول أون-50 مل--يعمل للملابس من Rexona، مزيل عرق يحمل علامة ريكسونا ضمن تشكيلة العناية الشخصية في السعودية، يأتي بصيغة رول أون حسب.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6249,12 +6248,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>مزيل عرق Rexona 50 مل 2</t>
+          <t>مزيل عرق Rexona ألوفيرا 50 مل</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>اكتشف مزيل عرق Rexona 50 مل للعناية اليومية بمنطقة الإبط، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اكتشف التفاصيل كاملة الآن.</t>
+          <t>اطلب الآن ريكسونا - مزيل عرق رول أون 50مل الالو فيرا من Rexona، مزيل عرق من علامة ريكسونا ضمن تشكيلة العناية الشخصية في السعودية، يأتي بصيغة رول أون.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6276,7 +6275,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>تصفح مزيل عرق Dove 50 مل للعناية اليومية بمنطقة الإبط، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تصفح المزيد وتسوقي اليوم.</t>
+          <t>اكتشف دوف ديو عصا أوريجينال 50 مل من Dove، مزيل عرق بصيغة عصا صلبة للاستخدام اليومي ضمن تشكيلة العناية الشخصية في السعودية، تسوقي من متجرنا الآن.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6298,7 +6297,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>اطلب مزيل عرق QV للعناية اليومية بمنطقة الإبط، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اطلبه الآن بسهولة، وهو منتج من فئة مزيل عرق.</t>
+          <t>جرّبي رول مضاد للتعرق من كيوفي - 80ج من QV، مضاد تعرق يحمل علامة كيوفي ضمن تشكيلة العناية الشخصية في السعودية، يأتي بصيغة رول حسب الاسم اطلبيه اليوم.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6320,7 +6319,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>تسوق مزيل عرق QV 80 جم للعناية اليومية بمنطقة الإبط، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تسوق الآن من منتنيرو فعلاً.</t>
+          <t>تسوق كيوفي رول للعرق 80 جم من QV، رول للعرق من علامة كيوفي ضمن تشكيلة العناية الشخصية في السعودية، الكمية المذكورة في الاسم 80 جم تسوقي الآن.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6342,7 +6341,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>اكتشف كونسيلر Anastasia Beverly Hills لتغطية خفيفة ومظهر متجانس للبشرة، متوفر أونلاين في السعودية. اكتشف التفاصيل كاملة الآن، وهو منتج من فئة كونسيلر.</t>
+          <t>اكتشف كونسيلر أناستازيا 2 من Anastasia Beverly Hills، كونسيلر يحمل علامة أناستازيا ضمن تشكيلة كريمات الإخفاء والتصحيح في السعودية، رقم الدرجة المذكور هو 2.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6364,7 +6363,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>تصفح منتج عناية St. Ives ضمن روتين العناية الشخصية، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تصفح المزيد وتسوقي اليوم.</t>
+          <t>تصفح St. Ives مرطب الكولاجين والايلاستين المجدد من سانت اي من منتنيرو، مرطب يحمل اسم St. Ives ضمن تشكيلة مرطبات في السعودية تصفحي المزيد اطلبيه بسهولة.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6386,7 +6385,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>اطلب مرطب شفاه لترطيب الشفاه الجافة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اطلبه الآن بسهولة، وهو منتج من فئة مرطب شفاه.</t>
+          <t>اطلب الآن فورميولا ليب بالم يرطب الشفاه الجافة 15 من منتنيرو، بلسم شفاه من علامة Formula ضمن تشكيلة مرطب الشفاه في السعودية، يوضح الاسم أنه مخصص للشفاه.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6408,7 +6407,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>تسوق مرطب شفاه Palmer's لترطيب الشفاه الجافة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تسوق الآن من منتنيرو فعلاً بالفعل (2).</t>
+          <t>اطلعي على كريم تصفيف الشعر بزيت الزيتون من بالمرز 150 ج من Palmer's، كريم مخصص لتصفيف الشعر وفق الاسم ضمن تشكيلة العناية بالشعر في السعودية.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6430,7 +6429,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>اكتشف مرطب شفاه Palmer's 4 جرام لترطيب الشفاه الجافة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اكتشف التفاصيل كاملة الآن.</t>
+          <t>جرّبي بالمرز مرطب الشفاه بخلاصة جوز الهند 4 جرام من Palmer's، مرطب شفاه يحمل علامة Palmer's ضمن تشكيلة مرطب الشفاه في السعودية، يذكر خلاصة جوز الهند ضمن.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6452,7 +6451,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>تصفح مرطب شفاه Palmer's 100 جم لترطيب الشفاه الجافة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تصفح المزيد وتسوقي اليوم.</t>
+          <t>تسوق بالمرز كريم زبدة الكاكاو 100 جم من Palmer's، كريم يحمل علامة Palmer's ضمن تشكيلة العناية بالجسم في السعودية، يذكر زبدة الكاكاو في اسم المنتج.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6474,7 +6473,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>اطلب مرطب شفاه Palmer's 200 جرام لترطيب الشفاه الجافة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اطلبه الآن بسهولة فعلاً.</t>
+          <t>اكتشف بالمرز كريم زبدة كاكاو 200 جرام من Palmer's، كريم مخصص للعناية ببشرة الجسم ضمن تشكيلة العناية بالجسم في السعودية، يحمل اسم زبدة الكاكاو ضمن تعريف.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -6496,7 +6495,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>تسوق مرطب شفاه Palmer's 125 جم لترطيب الشفاه الجافة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تسوق الآن من منتنيرو فعلاً.</t>
+          <t>تصفح كريم بالمرز لعلامات تمدد الجلد 125جم من Palmer's، كريم للعناية ببشرة الجسم ضمن تشكيلة العناية بالجسم في السعودية، يرتبط اسمه بعلامات تمدد الجلد.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -6518,7 +6517,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>اكتشف مرطب شفاه Palmer's 30 جرام لترطيب الشفاه الجافة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اكتشف التفاصيل كاملة الآن.</t>
+          <t>اطلب الآن بالمرز كريم رضاعة مع زبدة الكاكاو 30 جرام من Palmer's، كريم عناية مرتبط بالرضاعة بحسب الاسم ضمن تشكيلة العناية بالجسم في السعودية.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -6540,7 +6539,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>تصفح مرطب شفاه Palmer's 125 جرام لترطيب الشفاه الجافة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تصفح المزيد وتسوقي اليوم.</t>
+          <t>اطلعي على بالمرز كريم الصدر 125 جرام من Palmer's، كريم عناية للجسم يحمل وصف الصدر في اسمه ضمن تشكيلة العناية بالجسم في السعودية، عبوة بوزن 125 جراماً.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -6557,12 +6556,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>مرطب شفاه Palmer's 125 جرام 2</t>
+          <t>كريم Palmer's لعلامات التمدد 125 جم</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>اطلب مرطب شفاه Palmer's 125 جرام لترطيب الشفاه الجافة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اطلبه الآن بسهولة فعلاً.</t>
+          <t>جرّبي بالمرز لعلامات التمدد 125 جرام من Palmer's، كريم جسم يرتبط اسمه بعلامات التمدد ضمن تشكيلة العناية بالجسم في السعودية، وزن العبوة 125 جراماً.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -6584,7 +6583,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>تسوق مرطب شفاه Palmer's 150 مل لترطيب الشفاه الجافة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تسوق الآن من منتنيرو فعلاً.</t>
+          <t>تسوق بالمرز زيت بزبدة الكاكاو 150 مل من Palmer's، زيت للعناية ببشرة الجسم ضمن تشكيلة العناية بالجسم في السعودية، يتضمن الاسم زبدة الكاكاو تسوقي الآن.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -6606,7 +6605,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>اكتشف مرطب شفاه Palmer's 60 مل لترطيب الشفاه الجافة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اكتشف التفاصيل كاملة الآن.</t>
+          <t>اكتشف بالمرز زيت العناية بالبشرة عطر ثمر الورد 60مل من Palmer's، زيت مخصص للعناية بالبشرة ضمن تشكيلة زيوت وزبدات في السعودية، يذكر الاسم عطر ثمر الورد.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -6628,7 +6627,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>تصفح مرطب شفاه Palmer's 250 مل لترطيب الشفاه الجافة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تصفح المزيد وتسوقي اليوم.</t>
+          <t>تصفح زيت مرطب للجسم من بالمرز 250 مل من Palmer's، زيت موصوف بأنه مرطب للجسم ضمن الاسم ضمن تشكيلة العناية بالجسم في السعودية، عبوة كبيرة نسبياً بحجم 250 مل.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -6645,12 +6644,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>مرطب شفاه Palmer's 150 مل 2</t>
+          <t>زيت جسم Palmer's كاكاو وورد 150 مل</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>اطلب مرطب شفاه Palmer's 150 مل لترطيب الشفاه الجافة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اطلبه الآن بسهولة فعلاً.</t>
+          <t>اطلب الآن بالمرز زيت الجسم بزبدة الكاكو ثمرة الورد150مل من Palmer's، زيت مخصص للعناية بالجسم ضمن تشكيلة العناية بالجسم في السعودية اطلبيه اليوم.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -6672,7 +6671,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>تسوق مرطب شفاه Palmer's 60 جرام لترطيب الشفاه الجافة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تسوق الآن من منتنيرو فعلاً.</t>
+          <t>اطلعي على بالمرز كريم القدمين ماجيك 60 جرام من Palmer's، كريم مخصص للعناية بالقدمين ضمن تشكيلة العناية بالجسم في السعودية، يحمل اسم ماجيك كما ورد في.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6689,12 +6688,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>مرطب شفاه Palmer's 250 مل 2</t>
+          <t>لوشن جسم Palmer's زبدة الشيا 250 مل</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>اكتشف مرطب شفاه Palmer's 250 مل لترطيب الشفاه الجافة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اكتشف التفاصيل كاملة الآن.</t>
+          <t>جرّبي بالمرز لوشن الجسم زبدة الشيا 250 مل من Palmer's، لوشن مخصص للاستخدام على الجسم ضمن تشكيلة العناية بالجسم في السعودية، يحمل اسم زبدة الشيا ضمن وصف.</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6716,7 +6715,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>تصفح مرطب شفاه Palmer's 150 جم لترطيب الشفاه الجافة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تصفح المزيد وتسوقي اليوم.</t>
+          <t>تسوق كريم مغذي للشعر ضد القشره من بالمرز - 150 جم من Palmer's، كريم مخصص للعناية بالشعر ضمن تشكيلة العناية بالشعر في السعودية، يذكر الاسم وصفًا مغذيًا.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6738,7 +6737,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>اطلب مرطب شفاه Palmer's 133 جم لترطيب الشفاه الجافة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اطلبه الآن بسهولة فعلاً.</t>
+          <t>اكتشف بالمرز صابون زبدة الكاكاو مع فيتامين 133 جم من Palmer's، صابون مخصص للاستخدام على الجسم ضمن تشكيلة العناية بالجسم في السعودية اطلبيه اليوم.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6760,7 +6759,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>تسوق مقشر Dove لتقشير البشرة وتنظيفها، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تسوق الآن من منتنيرو، وهو منتج من فئة مقشر.</t>
+          <t>تصفح دوف مقشر جسم بحليب الأرز 298 من Dove، مقشر مخصص للعناية بالجسم ضمن تشكيلة العناية بالجسم في السعودية، يذكر حليب الأرز ضمن اسم المنتج تسوقي الآن.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6782,7 +6781,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>اكتشف مقشر Dove 298 جم لتقشير البشرة وتنظيفها، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اكتشف التفاصيل كاملة الآن فعلاً.</t>
+          <t>اطلب الآن دوف مقشر الجسم بخلاصة بذور الرمان 298 جم من Dove، مقشر مخصص للاستخدام على الجسم ضمن تشكيلة العناية بالجسم في السعودية، يذكر خلاصة بذور الرمان في.</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6799,12 +6798,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>مقشر Dove 298 2</t>
+          <t>مقشر جسم Dove لافندر وجوز الهند</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>تصفح مقشر Dove لتقشير البشرة وتنظيفها، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تصفح المزيد وتسوقي اليوم، وهو منتج من فئة مقشر.</t>
+          <t>اطلعي على مقشر الجسم دوف باللافندر وحليب جوز الهند 298 من Dove، مقشر مخصص للجسم ضمن تشكيلة العناية بالجسم في السعودية، يذكر اللافندر ضمن اسم المنتج.</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6821,12 +6820,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>مقشر Dove 298 جم 2</t>
+          <t>مقشر جسم Dove لوز ومانجو</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>اطلب مقشر Dove 298 جم لتقشير البشرة وتنظيفها، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اطلبه الآن بسهولة، وهو منتج من فئة مقشر.</t>
+          <t>جرّبي دوف مقشر الجسم بزبدة اللوز والمانجو298جم من Dove، مقشر مخصص للعناية بالجسم ضمن تشكيلة العناية بالجسم في السعودية، يذكر زبدة اللوز ضمن اسم المنتج.</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6848,7 +6847,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>تسوق مقشر Dove لتقشير البشرة وتنظيفها، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تسوق الآن من منتنيرو، وهو منتج من فئة مقشر (2).</t>
+          <t>تسوق دوف مقشر الجسم بملح الهيمالايا وزيت الورد425ج من Dove، مخصص لتقشير بشرة الجسم ضمن تشكيلة العناية بالجسم في السعودية تسوقي الآن متوفر الآن.</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6870,7 +6869,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>اكتشف مقشر Dove 425 جم لتقشير البشرة وتنظيفها، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اكتشف التفاصيل كاملة الآن فعلاً.</t>
+          <t>اكتشف دوف, مقشر جسم بالكرز, وحليب الشيا , 425جم من Dove، مقشر مخصص لبشرة الجسم ضمن تشكيلة العناية بالجسم في السعودية، يذكر اسم المنتج الكرز وحليب الشيا.</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6892,7 +6891,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>تصفح معجون أسنان Sensodyne 50 مل لتنظيف الأسنان اليومي، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تصفح المزيد وتسوقي اليوم.</t>
+          <t>تصفح سنسوداين معجون اسنان إنتعاش زائد 50 مل من Sensodyne، معجون أسنان من علامة سنسوداين ضمن تشكيلة العناية الشخصية في السعودية، يحمل اسم انتعاش زائد.</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6914,7 +6913,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>اطلب بودرة Clinique لتثبيت المكياج طوال اليوم، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اطلبه الآن بسهولة، وهو منتج من فئة بودرة.</t>
+          <t>اطلب الآن بودرة كلينيك المضغوطة الشفافة غير اللامعة من Clinique، بودرة مخصصة لمكياج الوجه ضمن تشكيلة بودرة الوجه في السعودية، تركيبة مضغوطة وفق اسم المنتج.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6936,7 +6935,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>تسوق بخاخ Clinique 125 مل ضمن روتين العناية المعتاد، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تسوق الآن من منتنيرو فعلاً.</t>
+          <t>اطلعي على بخاخ مويستشر سيرج للوجه 125 مل - كلينيك من Clinique، بخاخ مخصص للوجه ضمن تشكيلة مرطبات في السعودية، ينتمي إلى مجموعة مويستشر سيرج من كلينيك.</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -6958,7 +6957,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>اكتشف بلسم تنظيف Clinique 125 مل لتنظيف البشرة وإزالة المكياج، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اكتشف التفاصيل كاملة الآن.</t>
+          <t>جرّبي كلينيك بلسم تنظيف تيك ذا داي اوف للجنسين125مل من Clinique، بلسم مخصص لتنظيف الوجه ضمن تشكيلة تنظيف الوجه في السعودية، يحمل اسم تيك ذا داي أوف.</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -6980,7 +6979,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>تصفح جل Clinique 125 مل ضمن روتين العناية المعتاد، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تصفح المزيد وتسوقي اليوم.</t>
+          <t>تسوق كلينيك جل مرطب درامتكلي ديفرنت - 125 مل من Clinique، جل مرطب للوجه من كلينيك ضمن تشكيلة مرطبات في السعودية، يحمل اسم درامتكلي ديفرنت تصفحي المزيد.</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -7002,7 +7001,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>اطلب صابون Clinique 200 مل للعناية اليومية بالبشرة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اطلبه الآن بسهولة فعلاً.</t>
+          <t>اكتشف كلينيك صابون سائل للوجه للبشرة الدهنية 200مل من Clinique، صابون سائل مخصص لتنظيف الوجه ضمن تشكيلة تنظيف الوجه في السعودية، مذكور للبشرة الدهنية في.</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -7024,7 +7023,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>تسوق زيت De La Cruz 65 مل لترطيب البشرة والجسم، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تسوق الآن من منتنيرو، وهو منتج من فئة زيت.</t>
+          <t>تصفح زيت فيتامين E من دي لا كروز 65 مل من De La Cruz، زيت عناية بالبشرة بقوام زيتي خفيف وحجم 65 مل ضمن تشكيلة العناية بالبشرة بالسعودية، تسوقي الآن.</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -7046,7 +7045,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>اكتشف كريم De La Cruz 12 جم للعناية اليومية بالبشرة، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اكتشف التفاصيل كاملة الآن.</t>
+          <t>اطلب الآن كريم فيتامين هـ من دي لا كروز - 12جم من De La Cruz، قوام كريم وفق نوع المنتج الوارد في الاسم ضمن تشكيلة مرطبات في السعودية، يحمل اسم فيتامين هـ.</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7063,12 +7062,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>كريم أساس Estée Lauder 1</t>
+          <t>كريم أساس Estée Lauder درجة 1W1</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>تصفح كريم أساس Estée Lauder لمظهر بشرة متجانس، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تصفح المزيد وتسوقي اليوم فعلاً.</t>
+          <t>اطلعي على كريم أساس 1 دبليو1 دبل وير من استي لودر من Estée Lauder، كريم أساس للوجه من استي لودر ضمن تشكيلة أساس وبرايمر في السعودية تصفحي المزيد.</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7090,7 +7089,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>اطلب كريم أساس Estée Lauder لمظهر بشرة متجانس، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اطلبه الآن بسهولة فعلاً بالفعل.</t>
+          <t>جرّبي كريم أساس دبل وير 1w2 من استي لودر من Estée Lauder، كريم أساس من استي لودر ضمن تشكيلة أساس وبرايمر في السعودية، يحمل تسمية دبل وير اطلبيه اليوم.</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7107,12 +7106,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>كريم أساس Estée Lauder 2</t>
+          <t>كريم أساس Estée Lauder درجة 2W</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>تسوق كريم أساس Estée Lauder لمظهر بشرة متجانس، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تسوق الآن من منتنيرو فعلاً بالفعل.</t>
+          <t>تسوق Estée Lauder كريم أساس مزدوج الثبات من ايستية لودر 2دابليو من Estée Lauder، مستحضر كريم أساس للوجه ضمن تشكيلة أساس وبرايمر في السعودية.</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7134,7 +7133,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>اكتشف مزيل عرق Arm &amp; Hammer 71 جم للعناية اليومية بمنطقة الإبط، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اكتشف التفاصيل كاملة الآن.</t>
+          <t>اطلب ارم اند هامر اسنشيالز مزيل عرق النظافه 71 جم من Arm &amp; Hammer، مزيل عرق صلب للعناية الشخصية اليومية ضمن تشكيلة العناية الشخصية بالسعودية.</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7151,12 +7150,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>مزيل عرق Arm &amp; Hammer 71 جم 2</t>
+          <t>مزيل عرق Arm &amp; Hammer روزماري ولافندر</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>تصفح مزيل عرق Arm &amp; Hammer 71 جم للعناية اليومية بمنطقة الإبط، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تصفح المزيد وتسوقي اليوم.</t>
+          <t>تصفح Arm &amp; Hammer مزيل العرق برائحة الروزماري واللافندر 71 جم من Arm &amp; Hammer، مزيل عرق من ارم اند هامر ضمن تشكيلة العناية الشخصية في السعودية.</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -7178,7 +7177,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>اطلب مزيل عرق Arm &amp; Hammer 28 غ للعناية اليومية بمنطقة الإبط، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اطلبه الآن بسهولة.</t>
+          <t>اطلب الآن Arm &amp; Hammer مزيل مانع للتعرق الترا ماكس من ارم اندهامر28غ من Arm &amp; Hammer، مانع تعرّق من علامة ارم اند هامر ضمن تشكيلة العناية الشخصية في.</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -7195,12 +7194,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>مزيل عرق Arm &amp; Hammer 28 غ 2</t>
+          <t>مزيل عرق Arm &amp; Hammer للنساء 28 غ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>تسوق مزيل عرق Arm &amp; Hammer 28 غ للعناية اليومية بمنطقة الإبط، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. تسوق الآن من منتنيرو.</t>
+          <t>اطلعي على Arm &amp; Hammer مزيل مانع للتعرق الترا ماكس للنساء 28غ من Arm &amp; Hammer، مانع تعرّق من ارم اند هامر ضمن تشكيلة العناية الشخصية في السعودية.</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -7222,7 +7221,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>اكتشف مزيل عرق Arm &amp; Hammer للعناية اليومية بمنطقة الإبط، متوفر أونلاين في السعودية ضمن تشكيلة منتنيرو لمستحضرات التجميل. اكتشف التفاصيل كاملة الآن.</t>
+          <t>جرّبي ارم اند هامر الترا ماكس مزيل عرق ستيك غير معط من Arm &amp; Hammer، مزيل عرق بصيغة ستيك ضمن تشكيلة العناية الشخصية في السعودية، يحمل اسم ألترا ماكس من.</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">

--- a/المنتجات/batch1-merchant-seo.xlsx
+++ b/المنتجات/batch1-merchant-seo.xlsx
@@ -5417,7 +5417,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>اكتشف كونسيلر مايبيلين فيت مي رقم 20 من Maybelline New York، كونسيلر مخصص للوجه ضمن تشكيلة كريمات الإخفاء والتصحيح في السعودية، يحمل تسمية فيت مي من.</t>
+          <t>اكتشف كونسيلر مايبيلين فيت مي رقم 20 من Maybelline New York، كونسيلر مخصص للوجه ضمن تشكيلة كريمات الإخفاء والتصحيح في السعودية، ويحمل رقم الدرجة 20.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>تصفح مسكرة رموش لوريال بانورامار الذهبية من L'Oréal Paris، مستحضر مخصص لتطبيقه على الرموش ضمن تشكيلة ماسكارا في السعودية، تنتمي إلى مجموعة بانوراما من.</t>
+          <t>تصفح مسكرة رموش لوريال بانورامار الذهبية من L'Oréal Paris، مستحضر مخصص لتطبيقه على الرموش ضمن تشكيلة ماسكارا في السعودية، من مجموعة بانوراما الذهبية.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>اطلب الآن Maybelline روج سائل سوبر ستاي انرايفلد من ميبيلين - 30 من Maybelline New York، أحمر شفاه سائل مخصص لمكياج الشفاه ضمن تشكيلة أحمر الشفاه في.</t>
+          <t>اطلب الآن Maybelline روج سائل سوبر ستاي انرايفلد من ميبيلين - 30 من Maybelline New York، أحمر شفاه سائل مخصص لمكياج الشفاه ضمن تشكيلة أحمر الشفاه، درجة 30.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>تصفح Maybelline ميبيلين لاش سينسيشنال سكاي هاي ماسكرا اسود من Maybelline New York، ماسكارا للعين من مجموعة Lash Sensational Sky High ضمن تشكيلة ماسكارا في.</t>
+          <t>تصفح Maybelline ميبيلين لاش سينسيشنال سكاي هاي ماسكرا اسود من Maybelline New York، ماسكارا للعين من مجموعة Lash Sensational Sky High باللون الأسود.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>جرّبي بالمرز مرطب الشفاه بخلاصة جوز الهند 4 جرام من Palmer's، مرطب شفاه يحمل علامة Palmer's ضمن تشكيلة مرطب الشفاه في السعودية، يذكر خلاصة جوز الهند ضمن.</t>
+          <t>جرّبي بالمرز مرطب الشفاه بخلاصة جوز الهند 4 جرام من Palmer's، مرطب شفاه يحمل علامة Palmer's ضمن تشكيلة مرطب الشفاه في السعودية، بخلاصة جوز الهند.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>اطلعي على بالمرز كريم القدمين ماجيك 60 جرام من Palmer's، كريم مخصص للعناية بالقدمين ضمن تشكيلة العناية بالجسم في السعودية، يحمل اسم ماجيك كما ورد في.</t>
+          <t>اطلعي على بالمرز كريم القدمين ماجيك 60 جرام من Palmer's، كريم مخصص للعناية بالقدمين ضمن تشكيلة العناية بالجسم في السعودية، ويحمل اسم ماجيك على العبوة.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>اطلب الآن دوف مقشر الجسم بخلاصة بذور الرمان 298 جم من Dove، مقشر مخصص للاستخدام على الجسم ضمن تشكيلة العناية بالجسم في السعودية، يذكر خلاصة بذور الرمان في.</t>
+          <t>اطلب الآن دوف مقشر الجسم بخلاصة بذور الرمان 298 جم من Dove، مقشر مخصص للاستخدام على الجسم ضمن تشكيلة العناية بالجسم في السعودية، بخلاصة بذور الرمان.</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>اكتشف كلينيك صابون سائل للوجه للبشرة الدهنية 200مل من Clinique، صابون سائل مخصص لتنظيف الوجه ضمن تشكيلة تنظيف الوجه في السعودية، مذكور للبشرة الدهنية في.</t>
+          <t>اكتشف كلينيك صابون سائل للوجه للبشرة الدهنية 200مل من Clinique، صابون سائل مخصص لتنظيف الوجه ضمن تشكيلة تنظيف الوجه في السعودية، للبشرة الدهنية.</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>اطلب الآن Arm &amp; Hammer مزيل مانع للتعرق الترا ماكس من ارم اندهامر28غ من Arm &amp; Hammer، مانع تعرّق من علامة ارم اند هامر ضمن تشكيلة العناية الشخصية في.</t>
+          <t>اطلب الآن Arm &amp; Hammer مزيل مانع للتعرق الترا ماكس من ارم اندهامر28غ من Arm &amp; Hammer، مانع تعرّق من علامة ارم اند هامر ضمن تشكيلة العناية الشخصية.</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>جرّبي ارم اند هامر الترا ماكس مزيل عرق ستيك غير معط من Arm &amp; Hammer، مزيل عرق بصيغة ستيك ضمن تشكيلة العناية الشخصية في السعودية، يحمل اسم ألترا ماكس من.</t>
+          <t>جرّبي ارم اند هامر الترا ماكس مزيل عرق ستيك غير معطر من Arm &amp; Hammer، مزيل عرق بصيغة ستيك ضمن تشكيلة العناية الشخصية في السعودية، من خط ألترا ماكس.</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
